--- a/2026/GALERIA MITRE/Junio/Junio MITRE.xlsx
+++ b/2026/GALERIA MITRE/Junio/Junio MITRE.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GALERIA MITRE\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GALERIA MITRE\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9676EC2-6D8E-4979-B090-74A30369A36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{907A137E-98A5-4F56-8D31-65B2990C84D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="207">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -503,12 +503,6 @@
     <t>UF:</t>
   </si>
   <si>
-    <t>VTO 18/06</t>
-  </si>
-  <si>
-    <t>Julio Doartero - Reparacion de tres baños, de dos mochilas, cambio de canilla y sellado de lavatorio - Mano de obra y materiales</t>
-  </si>
-  <si>
     <t>Transf 22/05</t>
   </si>
   <si>
@@ -518,12 +512,6 @@
     <t>Andes elevadores - Servicio de mantenimiento de ascensores</t>
   </si>
   <si>
-    <t>Transf 05/05</t>
-  </si>
-  <si>
-    <t>Andes elevadores - Reparacion de placa de control de maniobras - Cambio de componentes averiados</t>
-  </si>
-  <si>
     <t>Honorarios Sra. Abogada - Lorena Ferreiro</t>
   </si>
   <si>
@@ -533,12 +521,6 @@
     <t>Cuello Natalia - Desobstruccion columna en baño piso 1</t>
   </si>
   <si>
-    <t>Cuello Natalia - Desobstruccion columna en baño de galeria y desobstruccion en pileta de sotano</t>
-  </si>
-  <si>
-    <t>Cuello Natalia - Desobstruccion de inodoro en entrepiso</t>
-  </si>
-  <si>
     <t>TSG - Municipalidad de avellaneda</t>
   </si>
   <si>
@@ -548,9 +530,6 @@
     <t>Cuota 33/36 - planes de pago - Afip - contrib. de seg. social 06/2022 y 11/2022</t>
   </si>
   <si>
-    <t>Mozart SRL - Recarga de matafuegos vencidos en diciembre</t>
-  </si>
-  <si>
     <t>Debito 22/05</t>
   </si>
   <si>
@@ -575,12 +554,6 @@
     <t>Efectivo</t>
   </si>
   <si>
-    <t>Carrafiele Julio -  Mes de Abril</t>
-  </si>
-  <si>
-    <t>Ivana del Carmen Roldan -  Mes de Abril</t>
-  </si>
-  <si>
     <t>Deposito ya identificado mes anterior</t>
   </si>
   <si>
@@ -636,6 +609,45 @@
   </si>
   <si>
     <t>Local 15: Según los comprobantes adjuntos, se realizaron cuatro transferencias desde la cuenta de titularidad de Capetillo Silvina Vivian por un monto de $100.000,00 cada una. Las operaciones fueron efectuadas el 02/06/2026, el 03/06/2026, el 09/06/2026 y el 17/06/2026. El monto total transferido asciende a $400.000,00.</t>
+  </si>
+  <si>
+    <t>VTO 17/07</t>
+  </si>
+  <si>
+    <t>Carrafiele Julio -  Mes de MAYO</t>
+  </si>
+  <si>
+    <t>Ivana del Carmen Roldan -  Mes de MAYO</t>
+  </si>
+  <si>
+    <t>creo que cobran mes atrasado</t>
+  </si>
+  <si>
+    <t>Transf 22/06</t>
+  </si>
+  <si>
+    <t>Grafica Tauge - Fotocopias BYN</t>
+  </si>
+  <si>
+    <t>Transf 09/06</t>
+  </si>
+  <si>
+    <t>Transf 08/06</t>
+  </si>
+  <si>
+    <t>Transf 18/06</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza</t>
+  </si>
+  <si>
+    <t>Andes elevadores - ReProvision y colocacion de nueva manga de cable para conexionado de indicador de PB por corto en el existente</t>
+  </si>
+  <si>
+    <t>Transf 11/06</t>
+  </si>
+  <si>
+    <t>Servisur - Instalacion tortuga plastica y lampara en escalera</t>
   </si>
 </sst>
 </file>
@@ -1302,7 +1314,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="234">
+  <cellXfs count="239">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1547,158 +1559,167 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2092,68 +2113,68 @@
       <c r="D3" s="98"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="180" t="s">
+      <c r="A4" s="193" t="s">
         <v>153</v>
       </c>
-      <c r="B4" s="180"/>
+      <c r="B4" s="193"/>
       <c r="C4" s="99"/>
       <c r="D4" s="99"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="180"/>
-      <c r="B5" s="180"/>
+      <c r="A5" s="193"/>
+      <c r="B5" s="193"/>
       <c r="C5" s="99"/>
       <c r="D5" s="99"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="180"/>
-      <c r="B6" s="180"/>
+      <c r="A6" s="193"/>
+      <c r="B6" s="193"/>
       <c r="C6" s="99"/>
       <c r="D6" s="99"/>
     </row>
     <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="180"/>
-      <c r="B7" s="180"/>
+      <c r="A7" s="193"/>
+      <c r="B7" s="193"/>
       <c r="C7" s="99"/>
       <c r="D7" s="99"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B9" s="191" t="s">
-        <v>158</v>
+      <c r="B9" s="188" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B10" s="191"/>
+      <c r="B10" s="188"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B11" s="191"/>
+      <c r="B11" s="188"/>
     </row>
     <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="180" t="s">
+      <c r="A14" s="193" t="s">
         <v>150</v>
       </c>
-      <c r="B14" s="180"/>
-      <c r="C14" s="180"/>
-      <c r="D14" s="180"/>
+      <c r="B14" s="193"/>
+      <c r="C14" s="193"/>
+      <c r="D14" s="193"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="180"/>
-      <c r="B15" s="180"/>
-      <c r="C15" s="180"/>
-      <c r="D15" s="180"/>
+      <c r="A15" s="193"/>
+      <c r="B15" s="193"/>
+      <c r="C15" s="193"/>
+      <c r="D15" s="193"/>
     </row>
     <row r="16" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="180"/>
-      <c r="B16" s="180"/>
-      <c r="C16" s="180"/>
-      <c r="D16" s="180"/>
+      <c r="A16" s="193"/>
+      <c r="B16" s="193"/>
+      <c r="C16" s="193"/>
+      <c r="D16" s="193"/>
     </row>
     <row r="17" spans="1:7" ht="156.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="180"/>
-      <c r="B17" s="180"/>
-      <c r="C17" s="180"/>
-      <c r="D17" s="180"/>
+      <c r="A17" s="193"/>
+      <c r="B17" s="193"/>
+      <c r="C17" s="193"/>
+      <c r="D17" s="193"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2167,6 +2188,10 @@
       <c r="B21" s="11"/>
       <c r="C21" s="8"/>
       <c r="D21" s="12"/>
+      <c r="E21" s="234" t="s">
+        <v>197</v>
+      </c>
+      <c r="F21" s="234"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="25" t="s">
@@ -2175,16 +2200,20 @@
       <c r="B22" s="25"/>
       <c r="C22" s="23"/>
       <c r="D22" s="23"/>
+      <c r="E22" s="234"/>
+      <c r="F22" s="234"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="188" t="s">
-        <v>182</v>
-      </c>
-      <c r="B23" s="189"/>
+      <c r="A23" s="186" t="s">
+        <v>195</v>
+      </c>
+      <c r="B23" s="187"/>
       <c r="C23" s="113">
         <v>939981.1</v>
       </c>
       <c r="D23" s="69"/>
+      <c r="E23" s="234"/>
+      <c r="F23" s="234"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
@@ -2195,6 +2224,8 @@
         <v>-148047.01999999999</v>
       </c>
       <c r="D24" s="69"/>
+      <c r="E24" s="234"/>
+      <c r="F24" s="234"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
@@ -2205,6 +2236,8 @@
         <v>0.92</v>
       </c>
       <c r="D25" s="69"/>
+      <c r="E25" s="234"/>
+      <c r="F25" s="234"/>
       <c r="G25" s="125"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -2217,16 +2250,20 @@
         <v>791935</v>
       </c>
       <c r="D26" s="43"/>
+      <c r="E26" s="234"/>
+      <c r="F26" s="234"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="188" t="s">
-        <v>183</v>
-      </c>
-      <c r="B27" s="189"/>
+      <c r="A27" s="186" t="s">
+        <v>196</v>
+      </c>
+      <c r="B27" s="187"/>
       <c r="C27" s="113">
         <v>849606.52</v>
       </c>
       <c r="D27" s="69"/>
+      <c r="E27" s="234"/>
+      <c r="F27" s="234"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
@@ -2237,6 +2274,8 @@
         <v>-210277.64</v>
       </c>
       <c r="D28" s="101"/>
+      <c r="E28" s="234"/>
+      <c r="F28" s="234"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
@@ -2261,7 +2300,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="128">
@@ -2311,7 +2350,7 @@
     </row>
     <row r="36" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="103" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B36" s="96"/>
       <c r="C36" s="113"/>
@@ -2320,27 +2359,27 @@
     </row>
     <row r="37" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="103" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="B37" s="96"/>
-      <c r="C37" s="113">
-        <v>135000</v>
+      <c r="C37" s="235">
+        <v>90000</v>
       </c>
       <c r="D37" s="111" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="G37" s="13"/>
     </row>
     <row r="38" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="103" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B38" s="96"/>
-      <c r="C38" s="113">
+      <c r="C38" s="235">
         <v>200000</v>
       </c>
       <c r="D38" s="111" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="G38" s="13"/>
     </row>
@@ -2352,7 +2391,7 @@
       <c r="C39" s="156"/>
       <c r="D39" s="71">
         <f>SUM(C36:C38)</f>
-        <v>335000</v>
+        <v>290000</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -2364,15 +2403,15 @@
       <c r="D40" s="49"/>
     </row>
     <row r="41" spans="1:7" s="32" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="184" t="s">
+      <c r="A41" s="189" t="s">
         <v>132</v>
       </c>
-      <c r="B41" s="185"/>
+      <c r="B41" s="190"/>
       <c r="C41" s="127">
         <v>111379</v>
       </c>
       <c r="D41" s="126" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2406,10 +2445,10 @@
       <c r="F44" s="104"/>
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="184" t="s">
-        <v>172</v>
-      </c>
-      <c r="B45" s="185"/>
+      <c r="A45" s="189" t="s">
+        <v>166</v>
+      </c>
+      <c r="B45" s="190"/>
       <c r="C45" s="131">
         <v>11596.99</v>
       </c>
@@ -2419,10 +2458,10 @@
       <c r="F45" s="104"/>
     </row>
     <row r="46" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="184" t="s">
+      <c r="A46" s="189" t="s">
         <v>131</v>
       </c>
-      <c r="B46" s="185"/>
+      <c r="B46" s="190"/>
       <c r="C46" s="131">
         <v>11930.96</v>
       </c>
@@ -2436,10 +2475,10 @@
         <v>66</v>
       </c>
       <c r="B47" s="69" t="s">
-        <v>178</v>
-      </c>
-      <c r="C47" s="116">
-        <v>0</v>
+        <v>171</v>
+      </c>
+      <c r="C47" s="236">
+        <v>92127.95</v>
       </c>
       <c r="D47" s="110"/>
     </row>
@@ -2448,10 +2487,10 @@
         <v>67</v>
       </c>
       <c r="B48" s="69" t="s">
-        <v>178</v>
-      </c>
-      <c r="C48" s="116">
-        <v>0</v>
+        <v>171</v>
+      </c>
+      <c r="C48" s="236">
+        <v>10236.44</v>
       </c>
       <c r="D48" s="110">
         <f>D47</f>
@@ -2463,10 +2502,10 @@
         <v>68</v>
       </c>
       <c r="B49" s="69" t="s">
-        <v>178</v>
-      </c>
-      <c r="C49" s="116">
-        <v>0</v>
+        <v>171</v>
+      </c>
+      <c r="C49" s="236">
+        <v>200516.68</v>
       </c>
       <c r="D49" s="108">
         <f>D47</f>
@@ -2481,7 +2520,7 @@
       <c r="C50" s="31"/>
       <c r="D50" s="73">
         <f>SUM(C44:C49)</f>
-        <v>23527.949999999997</v>
+        <v>326409.02</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -2497,33 +2536,35 @@
         <v>128</v>
       </c>
       <c r="B52" s="69"/>
-      <c r="C52" s="116">
-        <v>0</v>
-      </c>
-      <c r="D52" s="107"/>
+      <c r="C52" s="236">
+        <v>324333.89</v>
+      </c>
+      <c r="D52" s="107" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="53" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="69" t="s">
         <v>127</v>
       </c>
       <c r="B53" s="69"/>
-      <c r="C53" s="116">
-        <v>130169.33</v>
+      <c r="C53" s="236">
+        <v>164200</v>
       </c>
       <c r="D53" s="107" t="s">
-        <v>163</v>
+        <v>201</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="69" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B54" s="69"/>
-      <c r="C54" s="116">
-        <v>1322015.6299999999</v>
+      <c r="C54" s="236">
+        <v>1405375.2</v>
       </c>
       <c r="D54" s="107" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2535,19 +2576,19 @@
         <v>35276.449999999997</v>
       </c>
       <c r="D55" s="107" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="69" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B56" s="132"/>
-      <c r="C56" s="116">
+      <c r="C56" s="236">
         <v>78534</v>
       </c>
       <c r="D56" s="107" t="s">
-        <v>163</v>
+        <v>200</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2558,7 +2599,7 @@
       <c r="C57" s="29"/>
       <c r="D57" s="73">
         <f>SUM(C52:C56)</f>
-        <v>1565995.41</v>
+        <v>2007719.5399999998</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2570,107 +2611,105 @@
       <c r="D58" s="76"/>
     </row>
     <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="186" t="s">
-        <v>162</v>
-      </c>
-      <c r="B59" s="187"/>
-      <c r="C59" s="116">
-        <v>171600</v>
+      <c r="A59" s="191" t="s">
+        <v>160</v>
+      </c>
+      <c r="B59" s="192"/>
+      <c r="C59" s="236">
+        <v>202000</v>
       </c>
       <c r="D59" s="107" t="s">
-        <v>163</v>
+        <v>202</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="186" t="s">
-        <v>164</v>
-      </c>
-      <c r="B60" s="187"/>
-      <c r="C60" s="116">
-        <v>326000</v>
+      <c r="A60" s="191" t="s">
+        <v>204</v>
+      </c>
+      <c r="B60" s="192"/>
+      <c r="C60" s="236">
+        <v>229900</v>
       </c>
       <c r="D60" s="107" t="s">
-        <v>163</v>
+        <v>202</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="186" t="s">
-        <v>180</v>
-      </c>
-      <c r="B61" s="187"/>
+      <c r="A61" s="191" t="s">
+        <v>173</v>
+      </c>
+      <c r="B61" s="192"/>
       <c r="C61" s="116">
         <v>90000</v>
       </c>
       <c r="D61" s="162" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="184" t="s">
-        <v>159</v>
-      </c>
-      <c r="B62" s="185"/>
-      <c r="C62" s="116">
-        <v>180000</v>
+      <c r="A62" s="189" t="s">
+        <v>206</v>
+      </c>
+      <c r="B62" s="190"/>
+      <c r="C62" s="236">
+        <v>35000</v>
       </c>
       <c r="D62" s="109" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E62" s="116"/>
       <c r="F62" s="37"/>
     </row>
     <row r="63" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="184" t="s">
-        <v>173</v>
-      </c>
-      <c r="B63" s="185"/>
-      <c r="C63" s="116">
-        <v>1745880</v>
+      <c r="A63" s="237"/>
+      <c r="B63" s="238"/>
+      <c r="C63" s="236">
+        <v>9395</v>
       </c>
       <c r="D63" s="109" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E63" s="116"/>
       <c r="F63" s="37"/>
     </row>
     <row r="64" spans="1:6" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="186" t="s">
-        <v>168</v>
-      </c>
-      <c r="B64" s="187"/>
-      <c r="C64" s="116">
-        <v>77600</v>
+      <c r="A64" s="191" t="s">
+        <v>199</v>
+      </c>
+      <c r="B64" s="192"/>
+      <c r="C64" s="236">
+        <v>18300</v>
       </c>
       <c r="D64" s="109" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E64" s="157"/>
       <c r="F64" s="37"/>
     </row>
     <row r="65" spans="1:6" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="186" t="s">
-        <v>169</v>
-      </c>
-      <c r="B65" s="187"/>
-      <c r="C65" s="116">
-        <v>95700</v>
-      </c>
-      <c r="D65" s="109" t="s">
-        <v>166</v>
+      <c r="A65" s="191" t="s">
+        <v>203</v>
+      </c>
+      <c r="B65" s="192"/>
+      <c r="C65" s="236">
+        <v>225200</v>
+      </c>
+      <c r="D65" s="107" t="s">
+        <v>202</v>
       </c>
       <c r="E65" s="157"/>
       <c r="F65" s="37"/>
     </row>
     <row r="66" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="186" t="s">
-        <v>167</v>
-      </c>
-      <c r="B66" s="187"/>
+      <c r="A66" s="191" t="s">
+        <v>163</v>
+      </c>
+      <c r="B66" s="192"/>
       <c r="C66" s="116">
         <v>46200</v>
       </c>
       <c r="D66" s="109" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E66" s="37"/>
       <c r="F66" s="37"/>
@@ -2683,7 +2722,7 @@
       <c r="C67" s="23"/>
       <c r="D67" s="79">
         <f>SUM(C59:C66)</f>
-        <v>2732980</v>
+        <v>855995</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2695,10 +2734,10 @@
       <c r="D68" s="76"/>
     </row>
     <row r="69" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="184" t="s">
+      <c r="A69" s="189" t="s">
         <v>74</v>
       </c>
-      <c r="B69" s="185"/>
+      <c r="B69" s="190"/>
       <c r="C69" s="116">
         <v>60000</v>
       </c>
@@ -2733,11 +2772,11 @@
       <c r="D72" s="82"/>
     </row>
     <row r="73" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="181" t="s">
+      <c r="A73" s="194" t="s">
         <v>69</v>
       </c>
-      <c r="B73" s="182"/>
-      <c r="C73" s="183"/>
+      <c r="B73" s="195"/>
+      <c r="C73" s="196"/>
       <c r="D73" s="83"/>
     </row>
     <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2754,7 +2793,7 @@
       <c r="C75" s="86"/>
       <c r="D75" s="87">
         <f>(SUM(D23:D73))</f>
-        <v>6780039.5600000005</v>
+        <v>5602659.7599999998</v>
       </c>
       <c r="E75" s="37"/>
       <c r="F75" s="37"/>
@@ -2777,14 +2816,14 @@
       <c r="D78" s="89"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="188"/>
-      <c r="B79" s="189"/>
+      <c r="A79" s="186"/>
+      <c r="B79" s="187"/>
       <c r="C79" s="77"/>
       <c r="D79" s="75"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="188"/>
-      <c r="B80" s="189"/>
+      <c r="A80" s="186"/>
+      <c r="B80" s="187"/>
       <c r="C80" s="77"/>
       <c r="D80" s="75"/>
     </row>
@@ -2834,7 +2873,7 @@
       </c>
       <c r="B89" s="68">
         <f>D75</f>
-        <v>6780039.5600000005</v>
+        <v>5602659.7599999998</v>
       </c>
       <c r="C89" s="37"/>
     </row>
@@ -2844,7 +2883,7 @@
       </c>
       <c r="B90" s="68">
         <f>D75-D73</f>
-        <v>6780039.5600000005</v>
+        <v>5602659.7599999998</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2899,7 +2938,7 @@
     </row>
     <row r="100" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="133" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B100" s="106">
         <v>-50000</v>
@@ -2907,7 +2946,7 @@
     </row>
     <row r="101" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="133" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B101" s="106">
         <v>-46400</v>
@@ -2927,7 +2966,7 @@
       </c>
       <c r="B103" s="106">
         <f>-B90</f>
-        <v>-6780039.5600000005</v>
+        <v>-5602659.7599999998</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
@@ -2945,7 +2984,7 @@
       </c>
       <c r="B105" s="94">
         <f>SUM(B97:B104)</f>
-        <v>-14222.14999999851</v>
+        <v>1163157.6500000022</v>
       </c>
       <c r="D105" s="129"/>
     </row>
@@ -2956,7 +2995,7 @@
     </row>
     <row r="107" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="146" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B107" s="147">
         <v>1490504.61</v>
@@ -2982,18 +3021,18 @@
       <c r="D111" s="130"/>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="190" t="s">
+      <c r="A112" s="185" t="s">
         <v>50</v>
       </c>
-      <c r="B112" s="190"/>
+      <c r="B112" s="185"/>
     </row>
     <row r="113" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="190"/>
-      <c r="B113" s="190"/>
+      <c r="A113" s="185"/>
+      <c r="B113" s="185"/>
     </row>
     <row r="114" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="90" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="B114" s="28">
         <v>600000</v>
@@ -3013,13 +3052,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A112:B113"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A61:B61"/>
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A14:D17"/>
     <mergeCell ref="A73:C73"/>
@@ -3034,6 +3066,13 @@
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A112:B113"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A61:B61"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3068,17 +3107,17 @@
   <sheetData>
     <row r="1" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
-      <c r="B1" s="192" t="s">
+      <c r="B1" s="203" t="s">
         <v>153</v>
       </c>
-      <c r="C1" s="193"/>
-      <c r="D1" s="193"/>
-      <c r="E1" s="193"/>
-      <c r="F1" s="193"/>
-      <c r="G1" s="193"/>
-      <c r="H1" s="193"/>
-      <c r="I1" s="193"/>
-      <c r="J1" s="194"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="204"/>
+      <c r="I1" s="204"/>
+      <c r="J1" s="205"/>
       <c r="K1" s="142" t="s">
         <v>4</v>
       </c>
@@ -3096,15 +3135,15 @@
     </row>
     <row r="2" spans="1:18" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6"/>
-      <c r="B2" s="195"/>
-      <c r="C2" s="196"/>
-      <c r="D2" s="196"/>
-      <c r="E2" s="196"/>
-      <c r="F2" s="196"/>
-      <c r="G2" s="196"/>
-      <c r="H2" s="196"/>
-      <c r="I2" s="196"/>
-      <c r="J2" s="197"/>
+      <c r="B2" s="206"/>
+      <c r="C2" s="207"/>
+      <c r="D2" s="207"/>
+      <c r="E2" s="207"/>
+      <c r="F2" s="207"/>
+      <c r="G2" s="207"/>
+      <c r="H2" s="207"/>
+      <c r="I2" s="207"/>
+      <c r="J2" s="208"/>
       <c r="K2" s="144" t="s">
         <v>63</v>
       </c>
@@ -3117,28 +3156,28 @@
     </row>
     <row r="3" spans="1:18" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
-      <c r="B3" s="211" t="s">
+      <c r="B3" s="220" t="s">
         <v>150</v>
       </c>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="212"/>
-      <c r="G3" s="212"/>
-      <c r="H3" s="212"/>
-      <c r="I3" s="212"/>
-      <c r="J3" s="212"/>
-      <c r="K3" s="212"/>
-      <c r="L3" s="212"/>
-      <c r="M3" s="212"/>
-      <c r="N3" s="212"/>
-      <c r="O3" s="213"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="221"/>
+      <c r="E3" s="221"/>
+      <c r="F3" s="221"/>
+      <c r="G3" s="221"/>
+      <c r="H3" s="221"/>
+      <c r="I3" s="221"/>
+      <c r="J3" s="221"/>
+      <c r="K3" s="221"/>
+      <c r="L3" s="221"/>
+      <c r="M3" s="221"/>
+      <c r="N3" s="221"/>
+      <c r="O3" s="222"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="214" t="s">
+      <c r="A4" s="197" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="216" t="s">
+      <c r="B4" s="199" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="201" t="s">
@@ -3159,48 +3198,48 @@
       <c r="H4" s="201" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="206" t="s">
+      <c r="I4" s="215" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="203" t="s">
+      <c r="J4" s="213" t="s">
         <v>46</v>
       </c>
-      <c r="K4" s="203" t="s">
+      <c r="K4" s="213" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="203" t="s">
+      <c r="L4" s="213" t="s">
         <v>45</v>
       </c>
-      <c r="M4" s="209" t="s">
+      <c r="M4" s="218" t="s">
         <v>58</v>
       </c>
       <c r="N4" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="O4" s="198" t="s">
+      <c r="O4" s="209" t="s">
         <v>56</v>
       </c>
       <c r="R4" s="37"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="215"/>
-      <c r="B5" s="217"/>
-      <c r="C5" s="205"/>
-      <c r="D5" s="205"/>
-      <c r="E5" s="205"/>
-      <c r="F5" s="205"/>
-      <c r="G5" s="205"/>
-      <c r="H5" s="202"/>
-      <c r="I5" s="207"/>
-      <c r="J5" s="204"/>
-      <c r="K5" s="208"/>
-      <c r="L5" s="204"/>
-      <c r="M5" s="210"/>
+      <c r="A5" s="198"/>
+      <c r="B5" s="200"/>
+      <c r="C5" s="202"/>
+      <c r="D5" s="202"/>
+      <c r="E5" s="202"/>
+      <c r="F5" s="202"/>
+      <c r="G5" s="202"/>
+      <c r="H5" s="212"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
+      <c r="K5" s="217"/>
+      <c r="L5" s="214"/>
+      <c r="M5" s="219"/>
       <c r="N5" s="46" t="str">
         <f>RESUMEN!B9</f>
-        <v>VTO 18/06</v>
-      </c>
-      <c r="O5" s="199"/>
+        <v>VTO 17/07</v>
+      </c>
+      <c r="O5" s="210"/>
     </row>
     <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
@@ -4052,14 +4091,14 @@
     </row>
     <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
-      <c r="B21" s="229">
+      <c r="B21" s="180">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="C21" s="229" t="s">
+      <c r="C21" s="180" t="s">
         <v>118</v>
       </c>
-      <c r="D21" s="229" t="s">
+      <c r="D21" s="180" t="s">
         <v>87</v>
       </c>
       <c r="E21" s="51">
@@ -4104,7 +4143,7 @@
         <v>0.15</v>
       </c>
       <c r="Q21" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="R21" s="37"/>
     </row>
@@ -6343,7 +6382,7 @@
         <v>0.55000000000000027</v>
       </c>
       <c r="Q61" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
     </row>
     <row r="62" spans="2:17" x14ac:dyDescent="0.3">
@@ -6576,92 +6615,87 @@
     </row>
     <row r="68" spans="2:16" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="69" spans="2:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D69" s="200" t="s">
+      <c r="D69" s="211" t="s">
         <v>70</v>
       </c>
-      <c r="E69" s="200"/>
-      <c r="F69" s="200"/>
-      <c r="G69" s="200"/>
-      <c r="H69" s="200"/>
-      <c r="I69" s="200"/>
-      <c r="J69" s="200"/>
-      <c r="K69" s="200"/>
-      <c r="L69" s="200"/>
-      <c r="M69" s="200"/>
-      <c r="N69" s="200"/>
+      <c r="E69" s="211"/>
+      <c r="F69" s="211"/>
+      <c r="G69" s="211"/>
+      <c r="H69" s="211"/>
+      <c r="I69" s="211"/>
+      <c r="J69" s="211"/>
+      <c r="K69" s="211"/>
+      <c r="L69" s="211"/>
+      <c r="M69" s="211"/>
+      <c r="N69" s="211"/>
     </row>
     <row r="70" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D70" s="200"/>
-      <c r="E70" s="200"/>
-      <c r="F70" s="200"/>
-      <c r="G70" s="200"/>
-      <c r="H70" s="200"/>
-      <c r="I70" s="200"/>
-      <c r="J70" s="200"/>
-      <c r="K70" s="200"/>
-      <c r="L70" s="200"/>
-      <c r="M70" s="200"/>
-      <c r="N70" s="200"/>
+      <c r="D70" s="211"/>
+      <c r="E70" s="211"/>
+      <c r="F70" s="211"/>
+      <c r="G70" s="211"/>
+      <c r="H70" s="211"/>
+      <c r="I70" s="211"/>
+      <c r="J70" s="211"/>
+      <c r="K70" s="211"/>
+      <c r="L70" s="211"/>
+      <c r="M70" s="211"/>
+      <c r="N70" s="211"/>
     </row>
     <row r="71" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D71" s="200"/>
-      <c r="E71" s="200"/>
-      <c r="F71" s="200"/>
-      <c r="G71" s="200"/>
-      <c r="H71" s="200"/>
-      <c r="I71" s="200"/>
-      <c r="J71" s="200"/>
-      <c r="K71" s="200"/>
-      <c r="L71" s="200"/>
-      <c r="M71" s="200"/>
-      <c r="N71" s="200"/>
+      <c r="D71" s="211"/>
+      <c r="E71" s="211"/>
+      <c r="F71" s="211"/>
+      <c r="G71" s="211"/>
+      <c r="H71" s="211"/>
+      <c r="I71" s="211"/>
+      <c r="J71" s="211"/>
+      <c r="K71" s="211"/>
+      <c r="L71" s="211"/>
+      <c r="M71" s="211"/>
+      <c r="N71" s="211"/>
     </row>
     <row r="72" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D72" s="200"/>
-      <c r="E72" s="200"/>
-      <c r="F72" s="200"/>
-      <c r="G72" s="200"/>
-      <c r="H72" s="200"/>
-      <c r="I72" s="200"/>
-      <c r="J72" s="200"/>
-      <c r="K72" s="200"/>
-      <c r="L72" s="200"/>
-      <c r="M72" s="200"/>
-      <c r="N72" s="200"/>
+      <c r="D72" s="211"/>
+      <c r="E72" s="211"/>
+      <c r="F72" s="211"/>
+      <c r="G72" s="211"/>
+      <c r="H72" s="211"/>
+      <c r="I72" s="211"/>
+      <c r="J72" s="211"/>
+      <c r="K72" s="211"/>
+      <c r="L72" s="211"/>
+      <c r="M72" s="211"/>
+      <c r="N72" s="211"/>
     </row>
     <row r="73" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D73" s="200"/>
-      <c r="E73" s="200"/>
-      <c r="F73" s="200"/>
-      <c r="G73" s="200"/>
-      <c r="H73" s="200"/>
-      <c r="I73" s="200"/>
-      <c r="J73" s="200"/>
-      <c r="K73" s="200"/>
-      <c r="L73" s="200"/>
-      <c r="M73" s="200"/>
-      <c r="N73" s="200"/>
+      <c r="D73" s="211"/>
+      <c r="E73" s="211"/>
+      <c r="F73" s="211"/>
+      <c r="G73" s="211"/>
+      <c r="H73" s="211"/>
+      <c r="I73" s="211"/>
+      <c r="J73" s="211"/>
+      <c r="K73" s="211"/>
+      <c r="L73" s="211"/>
+      <c r="M73" s="211"/>
+      <c r="N73" s="211"/>
     </row>
     <row r="74" spans="2:16" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D74" s="200"/>
-      <c r="E74" s="200"/>
-      <c r="F74" s="200"/>
-      <c r="G74" s="200"/>
-      <c r="H74" s="200"/>
-      <c r="I74" s="200"/>
-      <c r="J74" s="200"/>
-      <c r="K74" s="200"/>
-      <c r="L74" s="200"/>
-      <c r="M74" s="200"/>
-      <c r="N74" s="200"/>
+      <c r="D74" s="211"/>
+      <c r="E74" s="211"/>
+      <c r="F74" s="211"/>
+      <c r="G74" s="211"/>
+      <c r="H74" s="211"/>
+      <c r="I74" s="211"/>
+      <c r="J74" s="211"/>
+      <c r="K74" s="211"/>
+      <c r="L74" s="211"/>
+      <c r="M74" s="211"/>
+      <c r="N74" s="211"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
     <mergeCell ref="B1:J2"/>
     <mergeCell ref="O4:O5"/>
     <mergeCell ref="D69:N74"/>
@@ -6674,6 +6708,11 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="B3:O3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -6703,7 +6742,7 @@
         <v>157</v>
       </c>
       <c r="D4" s="154" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="H4" s="150"/>
     </row>
@@ -6715,34 +6754,34 @@
       <c r="J5" s="104"/>
     </row>
     <row r="6" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C6" s="220" t="s">
-        <v>189</v>
-      </c>
-      <c r="D6" s="221"/>
-      <c r="E6" s="221"/>
-      <c r="F6" s="221"/>
-      <c r="G6" s="221"/>
-      <c r="H6" s="222"/>
+      <c r="C6" s="223" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6" s="224"/>
+      <c r="E6" s="224"/>
+      <c r="F6" s="224"/>
+      <c r="G6" s="224"/>
+      <c r="H6" s="225"/>
       <c r="I6" s="104"/>
       <c r="J6" s="104"/>
     </row>
     <row r="7" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C7" s="223"/>
-      <c r="D7" s="224"/>
-      <c r="E7" s="224"/>
-      <c r="F7" s="224"/>
-      <c r="G7" s="224"/>
-      <c r="H7" s="225"/>
+      <c r="C7" s="226"/>
+      <c r="D7" s="227"/>
+      <c r="E7" s="227"/>
+      <c r="F7" s="227"/>
+      <c r="G7" s="227"/>
+      <c r="H7" s="228"/>
       <c r="I7" s="104"/>
       <c r="J7" s="104"/>
     </row>
     <row r="8" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C8" s="226"/>
-      <c r="D8" s="227"/>
-      <c r="E8" s="227"/>
-      <c r="F8" s="227"/>
-      <c r="G8" s="227"/>
-      <c r="H8" s="228"/>
+      <c r="C8" s="229"/>
+      <c r="D8" s="230"/>
+      <c r="E8" s="230"/>
+      <c r="F8" s="230"/>
+      <c r="G8" s="230"/>
+      <c r="H8" s="231"/>
       <c r="I8" s="104"/>
       <c r="J8" s="104"/>
     </row>
@@ -6773,7 +6812,7 @@
         <v>157</v>
       </c>
       <c r="D12" s="161" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="H12" s="150"/>
     </row>
@@ -6783,30 +6822,30 @@
       <c r="H13" s="150"/>
     </row>
     <row r="14" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C14" s="220" t="s">
-        <v>191</v>
-      </c>
-      <c r="D14" s="221"/>
-      <c r="E14" s="221"/>
-      <c r="F14" s="221"/>
-      <c r="G14" s="221"/>
-      <c r="H14" s="222"/>
+      <c r="C14" s="223" t="s">
+        <v>182</v>
+      </c>
+      <c r="D14" s="224"/>
+      <c r="E14" s="224"/>
+      <c r="F14" s="224"/>
+      <c r="G14" s="224"/>
+      <c r="H14" s="225"/>
     </row>
     <row r="15" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C15" s="223"/>
-      <c r="D15" s="224"/>
-      <c r="E15" s="224"/>
-      <c r="F15" s="224"/>
-      <c r="G15" s="224"/>
-      <c r="H15" s="225"/>
+      <c r="C15" s="226"/>
+      <c r="D15" s="227"/>
+      <c r="E15" s="227"/>
+      <c r="F15" s="227"/>
+      <c r="G15" s="227"/>
+      <c r="H15" s="228"/>
     </row>
     <row r="16" spans="3:10" ht="67.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C16" s="226"/>
-      <c r="D16" s="227"/>
-      <c r="E16" s="227"/>
-      <c r="F16" s="227"/>
-      <c r="G16" s="227"/>
-      <c r="H16" s="228"/>
+      <c r="C16" s="229"/>
+      <c r="D16" s="230"/>
+      <c r="E16" s="230"/>
+      <c r="F16" s="230"/>
+      <c r="G16" s="230"/>
+      <c r="H16" s="231"/>
     </row>
     <row r="18" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="19" spans="3:8" x14ac:dyDescent="0.3">
@@ -6827,7 +6866,7 @@
         <v>157</v>
       </c>
       <c r="D20" s="170" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="H20" s="150"/>
     </row>
@@ -6837,30 +6876,30 @@
       <c r="H21" s="150"/>
     </row>
     <row r="22" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C22" s="220" t="s">
-        <v>193</v>
-      </c>
-      <c r="D22" s="221"/>
-      <c r="E22" s="221"/>
-      <c r="F22" s="221"/>
-      <c r="G22" s="221"/>
-      <c r="H22" s="222"/>
+      <c r="C22" s="223" t="s">
+        <v>184</v>
+      </c>
+      <c r="D22" s="224"/>
+      <c r="E22" s="224"/>
+      <c r="F22" s="224"/>
+      <c r="G22" s="224"/>
+      <c r="H22" s="225"/>
     </row>
     <row r="23" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C23" s="223"/>
-      <c r="D23" s="224"/>
-      <c r="E23" s="224"/>
-      <c r="F23" s="224"/>
-      <c r="G23" s="224"/>
-      <c r="H23" s="225"/>
+      <c r="C23" s="226"/>
+      <c r="D23" s="227"/>
+      <c r="E23" s="227"/>
+      <c r="F23" s="227"/>
+      <c r="G23" s="227"/>
+      <c r="H23" s="228"/>
     </row>
     <row r="24" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C24" s="226"/>
-      <c r="D24" s="227"/>
-      <c r="E24" s="227"/>
-      <c r="F24" s="227"/>
-      <c r="G24" s="227"/>
-      <c r="H24" s="228"/>
+      <c r="C24" s="229"/>
+      <c r="D24" s="230"/>
+      <c r="E24" s="230"/>
+      <c r="F24" s="230"/>
+      <c r="G24" s="230"/>
+      <c r="H24" s="231"/>
     </row>
     <row r="26" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="27" spans="3:8" x14ac:dyDescent="0.3">
@@ -6881,7 +6920,7 @@
         <v>157</v>
       </c>
       <c r="D28" s="174" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="H28" s="150"/>
     </row>
@@ -6891,30 +6930,30 @@
       <c r="H29" s="150"/>
     </row>
     <row r="30" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C30" s="220" t="s">
-        <v>195</v>
-      </c>
-      <c r="D30" s="221"/>
-      <c r="E30" s="221"/>
-      <c r="F30" s="221"/>
-      <c r="G30" s="221"/>
-      <c r="H30" s="222"/>
+      <c r="C30" s="223" t="s">
+        <v>186</v>
+      </c>
+      <c r="D30" s="224"/>
+      <c r="E30" s="224"/>
+      <c r="F30" s="224"/>
+      <c r="G30" s="224"/>
+      <c r="H30" s="225"/>
     </row>
     <row r="31" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C31" s="223"/>
-      <c r="D31" s="224"/>
-      <c r="E31" s="224"/>
-      <c r="F31" s="224"/>
-      <c r="G31" s="224"/>
-      <c r="H31" s="225"/>
+      <c r="C31" s="226"/>
+      <c r="D31" s="227"/>
+      <c r="E31" s="227"/>
+      <c r="F31" s="227"/>
+      <c r="G31" s="227"/>
+      <c r="H31" s="228"/>
     </row>
     <row r="32" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C32" s="226"/>
-      <c r="D32" s="227"/>
-      <c r="E32" s="227"/>
-      <c r="F32" s="227"/>
-      <c r="G32" s="227"/>
-      <c r="H32" s="228"/>
+      <c r="C32" s="229"/>
+      <c r="D32" s="230"/>
+      <c r="E32" s="230"/>
+      <c r="F32" s="230"/>
+      <c r="G32" s="230"/>
+      <c r="H32" s="231"/>
     </row>
     <row r="34" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
@@ -6929,72 +6968,72 @@
       <c r="F35" s="148"/>
       <c r="G35" s="148"/>
       <c r="H35" s="149"/>
-      <c r="I35" s="218" t="s">
-        <v>198</v>
-      </c>
-      <c r="J35" s="219"/>
-      <c r="K35" s="219"/>
-      <c r="L35" s="219"/>
+      <c r="I35" s="232" t="s">
+        <v>189</v>
+      </c>
+      <c r="J35" s="233"/>
+      <c r="K35" s="233"/>
+      <c r="L35" s="233"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C36" s="160" t="s">
         <v>157</v>
       </c>
       <c r="D36" s="161" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="H36" s="150"/>
-      <c r="I36" s="218"/>
-      <c r="J36" s="219"/>
-      <c r="K36" s="219"/>
-      <c r="L36" s="219"/>
+      <c r="I36" s="232"/>
+      <c r="J36" s="233"/>
+      <c r="K36" s="233"/>
+      <c r="L36" s="233"/>
     </row>
     <row r="37" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C37" s="160"/>
       <c r="D37" s="161"/>
       <c r="H37" s="150"/>
-      <c r="I37" s="218"/>
-      <c r="J37" s="219"/>
-      <c r="K37" s="219"/>
-      <c r="L37" s="219"/>
+      <c r="I37" s="232"/>
+      <c r="J37" s="233"/>
+      <c r="K37" s="233"/>
+      <c r="L37" s="233"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C38" s="220" t="s">
-        <v>197</v>
-      </c>
-      <c r="D38" s="221"/>
-      <c r="E38" s="221"/>
-      <c r="F38" s="221"/>
-      <c r="G38" s="221"/>
-      <c r="H38" s="222"/>
-      <c r="I38" s="218"/>
-      <c r="J38" s="219"/>
-      <c r="K38" s="219"/>
-      <c r="L38" s="219"/>
+      <c r="C38" s="223" t="s">
+        <v>188</v>
+      </c>
+      <c r="D38" s="224"/>
+      <c r="E38" s="224"/>
+      <c r="F38" s="224"/>
+      <c r="G38" s="224"/>
+      <c r="H38" s="225"/>
+      <c r="I38" s="232"/>
+      <c r="J38" s="233"/>
+      <c r="K38" s="233"/>
+      <c r="L38" s="233"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C39" s="223"/>
-      <c r="D39" s="224"/>
-      <c r="E39" s="224"/>
-      <c r="F39" s="224"/>
-      <c r="G39" s="224"/>
-      <c r="H39" s="225"/>
-      <c r="I39" s="218"/>
-      <c r="J39" s="219"/>
-      <c r="K39" s="219"/>
-      <c r="L39" s="219"/>
+      <c r="C39" s="226"/>
+      <c r="D39" s="227"/>
+      <c r="E39" s="227"/>
+      <c r="F39" s="227"/>
+      <c r="G39" s="227"/>
+      <c r="H39" s="228"/>
+      <c r="I39" s="232"/>
+      <c r="J39" s="233"/>
+      <c r="K39" s="233"/>
+      <c r="L39" s="233"/>
     </row>
     <row r="40" spans="1:12" ht="34.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C40" s="226"/>
-      <c r="D40" s="227"/>
-      <c r="E40" s="227"/>
-      <c r="F40" s="227"/>
-      <c r="G40" s="227"/>
-      <c r="H40" s="228"/>
-      <c r="I40" s="218"/>
-      <c r="J40" s="219"/>
-      <c r="K40" s="219"/>
-      <c r="L40" s="219"/>
+      <c r="C40" s="229"/>
+      <c r="D40" s="230"/>
+      <c r="E40" s="230"/>
+      <c r="F40" s="230"/>
+      <c r="G40" s="230"/>
+      <c r="H40" s="231"/>
+      <c r="I40" s="232"/>
+      <c r="J40" s="233"/>
+      <c r="K40" s="233"/>
+      <c r="L40" s="233"/>
     </row>
     <row r="42" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="125"/>
@@ -7017,7 +7056,7 @@
         <v>157</v>
       </c>
       <c r="D44" s="179" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="H44" s="150"/>
     </row>
@@ -7027,37 +7066,37 @@
       <c r="H45" s="150"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C46" s="220" t="s">
-        <v>200</v>
-      </c>
-      <c r="D46" s="221"/>
-      <c r="E46" s="221"/>
-      <c r="F46" s="221"/>
-      <c r="G46" s="221"/>
-      <c r="H46" s="222"/>
+      <c r="C46" s="223" t="s">
+        <v>191</v>
+      </c>
+      <c r="D46" s="224"/>
+      <c r="E46" s="224"/>
+      <c r="F46" s="224"/>
+      <c r="G46" s="224"/>
+      <c r="H46" s="225"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C47" s="223"/>
-      <c r="D47" s="224"/>
-      <c r="E47" s="224"/>
-      <c r="F47" s="224"/>
-      <c r="G47" s="224"/>
-      <c r="H47" s="225"/>
+      <c r="C47" s="226"/>
+      <c r="D47" s="227"/>
+      <c r="E47" s="227"/>
+      <c r="F47" s="227"/>
+      <c r="G47" s="227"/>
+      <c r="H47" s="228"/>
     </row>
     <row r="48" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C48" s="226"/>
-      <c r="D48" s="227"/>
-      <c r="E48" s="227"/>
-      <c r="F48" s="227"/>
-      <c r="G48" s="227"/>
-      <c r="H48" s="228"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="231"/>
     </row>
     <row r="50" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="51" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C51" s="230" t="s">
+      <c r="C51" s="181" t="s">
         <v>156</v>
       </c>
-      <c r="D51" s="231">
+      <c r="D51" s="182">
         <f>D43+1</f>
         <v>7</v>
       </c>
@@ -7067,44 +7106,44 @@
       <c r="H51" s="149"/>
     </row>
     <row r="52" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C52" s="232" t="s">
+      <c r="C52" s="183" t="s">
         <v>157</v>
       </c>
-      <c r="D52" s="233" t="s">
-        <v>199</v>
+      <c r="D52" s="184" t="s">
+        <v>190</v>
       </c>
       <c r="H52" s="150"/>
     </row>
     <row r="53" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C53" s="232"/>
-      <c r="D53" s="233"/>
+      <c r="C53" s="183"/>
+      <c r="D53" s="184"/>
       <c r="H53" s="150"/>
     </row>
     <row r="54" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C54" s="220" t="s">
-        <v>202</v>
-      </c>
-      <c r="D54" s="221"/>
-      <c r="E54" s="221"/>
-      <c r="F54" s="221"/>
-      <c r="G54" s="221"/>
-      <c r="H54" s="222"/>
+      <c r="C54" s="223" t="s">
+        <v>193</v>
+      </c>
+      <c r="D54" s="224"/>
+      <c r="E54" s="224"/>
+      <c r="F54" s="224"/>
+      <c r="G54" s="224"/>
+      <c r="H54" s="225"/>
     </row>
     <row r="55" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C55" s="223"/>
-      <c r="D55" s="224"/>
-      <c r="E55" s="224"/>
-      <c r="F55" s="224"/>
-      <c r="G55" s="224"/>
-      <c r="H55" s="225"/>
+      <c r="C55" s="226"/>
+      <c r="D55" s="227"/>
+      <c r="E55" s="227"/>
+      <c r="F55" s="227"/>
+      <c r="G55" s="227"/>
+      <c r="H55" s="228"/>
     </row>
     <row r="56" spans="3:8" ht="67.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C56" s="226"/>
-      <c r="D56" s="227"/>
-      <c r="E56" s="227"/>
-      <c r="F56" s="227"/>
-      <c r="G56" s="227"/>
-      <c r="H56" s="228"/>
+      <c r="C56" s="229"/>
+      <c r="D56" s="230"/>
+      <c r="E56" s="230"/>
+      <c r="F56" s="230"/>
+      <c r="G56" s="230"/>
+      <c r="H56" s="231"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/2026/GALERIA MITRE/Junio/Junio MITRE.xlsx
+++ b/2026/GALERIA MITRE/Junio/Junio MITRE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GALERIA MITRE\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE882404-4767-49EE-B70E-C97F3A47E984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D846D8-46D4-4D02-94C9-4BC8B06DC054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="197">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -524,54 +524,9 @@
     <t>Juana Acuña</t>
   </si>
   <si>
-    <t>Dinero Fondo FIMA - Al 03/06/2026</t>
-  </si>
-  <si>
-    <t>UF 37</t>
-  </si>
-  <si>
-    <t>El mes pasado habia pagado en tiempo y forma sus $63286,37 - Quitar punitorios y colocar su pago</t>
-  </si>
-  <si>
-    <t>UF 45</t>
-  </si>
-  <si>
-    <t>En el mes de Abril  pago $46.313,46 y se la pusimos a la UF 46 cuando era a la 45 (el error fue suyo por haber pagado con centavos incorrectos) - En el mes de junio transfirio $87.463 el 04/06</t>
-  </si>
-  <si>
-    <t>UF 52</t>
-  </si>
-  <si>
-    <t>Deposito $164.000 el 11/05 y no se lo imputamos - Este mes deposito $116.000 el 05/06</t>
-  </si>
-  <si>
-    <t>UF 41</t>
-  </si>
-  <si>
-    <t>Deposito $95.000 el 05/06</t>
-  </si>
-  <si>
-    <t>Local 9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deposito $273,000 el 15/04 debemos agregarselo en su UF (local 9) , ademas el tiene: L8, L9, L17, L19, 1101, 5504 - Pero solo hay problema en los "numeros" del local 9 </t>
-  </si>
-  <si>
-    <t>ADEMAS DE ARREGLAR LA SITUACION DEL LOCAL 9, LAURA BORAS DEPOSITO EL 15/06 UN MONTON DE DEPOSITOS CON LA FOTO DE PARA DONDE VA CADA UNO. LAS ENVIO POR MAIL</t>
-  </si>
-  <si>
-    <t>Local 13 y 14</t>
-  </si>
-  <si>
-    <t>Transfirio $226.963,27 el 12/06</t>
-  </si>
-  <si>
     <t>Frisco - Capetello Silvia Viviana</t>
   </si>
   <si>
-    <t>Local 15: Según los comprobantes adjuntos, se realizaron cuatro transferencias desde la cuenta de titularidad de Capetillo Silvina Vivian por un monto de $100.000,00 cada una. Las operaciones fueron efectuadas el 02/06/2026, el 03/06/2026, el 09/06/2026 y el 17/06/2026. El monto total transferido asciende a $400.000,00.</t>
-  </si>
-  <si>
     <t>VTO 17/07</t>
   </si>
   <si>
@@ -639,6 +594,32 @@
   </si>
   <si>
     <t>PREVISION ORDINARIA ARCA Y SAC</t>
+  </si>
+  <si>
+    <t>Dinero Fondo FIMA - Al 05/07/2026</t>
+  </si>
+  <si>
+    <t>Local 5</t>
+  </si>
+  <si>
+    <t>El deposito no identificado del 22/05 por $600.000 es de el - Debe aboanr $474.829 contando el deposito y quita de punitorios</t>
+  </si>
+  <si>
+    <t>Frisco</t>
+  </si>
+  <si>
+    <t>Local 15</t>
+  </si>
+  <si>
+    <t>Dice que nos falto ponerle un pago del 28/05 de $150.000 - Nosotros le contrestamos: Buenos días, estimada Silvina:
+En el mes de mayo tenemos registrada la contabilización de un pago de $150.000 correspondiente al Local 15.
+¿Podría confirmarnos si realizó dos pagos por ese mismo importe?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deposito el 12/06 $262.000 - reveer </t>
+  </si>
+  <si>
+    <t>Deposito  $ 112.000,00 abonado el día 08 de julio de 2026</t>
   </si>
 </sst>
 </file>
@@ -821,7 +802,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -896,31 +877,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF002060"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="9" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1284,12 +1247,11 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="224">
+  <cellXfs count="218">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1456,28 +1418,9 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="7" fillId="4" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1485,132 +1428,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1620,14 +1437,8 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1641,15 +1452,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="7" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1667,6 +1469,157 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="10" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2036,1036 +1989,1036 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="193" t="s">
+      <c r="A1" s="131" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="194"/>
-      <c r="C1" s="195"/>
-      <c r="D1" s="195"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="134" t="s">
         <v>125</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
-      <c r="D2" s="196"/>
+      <c r="B2" s="134"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="134"/>
     </row>
     <row r="3" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="196" t="s">
+      <c r="A3" s="134" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="196"/>
-      <c r="C3" s="196"/>
-      <c r="D3" s="196"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="134"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="197" t="s">
+      <c r="A4" s="173" t="s">
         <v>151</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="198"/>
-      <c r="D4" s="198"/>
+      <c r="B4" s="173"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="135"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="197"/>
-      <c r="B5" s="197"/>
-      <c r="C5" s="198"/>
-      <c r="D5" s="198"/>
+      <c r="A5" s="173"/>
+      <c r="B5" s="173"/>
+      <c r="C5" s="135"/>
+      <c r="D5" s="135"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="197"/>
-      <c r="B6" s="197"/>
-      <c r="C6" s="198"/>
-      <c r="D6" s="198"/>
+      <c r="A6" s="173"/>
+      <c r="B6" s="173"/>
+      <c r="C6" s="135"/>
+      <c r="D6" s="135"/>
     </row>
     <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="197"/>
-      <c r="B7" s="197"/>
-      <c r="C7" s="198"/>
-      <c r="D7" s="198"/>
+      <c r="A7" s="173"/>
+      <c r="B7" s="173"/>
+      <c r="C7" s="135"/>
+      <c r="D7" s="135"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="64"/>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
+      <c r="A8" s="63"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="64"/>
-      <c r="B9" s="199" t="s">
-        <v>181</v>
-      </c>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
+      <c r="A9" s="63"/>
+      <c r="B9" s="172" t="s">
+        <v>166</v>
+      </c>
+      <c r="C9" s="63"/>
+      <c r="D9" s="63"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="64"/>
-      <c r="B10" s="199"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
+      <c r="A10" s="63"/>
+      <c r="B10" s="172"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="63"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="64"/>
-      <c r="B11" s="199"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
+      <c r="A11" s="63"/>
+      <c r="B11" s="172"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="63"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="64"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
+      <c r="A12" s="63"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="63"/>
     </row>
     <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="64"/>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
+      <c r="A13" s="63"/>
+      <c r="B13" s="63"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="63"/>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="197" t="s">
+      <c r="A14" s="173" t="s">
         <v>148</v>
       </c>
-      <c r="B14" s="197"/>
-      <c r="C14" s="197"/>
-      <c r="D14" s="197"/>
+      <c r="B14" s="173"/>
+      <c r="C14" s="173"/>
+      <c r="D14" s="173"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="197"/>
-      <c r="B15" s="197"/>
-      <c r="C15" s="197"/>
-      <c r="D15" s="197"/>
+      <c r="A15" s="173"/>
+      <c r="B15" s="173"/>
+      <c r="C15" s="173"/>
+      <c r="D15" s="173"/>
     </row>
     <row r="16" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="197"/>
-      <c r="B16" s="197"/>
-      <c r="C16" s="197"/>
-      <c r="D16" s="197"/>
+      <c r="A16" s="173"/>
+      <c r="B16" s="173"/>
+      <c r="C16" s="173"/>
+      <c r="D16" s="173"/>
     </row>
     <row r="17" spans="1:7" ht="156.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="197"/>
-      <c r="B17" s="197"/>
-      <c r="C17" s="197"/>
-      <c r="D17" s="197"/>
+      <c r="A17" s="173"/>
+      <c r="B17" s="173"/>
+      <c r="C17" s="173"/>
+      <c r="D17" s="173"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="64"/>
-      <c r="B18" s="64"/>
-      <c r="C18" s="64"/>
-      <c r="D18" s="64"/>
+      <c r="A18" s="63"/>
+      <c r="B18" s="63"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="63"/>
     </row>
     <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="200"/>
-      <c r="B19" s="64"/>
-      <c r="C19" s="64"/>
-      <c r="D19" s="64"/>
+      <c r="A19" s="136"/>
+      <c r="B19" s="63"/>
+      <c r="C19" s="63"/>
+      <c r="D19" s="63"/>
     </row>
     <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="64"/>
-      <c r="B20" s="64"/>
-      <c r="C20" s="64"/>
-      <c r="D20" s="64"/>
+      <c r="A20" s="63"/>
+      <c r="B20" s="63"/>
+      <c r="C20" s="63"/>
+      <c r="D20" s="63"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="201" t="s">
+      <c r="A21" s="137" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="202"/>
-      <c r="C21" s="68"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="149" t="s">
-        <v>184</v>
-      </c>
-      <c r="F21" s="149"/>
+      <c r="B21" s="138"/>
+      <c r="C21" s="67"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="129" t="s">
+        <v>169</v>
+      </c>
+      <c r="F21" s="129"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="149"/>
-      <c r="F22" s="149"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="129"/>
+      <c r="F22" s="129"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="150" t="s">
-        <v>182</v>
-      </c>
-      <c r="B23" s="151"/>
-      <c r="C23" s="83">
+      <c r="A23" s="170" t="s">
+        <v>167</v>
+      </c>
+      <c r="B23" s="171"/>
+      <c r="C23" s="82">
         <v>1231605.7</v>
       </c>
-      <c r="D23" s="49"/>
-      <c r="E23" s="149"/>
-      <c r="F23" s="149"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="129"/>
+      <c r="F23" s="129"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="49" t="s">
+      <c r="A24" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="B24" s="49"/>
-      <c r="C24" s="83">
+      <c r="B24" s="48"/>
+      <c r="C24" s="82">
         <v>-193977.9</v>
       </c>
-      <c r="D24" s="49"/>
-      <c r="E24" s="149"/>
-      <c r="F24" s="149"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="129"/>
+      <c r="F24" s="129"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="49"/>
-      <c r="C25" s="83">
+      <c r="B25" s="48"/>
+      <c r="C25" s="82">
         <v>0.2</v>
       </c>
-      <c r="D25" s="49"/>
-      <c r="E25" s="149"/>
-      <c r="F25" s="149"/>
-      <c r="G25" s="95"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="129"/>
+      <c r="F25" s="129"/>
+      <c r="G25" s="94"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="203" t="s">
+      <c r="A26" s="139" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="203"/>
-      <c r="C26" s="73">
+      <c r="B26" s="139"/>
+      <c r="C26" s="72">
         <f>SUM(C23:C25)</f>
         <v>1037627.9999999999</v>
       </c>
-      <c r="D26" s="203"/>
-      <c r="E26" s="149"/>
-      <c r="F26" s="149"/>
+      <c r="D26" s="139"/>
+      <c r="E26" s="129"/>
+      <c r="F26" s="129"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="150" t="s">
-        <v>183</v>
-      </c>
-      <c r="B27" s="151"/>
-      <c r="C27" s="83">
+      <c r="A27" s="170" t="s">
+        <v>168</v>
+      </c>
+      <c r="B27" s="171"/>
+      <c r="C27" s="82">
         <v>815681.8</v>
       </c>
-      <c r="D27" s="49"/>
-      <c r="E27" s="149"/>
-      <c r="F27" s="149"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="129"/>
+      <c r="F27" s="129"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="49" t="s">
+      <c r="A28" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="49"/>
-      <c r="C28" s="83">
+      <c r="B28" s="48"/>
+      <c r="C28" s="82">
         <v>-201881.24</v>
       </c>
-      <c r="D28" s="74"/>
-      <c r="E28" s="149"/>
-      <c r="F28" s="149"/>
+      <c r="D28" s="73"/>
+      <c r="E28" s="129"/>
+      <c r="F28" s="129"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="49" t="s">
+      <c r="A29" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="49"/>
-      <c r="C29" s="83">
+      <c r="B29" s="48"/>
+      <c r="C29" s="82">
         <v>0.44</v>
       </c>
-      <c r="D29" s="74"/>
+      <c r="D29" s="73"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="203" t="s">
+      <c r="A30" s="139" t="s">
         <v>53</v>
       </c>
-      <c r="B30" s="204"/>
-      <c r="C30" s="28">
+      <c r="B30" s="140"/>
+      <c r="C30" s="27">
         <f>SUM(C27:C29)</f>
         <v>613801</v>
       </c>
-      <c r="D30" s="50"/>
+      <c r="D30" s="49"/>
     </row>
     <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="49"/>
-      <c r="B31" s="49"/>
-      <c r="C31" s="98">
-        <v>0</v>
-      </c>
-      <c r="D31" s="74"/>
+      <c r="A31" s="48"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="97">
+        <v>0</v>
+      </c>
+      <c r="D31" s="73"/>
     </row>
     <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="49"/>
-      <c r="B32" s="49"/>
-      <c r="C32" s="98"/>
-      <c r="D32" s="74"/>
+      <c r="A32" s="48"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="97"/>
+      <c r="D32" s="73"/>
     </row>
     <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="203" t="s">
+      <c r="A33" s="139" t="s">
         <v>53</v>
       </c>
-      <c r="B33" s="204"/>
-      <c r="C33" s="28">
+      <c r="B33" s="140"/>
+      <c r="C33" s="27">
         <f>SUM(C31:C32)</f>
         <v>0</v>
       </c>
-      <c r="D33" s="50"/>
+      <c r="D33" s="49"/>
     </row>
     <row r="34" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="51">
+      <c r="A34" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="12"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="50">
         <f>+C26+C33+C30</f>
         <v>1651429</v>
       </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="12"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="52"/>
-      <c r="F35" s="5"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="51"/>
+      <c r="F35" s="4"/>
     </row>
     <row r="36" spans="1:7" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="150" t="s">
-        <v>198</v>
-      </c>
-      <c r="B36" s="151"/>
-      <c r="C36" s="83">
+      <c r="A36" s="170" t="s">
+        <v>183</v>
+      </c>
+      <c r="B36" s="171"/>
+      <c r="C36" s="82">
         <v>710000</v>
       </c>
-      <c r="D36" s="82"/>
-      <c r="G36" s="5"/>
+      <c r="D36" s="81"/>
+      <c r="G36" s="4"/>
     </row>
     <row r="37" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="205" t="s">
+      <c r="A37" s="141" t="s">
         <v>161</v>
       </c>
-      <c r="B37" s="206"/>
-      <c r="C37" s="83">
+      <c r="B37" s="142"/>
+      <c r="C37" s="82">
         <v>90000</v>
       </c>
-      <c r="D37" s="82" t="s">
-        <v>185</v>
-      </c>
-      <c r="G37" s="5"/>
+      <c r="D37" s="81" t="s">
+        <v>170</v>
+      </c>
+      <c r="G37" s="4"/>
     </row>
     <row r="38" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="205" t="s">
+      <c r="A38" s="141" t="s">
         <v>157</v>
       </c>
-      <c r="B38" s="206"/>
-      <c r="C38" s="83">
+      <c r="B38" s="142"/>
+      <c r="C38" s="82">
         <v>200000</v>
       </c>
-      <c r="D38" s="82" t="s">
-        <v>185</v>
-      </c>
-      <c r="G38" s="5"/>
+      <c r="D38" s="81" t="s">
+        <v>170</v>
+      </c>
+      <c r="G38" s="4"/>
     </row>
     <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="13" t="s">
+      <c r="A39" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="125"/>
-      <c r="D39" s="51">
+      <c r="B39" s="12"/>
+      <c r="C39" s="124"/>
+      <c r="D39" s="50">
         <f>SUM(C36:C38)</f>
         <v>1000000</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="32"/>
-    </row>
-    <row r="41" spans="1:7" s="20" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="150" t="s">
+      <c r="B40" s="12"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="31"/>
+    </row>
+    <row r="41" spans="1:7" s="19" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="170" t="s">
         <v>130</v>
       </c>
-      <c r="B41" s="151"/>
-      <c r="C41" s="97">
+      <c r="B41" s="171"/>
+      <c r="C41" s="96">
         <v>111379</v>
       </c>
-      <c r="D41" s="96" t="s">
-        <v>197</v>
+      <c r="D41" s="95" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="13" t="s">
+      <c r="A42" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="53">
+      <c r="B42" s="12"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="52">
         <f>SUM(C41:C41)</f>
         <v>111379</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="12" t="s">
+      <c r="A43" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B43" s="85"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="54"/>
+      <c r="B43" s="84"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="53"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="49" t="s">
+      <c r="A44" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="B44" s="49"/>
-      <c r="C44" s="101">
-        <v>0</v>
-      </c>
-      <c r="D44" s="78"/>
-      <c r="F44" s="75"/>
+      <c r="B44" s="48"/>
+      <c r="C44" s="100">
+        <v>0</v>
+      </c>
+      <c r="D44" s="77"/>
+      <c r="F44" s="74"/>
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="150" t="s">
-        <v>196</v>
-      </c>
-      <c r="B45" s="151"/>
-      <c r="C45" s="101">
+      <c r="A45" s="170" t="s">
+        <v>181</v>
+      </c>
+      <c r="B45" s="171"/>
+      <c r="C45" s="100">
         <v>11596.99</v>
       </c>
-      <c r="D45" s="81" t="s">
-        <v>195</v>
-      </c>
-      <c r="F45" s="75"/>
+      <c r="D45" s="80" t="s">
+        <v>180</v>
+      </c>
+      <c r="F45" s="74"/>
     </row>
     <row r="46" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="150" t="s">
+      <c r="A46" s="170" t="s">
         <v>129</v>
       </c>
-      <c r="B46" s="151"/>
-      <c r="C46" s="101">
+      <c r="B46" s="171"/>
+      <c r="C46" s="100">
         <v>11930.96</v>
       </c>
-      <c r="D46" s="78" t="str">
+      <c r="D46" s="77" t="str">
         <f>D45</f>
         <v>Debito 12/06</v>
       </c>
-      <c r="F46" s="75"/>
+      <c r="F46" s="74"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="49" t="s">
+      <c r="A47" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="B47" s="49" t="s">
+      <c r="B47" s="48" t="s">
         <v>162</v>
       </c>
-      <c r="C47" s="86">
+      <c r="C47" s="85">
         <v>92127.95</v>
       </c>
-      <c r="D47" s="81" t="s">
-        <v>195</v>
+      <c r="D47" s="80" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="49" t="s">
+      <c r="A48" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="B48" s="49" t="s">
+      <c r="B48" s="48" t="s">
         <v>162</v>
       </c>
-      <c r="C48" s="86">
+      <c r="C48" s="85">
         <v>10236.44</v>
       </c>
-      <c r="D48" s="81" t="str">
+      <c r="D48" s="80" t="str">
         <f>D47</f>
         <v>Debito 12/06</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="49" t="s">
+      <c r="A49" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="B49" s="49" t="s">
+      <c r="B49" s="48" t="s">
         <v>162</v>
       </c>
-      <c r="C49" s="86">
+      <c r="C49" s="85">
         <v>200516.68</v>
       </c>
-      <c r="D49" s="79" t="str">
+      <c r="D49" s="78" t="str">
         <f>D47</f>
         <v>Debito 12/06</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="13" t="s">
+      <c r="A50" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B50" s="85"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="53">
+      <c r="B50" s="84"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="52">
         <f>SUM(C44:C49)</f>
         <v>326409.02</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="12" t="s">
+      <c r="A51" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B51" s="85"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="54"/>
+      <c r="B51" s="84"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="53"/>
     </row>
     <row r="52" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="49" t="s">
+      <c r="A52" s="48" t="s">
         <v>127</v>
       </c>
-      <c r="B52" s="49"/>
-      <c r="C52" s="86">
+      <c r="B52" s="48"/>
+      <c r="C52" s="85">
         <v>627717.51</v>
       </c>
-      <c r="D52" s="78" t="s">
-        <v>192</v>
+      <c r="D52" s="77" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="49" t="s">
+      <c r="A53" s="48" t="s">
         <v>126</v>
       </c>
-      <c r="B53" s="49"/>
-      <c r="C53" s="86">
+      <c r="B53" s="48"/>
+      <c r="C53" s="85">
         <v>164200</v>
       </c>
-      <c r="D53" s="78" t="s">
-        <v>188</v>
+      <c r="D53" s="77" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="49" t="s">
+      <c r="A54" s="48" t="s">
         <v>160</v>
       </c>
-      <c r="B54" s="49"/>
-      <c r="C54" s="86">
+      <c r="B54" s="48"/>
+      <c r="C54" s="85">
         <v>1405375.2</v>
       </c>
-      <c r="D54" s="78" t="s">
-        <v>189</v>
+      <c r="D54" s="77" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="49" t="s">
+      <c r="A55" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="B55" s="49"/>
-      <c r="C55" s="86">
+      <c r="B55" s="48"/>
+      <c r="C55" s="85">
         <v>37073.65</v>
       </c>
-      <c r="D55" s="78" t="s">
-        <v>192</v>
+      <c r="D55" s="77" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="49" t="s">
+      <c r="A56" s="48" t="s">
         <v>159</v>
       </c>
-      <c r="B56" s="102"/>
-      <c r="C56" s="86">
+      <c r="B56" s="101"/>
+      <c r="C56" s="85">
         <v>80576</v>
       </c>
-      <c r="D56" s="78" t="s">
-        <v>187</v>
+      <c r="D56" s="77" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="13" t="s">
+      <c r="A57" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B57" s="13"/>
-      <c r="C57" s="17"/>
-      <c r="D57" s="53">
+      <c r="B57" s="12"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="52">
         <f>SUM(C52:C56)</f>
         <v>2314942.36</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="12" t="s">
+      <c r="A58" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B58" s="13"/>
-      <c r="C58" s="17"/>
-      <c r="D58" s="56"/>
+      <c r="B58" s="12"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="55"/>
     </row>
     <row r="59" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="152" t="s">
+      <c r="A59" s="177" t="s">
         <v>156</v>
       </c>
-      <c r="B59" s="153"/>
-      <c r="C59" s="86">
+      <c r="B59" s="178"/>
+      <c r="C59" s="85">
         <v>202000</v>
       </c>
-      <c r="D59" s="78" t="s">
-        <v>189</v>
+      <c r="D59" s="77" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="152" t="s">
-        <v>191</v>
-      </c>
-      <c r="B60" s="153"/>
-      <c r="C60" s="86">
+      <c r="A60" s="177" t="s">
+        <v>176</v>
+      </c>
+      <c r="B60" s="178"/>
+      <c r="C60" s="85">
         <v>229900</v>
       </c>
-      <c r="D60" s="78" t="s">
-        <v>189</v>
+      <c r="D60" s="77" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="150" t="s">
-        <v>193</v>
-      </c>
-      <c r="B61" s="151"/>
-      <c r="C61" s="86">
+      <c r="A61" s="170" t="s">
+        <v>178</v>
+      </c>
+      <c r="B61" s="171"/>
+      <c r="C61" s="85">
         <v>35000</v>
       </c>
-      <c r="D61" s="78" t="s">
-        <v>192</v>
-      </c>
-      <c r="E61" s="86"/>
-      <c r="F61" s="25"/>
+      <c r="D61" s="77" t="s">
+        <v>177</v>
+      </c>
+      <c r="E61" s="85"/>
+      <c r="F61" s="24"/>
     </row>
     <row r="62" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="152" t="s">
-        <v>194</v>
-      </c>
-      <c r="B62" s="153"/>
-      <c r="C62" s="86">
+      <c r="A62" s="177" t="s">
+        <v>179</v>
+      </c>
+      <c r="B62" s="178"/>
+      <c r="C62" s="85">
         <v>9395</v>
       </c>
-      <c r="D62" s="78" t="s">
-        <v>192</v>
-      </c>
-      <c r="E62" s="86">
+      <c r="D62" s="77" t="s">
+        <v>177</v>
+      </c>
+      <c r="E62" s="85">
         <f>C62+C61</f>
         <v>44395</v>
       </c>
-      <c r="F62" s="25"/>
+      <c r="F62" s="24"/>
     </row>
     <row r="63" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="152" t="s">
-        <v>186</v>
-      </c>
-      <c r="B63" s="153"/>
-      <c r="C63" s="86">
+      <c r="A63" s="177" t="s">
+        <v>171</v>
+      </c>
+      <c r="B63" s="178"/>
+      <c r="C63" s="85">
         <v>18300</v>
       </c>
-      <c r="D63" s="80" t="s">
+      <c r="D63" s="79" t="s">
         <v>158</v>
       </c>
-      <c r="E63" s="126"/>
-      <c r="F63" s="25"/>
+      <c r="E63" s="125"/>
+      <c r="F63" s="24"/>
     </row>
     <row r="64" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="147" t="s">
-        <v>190</v>
-      </c>
-      <c r="B64" s="148"/>
-      <c r="C64" s="86">
+      <c r="A64" s="127" t="s">
+        <v>175</v>
+      </c>
+      <c r="B64" s="128"/>
+      <c r="C64" s="85">
         <v>225200</v>
       </c>
-      <c r="D64" s="78" t="s">
-        <v>189</v>
-      </c>
-      <c r="E64" s="126"/>
-      <c r="F64" s="25"/>
+      <c r="D64" s="77" t="s">
+        <v>174</v>
+      </c>
+      <c r="E64" s="125"/>
+      <c r="F64" s="24"/>
     </row>
     <row r="65" spans="1:6" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="147" t="s">
-        <v>190</v>
-      </c>
-      <c r="B65" s="148"/>
-      <c r="C65" s="86">
+      <c r="A65" s="127" t="s">
+        <v>175</v>
+      </c>
+      <c r="B65" s="128"/>
+      <c r="C65" s="85">
         <v>88500</v>
       </c>
-      <c r="D65" s="96" t="s">
-        <v>197</v>
-      </c>
-      <c r="E65" s="25"/>
-      <c r="F65" s="25"/>
+      <c r="D65" s="95" t="s">
+        <v>182</v>
+      </c>
+      <c r="E65" s="24"/>
+      <c r="F65" s="24"/>
     </row>
     <row r="66" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="13" t="s">
+      <c r="A66" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B66" s="12"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="59">
+      <c r="B66" s="11"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="58">
         <f>SUM(C59:C65)</f>
         <v>808295</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="12" t="s">
+      <c r="A67" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B67" s="87"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="56"/>
+      <c r="B67" s="86"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="55"/>
     </row>
     <row r="68" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="150" t="s">
+      <c r="A68" s="170" t="s">
         <v>73</v>
       </c>
-      <c r="B68" s="151"/>
-      <c r="C68" s="86">
+      <c r="B68" s="171"/>
+      <c r="C68" s="85">
         <v>60000</v>
       </c>
-      <c r="D68" s="60"/>
+      <c r="D68" s="59"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="49" t="s">
+      <c r="A69" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="B69" s="49"/>
-      <c r="C69" s="86">
+      <c r="B69" s="48"/>
+      <c r="C69" s="85">
         <f>18446.4+600+23515.55+3766.99+10879.99+46995.77+5603.24+1720.48+18645.44+9072.47+11656.2</f>
         <v>150902.53</v>
       </c>
-      <c r="D69" s="58"/>
+      <c r="D69" s="57"/>
     </row>
     <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="207" t="s">
+      <c r="A70" s="143" t="s">
         <v>34</v>
       </c>
-      <c r="B70" s="207"/>
-      <c r="C70" s="61"/>
-      <c r="D70" s="53">
+      <c r="B70" s="143"/>
+      <c r="C70" s="60"/>
+      <c r="D70" s="52">
         <f>SUM(C68:C69)</f>
         <v>210902.53</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="49"/>
-      <c r="B71" s="49"/>
-      <c r="C71" s="49"/>
-      <c r="D71" s="62"/>
+      <c r="A71" s="48"/>
+      <c r="B71" s="48"/>
+      <c r="C71" s="48"/>
+      <c r="D71" s="61"/>
     </row>
     <row r="72" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="208" t="s">
-        <v>203</v>
-      </c>
-      <c r="B72" s="209"/>
-      <c r="C72" s="210"/>
-      <c r="D72" s="63">
+      <c r="A72" s="174" t="s">
+        <v>188</v>
+      </c>
+      <c r="B72" s="175"/>
+      <c r="C72" s="176"/>
+      <c r="D72" s="62">
         <f>(6780039.56+6780039.56*20%)-6423356.91</f>
         <v>1712690.561999999</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="211"/>
-      <c r="B73" s="64"/>
-      <c r="C73" s="64"/>
-      <c r="D73" s="65"/>
-      <c r="E73" s="25"/>
+      <c r="A73" s="144"/>
+      <c r="B73" s="63"/>
+      <c r="C73" s="63"/>
+      <c r="D73" s="64"/>
+      <c r="E73" s="24"/>
     </row>
     <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="212" t="s">
+      <c r="A74" s="145" t="s">
         <v>30</v>
       </c>
-      <c r="B74" s="213"/>
-      <c r="C74" s="66"/>
-      <c r="D74" s="67">
+      <c r="B74" s="146"/>
+      <c r="C74" s="65"/>
+      <c r="D74" s="66">
         <f>(SUM(D23:D72))</f>
         <v>8136047.4719999991</v>
       </c>
-      <c r="E74" s="25"/>
-      <c r="F74" s="25"/>
+      <c r="E74" s="24"/>
+      <c r="F74" s="24"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="64"/>
-      <c r="B75" s="64"/>
-      <c r="C75" s="64"/>
-      <c r="D75" s="64"/>
-      <c r="F75" s="76"/>
+      <c r="A75" s="63"/>
+      <c r="B75" s="63"/>
+      <c r="C75" s="63"/>
+      <c r="D75" s="63"/>
+      <c r="F75" s="75"/>
     </row>
     <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="64"/>
-      <c r="B76" s="64"/>
-      <c r="C76" s="64"/>
-      <c r="D76" s="64"/>
+      <c r="A76" s="63"/>
+      <c r="B76" s="63"/>
+      <c r="C76" s="63"/>
+      <c r="D76" s="63"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="201" t="s">
+      <c r="A77" s="137" t="s">
         <v>39</v>
       </c>
-      <c r="B77" s="202"/>
-      <c r="C77" s="68"/>
-      <c r="D77" s="69"/>
+      <c r="B77" s="138"/>
+      <c r="C77" s="67"/>
+      <c r="D77" s="68"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="150"/>
-      <c r="B78" s="151"/>
-      <c r="C78" s="57"/>
-      <c r="D78" s="55"/>
+      <c r="A78" s="170"/>
+      <c r="B78" s="171"/>
+      <c r="C78" s="56"/>
+      <c r="D78" s="54"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="150"/>
-      <c r="B79" s="151"/>
-      <c r="C79" s="57"/>
-      <c r="D79" s="55"/>
+      <c r="A79" s="170"/>
+      <c r="B79" s="171"/>
+      <c r="C79" s="56"/>
+      <c r="D79" s="54"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="147"/>
-      <c r="B80" s="214"/>
-      <c r="C80" s="57"/>
-      <c r="D80" s="55"/>
+      <c r="A80" s="127"/>
+      <c r="B80" s="147"/>
+      <c r="C80" s="56"/>
+      <c r="D80" s="54"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="215"/>
-      <c r="B81" s="216"/>
-      <c r="C81" s="217"/>
-      <c r="D81" s="217">
+      <c r="A81" s="148"/>
+      <c r="B81" s="149"/>
+      <c r="C81" s="150"/>
+      <c r="D81" s="150">
         <f>SUM(C78:C80)</f>
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="64"/>
-      <c r="B82" s="64"/>
-      <c r="C82" s="64"/>
-      <c r="D82" s="64"/>
+      <c r="A82" s="63"/>
+      <c r="B82" s="63"/>
+      <c r="C82" s="63"/>
+      <c r="D82" s="63"/>
     </row>
     <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="64"/>
-      <c r="B83" s="64"/>
-      <c r="C83" s="64"/>
-      <c r="D83" s="64"/>
+      <c r="A83" s="63"/>
+      <c r="B83" s="63"/>
+      <c r="C83" s="63"/>
+      <c r="D83" s="63"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="218" t="s">
+      <c r="A84" s="151" t="s">
         <v>40</v>
       </c>
-      <c r="B84" s="218"/>
-      <c r="C84" s="219"/>
-      <c r="D84" s="220">
+      <c r="B84" s="151"/>
+      <c r="C84" s="152"/>
+      <c r="D84" s="153">
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="64"/>
-      <c r="B85" s="64"/>
-      <c r="C85" s="64"/>
-      <c r="D85" s="64"/>
+      <c r="A85" s="63"/>
+      <c r="B85" s="63"/>
+      <c r="C85" s="63"/>
+      <c r="D85" s="63"/>
     </row>
     <row r="86" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="212" t="s">
+      <c r="A86" s="145" t="s">
         <v>41</v>
       </c>
-      <c r="B86" s="213"/>
-      <c r="C86" s="66"/>
-      <c r="D86" s="67">
+      <c r="B86" s="146"/>
+      <c r="C86" s="65"/>
+      <c r="D86" s="66">
         <f>D81+D84</f>
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="64"/>
-      <c r="B87" s="64"/>
-      <c r="C87" s="64"/>
-      <c r="D87" s="64"/>
+      <c r="A87" s="63"/>
+      <c r="B87" s="63"/>
+      <c r="C87" s="63"/>
+      <c r="D87" s="63"/>
     </row>
     <row r="88" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="221" t="s">
+      <c r="A88" s="154" t="s">
         <v>31</v>
       </c>
-      <c r="B88" s="222">
+      <c r="B88" s="155">
         <f>D74</f>
         <v>8136047.4719999991</v>
       </c>
-      <c r="C88" s="223"/>
-      <c r="D88" s="64"/>
+      <c r="C88" s="156"/>
+      <c r="D88" s="63"/>
     </row>
     <row r="89" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="221" t="s">
+      <c r="A89" s="154" t="s">
         <v>32</v>
       </c>
-      <c r="B89" s="222">
+      <c r="B89" s="155">
         <f>D74-D72</f>
         <v>6423356.9100000001</v>
       </c>
-      <c r="C89" s="64"/>
-      <c r="D89" s="64"/>
+      <c r="C89" s="63"/>
+      <c r="D89" s="63"/>
     </row>
     <row r="90" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="221" t="s">
+      <c r="A90" s="154" t="s">
         <v>42</v>
       </c>
-      <c r="B90" s="222">
+      <c r="B90" s="155">
         <f>D86-D84</f>
         <v>0</v>
       </c>
-      <c r="C90" s="64"/>
-      <c r="D90" s="64"/>
+      <c r="C90" s="63"/>
+      <c r="D90" s="63"/>
     </row>
     <row r="91" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="221" t="s">
+      <c r="A91" s="154" t="s">
         <v>59</v>
       </c>
-      <c r="B91" s="222">
+      <c r="B91" s="155">
         <f>D86</f>
         <v>0</v>
       </c>
-      <c r="C91" s="64"/>
-      <c r="D91" s="64"/>
+      <c r="C91" s="63"/>
+      <c r="D91" s="63"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="6" t="s">
+      <c r="A95" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B95" s="22"/>
+      <c r="B95" s="21"/>
     </row>
     <row r="96" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="11" t="s">
+      <c r="A96" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B96" s="72">
+      <c r="B96" s="71">
         <v>-14222.15</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="7" t="s">
+      <c r="A97" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B97" s="23">
+      <c r="B97" s="22">
         <f>PRORRATEO!G66</f>
         <v>7982295.1100000003</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="103" t="s">
+      <c r="A98" s="102" t="s">
         <v>61</v>
       </c>
-      <c r="B98" s="58">
+      <c r="B98" s="57">
         <f>B114</f>
         <v>828486</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="103" t="s">
+      <c r="A99" s="102" t="s">
         <v>163</v>
       </c>
-      <c r="B99" s="77">
+      <c r="B99" s="76">
         <v>-600000</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="103" t="s">
-        <v>201</v>
-      </c>
-      <c r="B100" s="77">
+      <c r="A100" s="102" t="s">
+        <v>186</v>
+      </c>
+      <c r="B100" s="76">
         <v>-273000</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="8" t="s">
+      <c r="A101" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B101" s="77">
+      <c r="B101" s="76">
         <f>-2773-4291-16073</f>
         <v>-23137</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="21" t="s">
+      <c r="A102" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B102" s="77">
+      <c r="B102" s="76">
         <f>-B89</f>
         <v>-6423356.9100000001</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" s="8" t="s">
+      <c r="A103" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B103" s="58">
+      <c r="B103" s="57">
         <f>-(B90)</f>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="10" t="s">
+      <c r="A104" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B104" s="72">
+      <c r="B104" s="71">
         <f>SUM(B96:B103)</f>
         <v>1477065.0500000007</v>
       </c>
-      <c r="D104" s="99"/>
+      <c r="D104" s="98"/>
     </row>
     <row r="105" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="1"/>
-      <c r="B105" s="104"/>
-      <c r="D105" s="99"/>
+      <c r="B105" s="103"/>
+      <c r="D105" s="98"/>
     </row>
     <row r="106" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="116" t="s">
-        <v>165</v>
-      </c>
-      <c r="B106" s="117">
-        <v>1490504.61</v>
-      </c>
-      <c r="D106" s="99"/>
+      <c r="A106" s="115" t="s">
+        <v>189</v>
+      </c>
+      <c r="B106" s="116">
+        <v>1465817.44</v>
+      </c>
+      <c r="D106" s="98"/>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
-      <c r="B107" s="104"/>
-      <c r="D107" s="99"/>
+      <c r="B107" s="103"/>
+      <c r="D107" s="98"/>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D108" s="100"/>
+      <c r="D108" s="99"/>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="154" t="s">
+      <c r="A109" s="169" t="s">
         <v>50</v>
       </c>
-      <c r="B109" s="154"/>
+      <c r="B109" s="169"/>
     </row>
     <row r="110" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="154"/>
-      <c r="B110" s="154"/>
+      <c r="A110" s="169"/>
+      <c r="B110" s="169"/>
     </row>
     <row r="111" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="70" t="s">
-        <v>199</v>
-      </c>
-      <c r="B111" s="16">
+      <c r="A111" s="69" t="s">
+        <v>184</v>
+      </c>
+      <c r="B111" s="15">
         <v>92118</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="70" t="s">
-        <v>202</v>
-      </c>
-      <c r="B112" s="16">
+      <c r="A112" s="69" t="s">
+        <v>187</v>
+      </c>
+      <c r="B112" s="15">
         <v>260000</v>
       </c>
     </row>
     <row r="113" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="70" t="s">
-        <v>200</v>
-      </c>
-      <c r="B113" s="16">
+      <c r="A113" s="69" t="s">
+        <v>185</v>
+      </c>
+      <c r="B113" s="15">
         <v>476368</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A114" s="26" t="s">
+      <c r="A114" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B114" s="71">
+      <c r="B114" s="70">
         <f>SUM(B111:B113)</f>
         <v>828486</v>
       </c>
@@ -3075,12 +3028,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A109:B110"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A14:D17"/>
     <mergeCell ref="A72:C72"/>
@@ -3094,6 +3041,12 @@
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A109:B110"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3128,1438 +3081,1438 @@
   <sheetData>
     <row r="1" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
-      <c r="B1" s="155" t="s">
+      <c r="B1" s="185" t="s">
         <v>151</v>
       </c>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="157"/>
-      <c r="K1" s="112" t="s">
+      <c r="C1" s="186"/>
+      <c r="D1" s="186"/>
+      <c r="E1" s="186"/>
+      <c r="F1" s="186"/>
+      <c r="G1" s="186"/>
+      <c r="H1" s="186"/>
+      <c r="I1" s="186"/>
+      <c r="J1" s="187"/>
+      <c r="K1" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="109">
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="108">
         <f>Q1</f>
         <v>8136047.4719999991</v>
       </c>
-      <c r="O1" s="110"/>
-      <c r="P1" s="5"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="4"/>
       <c r="Q1">
         <v>8136047.4719999991</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="158"/>
-      <c r="C2" s="159"/>
-      <c r="D2" s="159"/>
-      <c r="E2" s="159"/>
-      <c r="F2" s="159"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="159"/>
-      <c r="I2" s="159"/>
-      <c r="J2" s="160"/>
-      <c r="K2" s="114" t="s">
+      <c r="B2" s="188"/>
+      <c r="C2" s="189"/>
+      <c r="D2" s="189"/>
+      <c r="E2" s="189"/>
+      <c r="F2" s="189"/>
+      <c r="G2" s="189"/>
+      <c r="H2" s="189"/>
+      <c r="I2" s="189"/>
+      <c r="J2" s="190"/>
+      <c r="K2" s="113" t="s">
         <v>63</v>
       </c>
-      <c r="L2" s="115"/>
-      <c r="M2" s="115"/>
-      <c r="N2" s="84">
-        <v>0</v>
-      </c>
-      <c r="O2" s="111"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="83">
+        <v>0</v>
+      </c>
+      <c r="O2" s="110"/>
     </row>
     <row r="3" spans="1:18" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
-      <c r="B3" s="174" t="s">
+      <c r="B3" s="202" t="s">
         <v>148</v>
       </c>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="175"/>
-      <c r="I3" s="175"/>
-      <c r="J3" s="175"/>
-      <c r="K3" s="175"/>
-      <c r="L3" s="175"/>
-      <c r="M3" s="175"/>
-      <c r="N3" s="175"/>
-      <c r="O3" s="176"/>
+      <c r="C3" s="203"/>
+      <c r="D3" s="203"/>
+      <c r="E3" s="203"/>
+      <c r="F3" s="203"/>
+      <c r="G3" s="203"/>
+      <c r="H3" s="203"/>
+      <c r="I3" s="203"/>
+      <c r="J3" s="203"/>
+      <c r="K3" s="203"/>
+      <c r="L3" s="203"/>
+      <c r="M3" s="203"/>
+      <c r="N3" s="203"/>
+      <c r="O3" s="204"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="177" t="s">
+      <c r="A4" s="179" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="179" t="s">
+      <c r="B4" s="181" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="164" t="s">
+      <c r="C4" s="183" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="164" t="s">
+      <c r="D4" s="183" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="164" t="s">
+      <c r="E4" s="183" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="164" t="s">
+      <c r="F4" s="183" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="164" t="s">
+      <c r="G4" s="183" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="164" t="s">
+      <c r="H4" s="183" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="169" t="s">
+      <c r="I4" s="197" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="166" t="s">
+      <c r="J4" s="195" t="s">
         <v>46</v>
       </c>
-      <c r="K4" s="166" t="s">
+      <c r="K4" s="195" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="166" t="s">
+      <c r="L4" s="195" t="s">
         <v>45</v>
       </c>
-      <c r="M4" s="172" t="s">
+      <c r="M4" s="200" t="s">
         <v>58</v>
       </c>
-      <c r="N4" s="30" t="s">
+      <c r="N4" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="O4" s="161" t="s">
+      <c r="O4" s="191" t="s">
         <v>56</v>
       </c>
-      <c r="R4" s="25"/>
+      <c r="R4" s="24"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="178"/>
-      <c r="B5" s="180"/>
-      <c r="C5" s="168"/>
-      <c r="D5" s="168"/>
-      <c r="E5" s="168"/>
-      <c r="F5" s="168"/>
-      <c r="G5" s="168"/>
-      <c r="H5" s="165"/>
-      <c r="I5" s="170"/>
-      <c r="J5" s="167"/>
-      <c r="K5" s="171"/>
-      <c r="L5" s="167"/>
-      <c r="M5" s="173"/>
-      <c r="N5" s="29" t="str">
+      <c r="A5" s="180"/>
+      <c r="B5" s="182"/>
+      <c r="C5" s="184"/>
+      <c r="D5" s="184"/>
+      <c r="E5" s="184"/>
+      <c r="F5" s="184"/>
+      <c r="G5" s="184"/>
+      <c r="H5" s="194"/>
+      <c r="I5" s="198"/>
+      <c r="J5" s="196"/>
+      <c r="K5" s="199"/>
+      <c r="L5" s="196"/>
+      <c r="M5" s="201"/>
+      <c r="N5" s="28" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 17/07</v>
       </c>
-      <c r="O5" s="162"/>
+      <c r="O5" s="192"/>
     </row>
     <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="192" t="s">
+      <c r="A6" s="130" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="88">
-        <v>0</v>
-      </c>
-      <c r="C6" s="88" t="s">
+      <c r="B6" s="87">
+        <v>0</v>
+      </c>
+      <c r="C6" s="87" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="88" t="s">
+      <c r="D6" s="87" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="32">
         <v>1.58</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="33">
         <v>1583891</v>
       </c>
-      <c r="G6" s="35">
-        <v>0</v>
-      </c>
-      <c r="H6" s="36"/>
-      <c r="I6" s="37">
+      <c r="G6" s="34">
+        <v>0</v>
+      </c>
+      <c r="H6" s="35"/>
+      <c r="I6" s="36">
         <f>F6-G6</f>
         <v>1583891</v>
       </c>
-      <c r="J6" s="37">
+      <c r="J6" s="36">
         <f>IF(I6&gt;0,I6*2.95%,0)</f>
         <v>46724.784500000002</v>
       </c>
-      <c r="K6" s="38">
+      <c r="K6" s="37">
         <f>N$2*E6%</f>
         <v>0</v>
       </c>
-      <c r="L6" s="38">
+      <c r="L6" s="37">
         <f>N$1*E6%</f>
         <v>128549.5500576</v>
       </c>
-      <c r="M6" s="39">
-        <v>0</v>
-      </c>
-      <c r="N6" s="40">
+      <c r="M6" s="38">
+        <v>0</v>
+      </c>
+      <c r="N6" s="39">
         <f t="shared" ref="N6:N64" si="0">ROUND(SUM(I6:M6),0) + P6</f>
         <v>1759165</v>
       </c>
-      <c r="O6" s="41">
+      <c r="O6" s="40">
         <f t="shared" ref="O6:O64" si="1">ROUND(N6*3%,0) + N6</f>
         <v>1811940</v>
       </c>
-      <c r="P6" s="25">
+      <c r="P6" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="192"/>
-      <c r="B7" s="88">
+      <c r="A7" s="130"/>
+      <c r="B7" s="87">
         <v>1</v>
       </c>
-      <c r="C7" s="88" t="s">
+      <c r="C7" s="87" t="s">
         <v>103</v>
       </c>
-      <c r="D7" s="88" t="s">
+      <c r="D7" s="87" t="s">
         <v>75</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="32">
         <v>2.91</v>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="33">
         <v>462493.01</v>
       </c>
-      <c r="G7" s="35">
-        <v>0</v>
-      </c>
-      <c r="H7" s="36"/>
-      <c r="I7" s="37">
+      <c r="G7" s="34">
+        <v>0</v>
+      </c>
+      <c r="H7" s="35"/>
+      <c r="I7" s="36">
         <f>F7-G7</f>
         <v>462493.01</v>
       </c>
-      <c r="J7" s="37">
+      <c r="J7" s="36">
         <f>IF(I7&gt;0,I7*2.95%,0)</f>
         <v>13643.543795000001</v>
       </c>
-      <c r="K7" s="38">
+      <c r="K7" s="37">
         <f>N$2*E7%</f>
         <v>0</v>
       </c>
-      <c r="L7" s="38">
+      <c r="L7" s="37">
         <f>N$1*E7%</f>
         <v>236758.9814352</v>
       </c>
-      <c r="M7" s="39">
-        <v>0</v>
-      </c>
-      <c r="N7" s="40">
+      <c r="M7" s="38">
+        <v>0</v>
+      </c>
+      <c r="N7" s="39">
         <f t="shared" si="0"/>
         <v>712896.01</v>
       </c>
-      <c r="O7" s="41">
+      <c r="O7" s="40">
         <f t="shared" si="1"/>
         <v>734283.01</v>
       </c>
-      <c r="P7" s="25">
+      <c r="P7" s="24">
         <f>P5+0.01</f>
         <v>0.01</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="192" t="s">
+      <c r="A8" s="130" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="88">
+      <c r="B8" s="87">
         <f>B7+1</f>
         <v>2</v>
       </c>
-      <c r="C8" s="88" t="s">
+      <c r="C8" s="87" t="s">
         <v>104</v>
       </c>
-      <c r="D8" s="88" t="s">
+      <c r="D8" s="87" t="s">
         <v>76</v>
       </c>
-      <c r="E8" s="89">
+      <c r="E8" s="88">
         <v>1.94</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="34">
         <v>1266310.02</v>
       </c>
-      <c r="G8" s="35"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="90">
+      <c r="G8" s="34"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="89">
         <f t="shared" ref="I8:I64" si="2">F8-G8</f>
         <v>1266310.02</v>
       </c>
-      <c r="J8" s="90">
+      <c r="J8" s="89">
         <f t="shared" ref="J8:J64" si="3">IF(I8&gt;0,I8*2.95%,0)</f>
         <v>37356.14559</v>
       </c>
-      <c r="K8" s="91">
+      <c r="K8" s="90">
         <f t="shared" ref="K8:K64" si="4">N$2*E8%</f>
         <v>0</v>
       </c>
-      <c r="L8" s="91">
+      <c r="L8" s="90">
         <f t="shared" ref="L8:L64" si="5">N$1*E8%</f>
         <v>157839.32095679999</v>
       </c>
-      <c r="M8" s="92">
-        <v>0</v>
-      </c>
-      <c r="N8" s="93">
+      <c r="M8" s="91">
+        <v>0</v>
+      </c>
+      <c r="N8" s="92">
         <f t="shared" si="0"/>
         <v>1461505.02</v>
       </c>
-      <c r="O8" s="94">
+      <c r="O8" s="93">
         <f t="shared" si="1"/>
         <v>1505350.02</v>
       </c>
-      <c r="P8" s="25">
+      <c r="P8" s="24">
         <f>P7+0.01</f>
         <v>0.02</v>
       </c>
-      <c r="Q8" s="25"/>
+      <c r="Q8" s="24"/>
     </row>
     <row r="9" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="192" t="s">
+      <c r="A9" s="130" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="88">
+      <c r="B9" s="87">
         <f t="shared" ref="B9:B44" si="6">B8+1</f>
         <v>3</v>
       </c>
-      <c r="C9" s="88" t="s">
+      <c r="C9" s="87" t="s">
         <v>105</v>
       </c>
-      <c r="D9" s="105" t="s">
+      <c r="D9" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="E9" s="89">
+      <c r="E9" s="88">
         <v>1.78</v>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="34">
         <v>117937.03</v>
       </c>
-      <c r="G9" s="35">
+      <c r="G9" s="34">
         <f>F9</f>
         <v>117937.03</v>
       </c>
-      <c r="H9" s="36"/>
-      <c r="I9" s="90">
+      <c r="H9" s="35"/>
+      <c r="I9" s="89">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J9" s="90">
+      <c r="J9" s="89">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K9" s="91">
+      <c r="K9" s="90">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L9" s="91">
+      <c r="L9" s="90">
         <f t="shared" si="5"/>
         <v>144821.64500159997</v>
       </c>
-      <c r="M9" s="92">
-        <v>0</v>
-      </c>
-      <c r="N9" s="93">
+      <c r="M9" s="91">
+        <v>0</v>
+      </c>
+      <c r="N9" s="92">
         <f t="shared" si="0"/>
         <v>144822.03</v>
       </c>
-      <c r="O9" s="94">
+      <c r="O9" s="93">
         <f t="shared" si="1"/>
         <v>149167.03</v>
       </c>
-      <c r="P9" s="25">
+      <c r="P9" s="24">
         <f>P8+0.01</f>
         <v>0.03</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="192" t="s">
+      <c r="A10" s="130" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="88">
+      <c r="B10" s="87">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="C10" s="88" t="s">
+      <c r="C10" s="87" t="s">
         <v>106</v>
       </c>
-      <c r="D10" s="88" t="s">
+      <c r="D10" s="87" t="s">
         <v>78</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="32">
         <v>1.62</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="33">
         <v>109837.04</v>
       </c>
-      <c r="G10" s="35">
+      <c r="G10" s="34">
         <v>113132.04</v>
       </c>
-      <c r="H10" s="36"/>
-      <c r="I10" s="37">
+      <c r="H10" s="35"/>
+      <c r="I10" s="36">
         <f t="shared" si="2"/>
         <v>-3295</v>
       </c>
-      <c r="J10" s="37">
+      <c r="J10" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K10" s="38">
+      <c r="K10" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L10" s="38">
+      <c r="L10" s="37">
         <f t="shared" si="5"/>
         <v>131803.96904640002</v>
       </c>
-      <c r="M10" s="39">
-        <v>0</v>
-      </c>
-      <c r="N10" s="40">
+      <c r="M10" s="38">
+        <v>0</v>
+      </c>
+      <c r="N10" s="39">
         <f t="shared" si="0"/>
         <v>128509.04</v>
       </c>
-      <c r="O10" s="41">
+      <c r="O10" s="40">
         <f t="shared" si="1"/>
         <v>132364.03999999998</v>
       </c>
-      <c r="P10" s="25">
+      <c r="P10" s="24">
         <f t="shared" ref="P10:P64" si="7">P9+0.01</f>
         <v>0.04</v>
       </c>
-      <c r="Q10" s="31" t="s">
+      <c r="Q10" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="R10" s="25"/>
+      <c r="R10" s="24"/>
     </row>
     <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="192" t="s">
+      <c r="A11" s="157" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="88">
+      <c r="B11" s="158">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="C11" s="88" t="s">
+      <c r="C11" s="158" t="s">
         <v>107</v>
       </c>
-      <c r="D11" s="88" t="s">
+      <c r="D11" s="158" t="s">
         <v>79</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="32">
         <v>1.94</v>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="33">
         <v>925606.05</v>
       </c>
-      <c r="G11" s="35">
-        <v>0</v>
-      </c>
-      <c r="H11" s="36"/>
-      <c r="I11" s="37">
+      <c r="G11" s="34">
+        <v>0</v>
+      </c>
+      <c r="H11" s="35"/>
+      <c r="I11" s="36">
         <f t="shared" si="2"/>
         <v>925606.05</v>
       </c>
-      <c r="J11" s="37">
+      <c r="J11" s="36">
         <f t="shared" si="3"/>
         <v>27305.378475000001</v>
       </c>
-      <c r="K11" s="38">
+      <c r="K11" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L11" s="38">
+      <c r="L11" s="37">
         <f t="shared" si="5"/>
         <v>157839.32095679999</v>
       </c>
-      <c r="M11" s="39">
-        <v>0</v>
-      </c>
-      <c r="N11" s="40">
+      <c r="M11" s="38">
+        <v>0</v>
+      </c>
+      <c r="N11" s="39">
         <f t="shared" si="0"/>
         <v>1110751.05</v>
       </c>
-      <c r="O11" s="41">
+      <c r="O11" s="40">
         <f t="shared" si="1"/>
         <v>1144074.05</v>
       </c>
-      <c r="P11" s="25">
+      <c r="P11" s="24">
         <f t="shared" si="7"/>
         <v>0.05</v>
       </c>
-      <c r="R11" s="25"/>
+      <c r="R11" s="24"/>
     </row>
     <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="192"/>
-      <c r="B12" s="88">
+      <c r="A12" s="130"/>
+      <c r="B12" s="87">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="C12" s="88" t="s">
+      <c r="C12" s="87" t="s">
         <v>108</v>
       </c>
-      <c r="D12" s="88" t="s">
+      <c r="D12" s="87" t="s">
         <v>80</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="32">
         <v>1.78</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="33">
         <v>120685.06</v>
       </c>
-      <c r="G12" s="35">
+      <c r="G12" s="34">
         <v>124306.06</v>
       </c>
-      <c r="H12" s="36"/>
-      <c r="I12" s="37">
+      <c r="H12" s="35"/>
+      <c r="I12" s="36">
         <f t="shared" si="2"/>
         <v>-3621</v>
       </c>
-      <c r="J12" s="37">
+      <c r="J12" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K12" s="38">
+      <c r="K12" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L12" s="38">
+      <c r="L12" s="37">
         <f t="shared" si="5"/>
         <v>144821.64500159997</v>
       </c>
-      <c r="M12" s="39">
-        <v>0</v>
-      </c>
-      <c r="N12" s="40">
+      <c r="M12" s="38">
+        <v>0</v>
+      </c>
+      <c r="N12" s="39">
         <f t="shared" si="0"/>
         <v>141201.06</v>
       </c>
-      <c r="O12" s="41">
+      <c r="O12" s="40">
         <f t="shared" si="1"/>
         <v>145437.06</v>
       </c>
-      <c r="P12" s="25">
+      <c r="P12" s="24">
         <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
-      <c r="R12" s="25"/>
+      <c r="R12" s="24"/>
     </row>
     <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="192"/>
-      <c r="B13" s="88">
+      <c r="A13" s="130"/>
+      <c r="B13" s="87">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="C13" s="88" t="s">
+      <c r="C13" s="87" t="s">
         <v>109</v>
       </c>
-      <c r="D13" s="88" t="s">
+      <c r="D13" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="E13" s="33">
+      <c r="E13" s="32">
         <v>1.62</v>
       </c>
-      <c r="F13" s="34">
+      <c r="F13" s="33">
         <v>109837.07</v>
       </c>
-      <c r="G13" s="35">
+      <c r="G13" s="34">
         <v>113132.07</v>
       </c>
-      <c r="H13" s="36"/>
-      <c r="I13" s="37">
+      <c r="H13" s="35"/>
+      <c r="I13" s="36">
         <f t="shared" si="2"/>
         <v>-3295</v>
       </c>
-      <c r="J13" s="37">
+      <c r="J13" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K13" s="38">
+      <c r="K13" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L13" s="38">
+      <c r="L13" s="37">
         <f t="shared" si="5"/>
         <v>131803.96904640002</v>
       </c>
-      <c r="M13" s="39">
-        <v>0</v>
-      </c>
-      <c r="N13" s="40">
+      <c r="M13" s="38">
+        <v>0</v>
+      </c>
+      <c r="N13" s="39">
         <f t="shared" si="0"/>
         <v>128509.07</v>
       </c>
-      <c r="O13" s="41">
+      <c r="O13" s="40">
         <f t="shared" si="1"/>
         <v>132364.07</v>
       </c>
-      <c r="P13" s="25">
+      <c r="P13" s="24">
         <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="Q13" s="31" t="s">
+      <c r="Q13" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="R13" s="25"/>
+      <c r="R13" s="24"/>
     </row>
     <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="192"/>
-      <c r="B14" s="88">
+      <c r="A14" s="130"/>
+      <c r="B14" s="87">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="C14" s="88" t="s">
+      <c r="C14" s="87" t="s">
         <v>110</v>
       </c>
-      <c r="D14" s="88" t="s">
+      <c r="D14" s="87" t="s">
         <v>82</v>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="32">
         <v>1.62</v>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="33">
         <v>109473.08</v>
       </c>
-      <c r="G14" s="35">
+      <c r="G14" s="34">
         <v>110000</v>
       </c>
-      <c r="H14" s="36"/>
-      <c r="I14" s="37">
+      <c r="H14" s="35"/>
+      <c r="I14" s="36">
         <f t="shared" si="2"/>
         <v>-526.91999999999825</v>
       </c>
-      <c r="J14" s="37">
+      <c r="J14" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K14" s="38">
+      <c r="K14" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L14" s="38">
+      <c r="L14" s="37">
         <f t="shared" si="5"/>
         <v>131803.96904640002</v>
       </c>
-      <c r="M14" s="39">
-        <v>0</v>
-      </c>
-      <c r="N14" s="40">
+      <c r="M14" s="38">
+        <v>0</v>
+      </c>
+      <c r="N14" s="39">
         <f t="shared" si="0"/>
         <v>131277.07999999999</v>
       </c>
-      <c r="O14" s="41">
+      <c r="O14" s="40">
         <f t="shared" si="1"/>
         <v>135215.07999999999</v>
       </c>
-      <c r="P14" s="25">
+      <c r="P14" s="24">
         <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
-      <c r="R14" s="25"/>
+      <c r="R14" s="24"/>
     </row>
     <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="192"/>
-      <c r="B15" s="88">
+      <c r="A15" s="130"/>
+      <c r="B15" s="87">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="C15" s="88" t="s">
+      <c r="C15" s="87" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="88" t="s">
+      <c r="D15" s="87" t="s">
         <v>82</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="32">
         <v>7.59</v>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="33">
         <v>803173.09</v>
       </c>
-      <c r="G15" s="35">
+      <c r="G15" s="34">
         <f>514100+273000+16073</f>
         <v>803173</v>
       </c>
-      <c r="H15" s="36"/>
-      <c r="I15" s="37">
+      <c r="H15" s="35"/>
+      <c r="I15" s="36">
         <f t="shared" si="2"/>
         <v>8.999999996740371E-2</v>
       </c>
-      <c r="J15" s="37">
+      <c r="J15" s="36">
         <f t="shared" si="3"/>
         <v>2.6549999990384096E-3</v>
       </c>
-      <c r="K15" s="38">
+      <c r="K15" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L15" s="38">
+      <c r="L15" s="37">
         <f t="shared" si="5"/>
         <v>617526.00312479993</v>
       </c>
-      <c r="M15" s="39">
-        <v>0</v>
-      </c>
-      <c r="N15" s="40">
+      <c r="M15" s="38">
+        <v>0</v>
+      </c>
+      <c r="N15" s="39">
         <f t="shared" si="0"/>
         <v>617526.09</v>
       </c>
-      <c r="O15" s="41">
+      <c r="O15" s="40">
         <f t="shared" si="1"/>
         <v>636052.09</v>
       </c>
-      <c r="P15" s="25">
+      <c r="P15" s="24">
         <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
-      <c r="R15" s="25"/>
+      <c r="R15" s="24"/>
     </row>
     <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="192"/>
-      <c r="B16" s="88">
+      <c r="A16" s="130"/>
+      <c r="B16" s="87">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="C16" s="88" t="s">
+      <c r="C16" s="87" t="s">
         <v>112</v>
       </c>
-      <c r="D16" s="88" t="s">
+      <c r="D16" s="87" t="s">
         <v>83</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="32">
         <v>1.62</v>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="33">
         <v>59501.1</v>
       </c>
-      <c r="G16" s="35">
+      <c r="G16" s="34">
         <v>61286</v>
       </c>
-      <c r="H16" s="36"/>
-      <c r="I16" s="37">
+      <c r="H16" s="35"/>
+      <c r="I16" s="36">
         <f t="shared" si="2"/>
         <v>-1784.9000000000015</v>
       </c>
-      <c r="J16" s="37">
+      <c r="J16" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K16" s="38">
+      <c r="K16" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L16" s="38">
+      <c r="L16" s="37">
         <f t="shared" si="5"/>
         <v>131803.96904640002</v>
       </c>
-      <c r="M16" s="39">
-        <v>0</v>
-      </c>
-      <c r="N16" s="40">
+      <c r="M16" s="38">
+        <v>0</v>
+      </c>
+      <c r="N16" s="39">
         <f t="shared" si="0"/>
         <v>130019.1</v>
       </c>
-      <c r="O16" s="41">
+      <c r="O16" s="40">
         <f t="shared" si="1"/>
         <v>133920.1</v>
       </c>
-      <c r="P16" s="25">
+      <c r="P16" s="24">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="Q16" t="s">
         <v>145</v>
       </c>
-      <c r="R16" s="25"/>
+      <c r="R16" s="24"/>
     </row>
     <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="192"/>
-      <c r="B17" s="88">
+      <c r="A17" s="130"/>
+      <c r="B17" s="87">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="C17" s="88" t="s">
+      <c r="C17" s="87" t="s">
         <v>113</v>
       </c>
-      <c r="D17" s="88" t="s">
+      <c r="D17" s="87" t="s">
         <v>84</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="32">
         <v>1.78</v>
       </c>
-      <c r="F17" s="34">
+      <c r="F17" s="33">
         <v>404905.11</v>
       </c>
-      <c r="G17" s="35">
-        <v>0</v>
-      </c>
-      <c r="H17" s="36"/>
-      <c r="I17" s="37">
+      <c r="G17" s="34">
+        <v>0</v>
+      </c>
+      <c r="H17" s="35"/>
+      <c r="I17" s="36">
         <f t="shared" si="2"/>
         <v>404905.11</v>
       </c>
-      <c r="J17" s="37">
+      <c r="J17" s="36">
         <f t="shared" si="3"/>
         <v>11944.700745</v>
       </c>
-      <c r="K17" s="38">
+      <c r="K17" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L17" s="38">
+      <c r="L17" s="37">
         <f t="shared" si="5"/>
         <v>144821.64500159997</v>
       </c>
-      <c r="M17" s="39">
-        <v>0</v>
-      </c>
-      <c r="N17" s="40">
+      <c r="M17" s="38">
+        <v>0</v>
+      </c>
+      <c r="N17" s="39">
         <f t="shared" si="0"/>
         <v>561671.11</v>
       </c>
-      <c r="O17" s="41">
+      <c r="O17" s="40">
         <f t="shared" si="1"/>
         <v>578521.11</v>
       </c>
-      <c r="P17" s="25">
+      <c r="P17" s="24">
         <f t="shared" si="7"/>
         <v>0.10999999999999999</v>
       </c>
-      <c r="R17" s="25"/>
+      <c r="R17" s="24"/>
     </row>
     <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="192"/>
-      <c r="B18" s="88">
+      <c r="A18" s="130"/>
+      <c r="B18" s="87">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="C18" s="88" t="s">
+      <c r="C18" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="D18" s="88" t="s">
+      <c r="D18" s="87" t="s">
         <v>84</v>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="32">
         <v>1.3</v>
       </c>
-      <c r="F18" s="34">
+      <c r="F18" s="33">
         <v>295773.12</v>
       </c>
-      <c r="G18" s="35">
-        <v>0</v>
-      </c>
-      <c r="H18" s="36"/>
-      <c r="I18" s="37">
+      <c r="G18" s="34">
+        <v>0</v>
+      </c>
+      <c r="H18" s="35"/>
+      <c r="I18" s="36">
         <f t="shared" si="2"/>
         <v>295773.12</v>
       </c>
-      <c r="J18" s="37">
+      <c r="J18" s="36">
         <f t="shared" si="3"/>
         <v>8725.3070399999997</v>
       </c>
-      <c r="K18" s="38">
+      <c r="K18" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L18" s="38">
+      <c r="L18" s="37">
         <f t="shared" si="5"/>
         <v>105768.617136</v>
       </c>
-      <c r="M18" s="39">
-        <v>0</v>
-      </c>
-      <c r="N18" s="40">
+      <c r="M18" s="38">
+        <v>0</v>
+      </c>
+      <c r="N18" s="39">
         <f t="shared" si="0"/>
         <v>410267.12</v>
       </c>
-      <c r="O18" s="41">
+      <c r="O18" s="40">
         <f t="shared" si="1"/>
         <v>422575.12</v>
       </c>
-      <c r="P18" s="25">
+      <c r="P18" s="24">
         <f t="shared" si="7"/>
         <v>0.11999999999999998</v>
       </c>
-      <c r="R18" s="25"/>
+      <c r="R18" s="24"/>
     </row>
     <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="192"/>
-      <c r="B19" s="88">
+      <c r="A19" s="130"/>
+      <c r="B19" s="87">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="C19" s="88" t="s">
+      <c r="C19" s="87" t="s">
         <v>115</v>
       </c>
-      <c r="D19" s="88" t="s">
+      <c r="D19" s="87" t="s">
         <v>85</v>
       </c>
-      <c r="E19" s="33">
+      <c r="E19" s="32">
         <v>1.38</v>
       </c>
-      <c r="F19" s="34">
+      <c r="F19" s="33">
         <v>93565.13</v>
       </c>
-      <c r="G19" s="35">
+      <c r="G19" s="34">
         <f>226963.27-G20</f>
         <v>100176.12999999999</v>
       </c>
-      <c r="H19" s="36"/>
-      <c r="I19" s="37">
+      <c r="H19" s="35"/>
+      <c r="I19" s="36">
         <f t="shared" si="2"/>
         <v>-6610.9999999999854</v>
       </c>
-      <c r="J19" s="37">
+      <c r="J19" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K19" s="38">
+      <c r="K19" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L19" s="38">
+      <c r="L19" s="37">
         <f t="shared" si="5"/>
         <v>112277.45511359998</v>
       </c>
-      <c r="M19" s="39">
-        <v>0</v>
-      </c>
-      <c r="N19" s="40">
+      <c r="M19" s="38">
+        <v>0</v>
+      </c>
+      <c r="N19" s="39">
         <f t="shared" si="0"/>
         <v>105666.13</v>
       </c>
-      <c r="O19" s="41">
+      <c r="O19" s="40">
         <f t="shared" si="1"/>
         <v>108836.13</v>
       </c>
-      <c r="P19" s="25">
+      <c r="P19" s="24">
         <f t="shared" si="7"/>
         <v>0.12999999999999998</v>
       </c>
       <c r="Q19" t="s">
         <v>147</v>
       </c>
-      <c r="R19" s="25"/>
+      <c r="R19" s="24"/>
     </row>
     <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="192"/>
-      <c r="B20" s="88">
+      <c r="A20" s="130"/>
+      <c r="B20" s="87">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="C20" s="88" t="s">
+      <c r="C20" s="87" t="s">
         <v>116</v>
       </c>
-      <c r="D20" s="88" t="s">
+      <c r="D20" s="87" t="s">
         <v>85</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="32">
         <v>1.87</v>
       </c>
-      <c r="F20" s="34">
+      <c r="F20" s="33">
         <v>126787.14</v>
       </c>
-      <c r="G20" s="35">
+      <c r="G20" s="34">
         <f>F20</f>
         <v>126787.14</v>
       </c>
-      <c r="H20" s="36"/>
-      <c r="I20" s="37">
+      <c r="H20" s="35"/>
+      <c r="I20" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="37">
+      <c r="J20" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K20" s="38">
+      <c r="K20" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L20" s="38">
+      <c r="L20" s="37">
         <f t="shared" si="5"/>
         <v>152144.0877264</v>
       </c>
-      <c r="M20" s="39">
-        <v>0</v>
-      </c>
-      <c r="N20" s="40">
+      <c r="M20" s="38">
+        <v>0</v>
+      </c>
+      <c r="N20" s="39">
         <f t="shared" si="0"/>
         <v>152144.14000000001</v>
       </c>
-      <c r="O20" s="41">
+      <c r="O20" s="40">
         <f t="shared" si="1"/>
         <v>156708.14000000001</v>
       </c>
-      <c r="P20" s="25">
+      <c r="P20" s="24">
         <f t="shared" si="7"/>
         <v>0.13999999999999999</v>
       </c>
       <c r="Q20" t="s">
         <v>147</v>
       </c>
-      <c r="R20" s="25"/>
+      <c r="R20" s="24"/>
     </row>
     <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="192"/>
-      <c r="B21" s="88">
+      <c r="A21" s="130"/>
+      <c r="B21" s="159">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="C21" s="88" t="s">
+      <c r="C21" s="159" t="s">
         <v>117</v>
       </c>
-      <c r="D21" s="88" t="s">
+      <c r="D21" s="159" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="32">
         <v>2.91</v>
       </c>
-      <c r="F21" s="34">
+      <c r="F21" s="33">
         <v>1018878.15</v>
       </c>
-      <c r="G21" s="35">
+      <c r="G21" s="34">
         <f>100000*5+200000</f>
         <v>700000</v>
       </c>
-      <c r="H21" s="36"/>
-      <c r="I21" s="37">
+      <c r="H21" s="35"/>
+      <c r="I21" s="36">
         <f t="shared" si="2"/>
         <v>318878.15000000002</v>
       </c>
-      <c r="J21" s="37">
+      <c r="J21" s="36">
         <f t="shared" si="3"/>
         <v>9406.9054250000008</v>
       </c>
-      <c r="K21" s="38">
+      <c r="K21" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L21" s="38">
+      <c r="L21" s="37">
         <f t="shared" si="5"/>
         <v>236758.9814352</v>
       </c>
-      <c r="M21" s="39">
-        <v>0</v>
-      </c>
-      <c r="N21" s="40">
+      <c r="M21" s="38">
+        <v>0</v>
+      </c>
+      <c r="N21" s="39">
         <f t="shared" si="0"/>
         <v>565044.15</v>
       </c>
-      <c r="O21" s="41">
+      <c r="O21" s="40">
         <f t="shared" si="1"/>
         <v>581995.15</v>
       </c>
-      <c r="P21" s="25">
+      <c r="P21" s="24">
         <f t="shared" si="7"/>
         <v>0.15</v>
       </c>
       <c r="Q21" t="s">
-        <v>179</v>
-      </c>
-      <c r="R21" s="25"/>
+        <v>165</v>
+      </c>
+      <c r="R21" s="24"/>
     </row>
     <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="192"/>
-      <c r="B22" s="88">
+      <c r="A22" s="130"/>
+      <c r="B22" s="87">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="C22" s="88" t="s">
+      <c r="C22" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="D22" s="88" t="s">
+      <c r="D22" s="87" t="s">
         <v>87</v>
       </c>
-      <c r="E22" s="33">
+      <c r="E22" s="32">
         <v>2.14</v>
       </c>
-      <c r="F22" s="34">
+      <c r="F22" s="33">
         <v>141755.16</v>
       </c>
-      <c r="G22" s="35">
+      <c r="G22" s="34">
         <v>146100</v>
       </c>
-      <c r="H22" s="36"/>
-      <c r="I22" s="37">
+      <c r="H22" s="35"/>
+      <c r="I22" s="36">
         <f t="shared" si="2"/>
         <v>-4344.8399999999965</v>
       </c>
-      <c r="J22" s="37">
+      <c r="J22" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K22" s="38">
+      <c r="K22" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L22" s="38">
+      <c r="L22" s="37">
         <f t="shared" si="5"/>
         <v>174111.4159008</v>
       </c>
-      <c r="M22" s="39">
-        <v>0</v>
-      </c>
-      <c r="N22" s="40">
+      <c r="M22" s="38">
+        <v>0</v>
+      </c>
+      <c r="N22" s="39">
         <f t="shared" si="0"/>
         <v>169767.16</v>
       </c>
-      <c r="O22" s="41">
+      <c r="O22" s="40">
         <f t="shared" si="1"/>
         <v>174860.16</v>
       </c>
-      <c r="P22" s="25">
+      <c r="P22" s="24">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
       <c r="Q22" t="s">
         <v>145</v>
       </c>
-      <c r="R22" s="25"/>
+      <c r="R22" s="24"/>
     </row>
     <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="192" t="s">
+      <c r="A23" s="130" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="88">
+      <c r="B23" s="87">
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="C23" s="88" t="s">
+      <c r="C23" s="87" t="s">
         <v>119</v>
       </c>
-      <c r="D23" s="88" t="s">
+      <c r="D23" s="87" t="s">
         <v>82</v>
       </c>
-      <c r="E23" s="33">
+      <c r="E23" s="32">
         <v>0.89</v>
       </c>
-      <c r="F23" s="34">
+      <c r="F23" s="33">
         <v>60260.17</v>
       </c>
-      <c r="G23" s="35">
+      <c r="G23" s="34">
         <v>60300</v>
       </c>
-      <c r="H23" s="36"/>
-      <c r="I23" s="37">
+      <c r="H23" s="35"/>
+      <c r="I23" s="36">
         <f t="shared" si="2"/>
         <v>-39.830000000001746</v>
       </c>
-      <c r="J23" s="37">
+      <c r="J23" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K23" s="38">
+      <c r="K23" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L23" s="38">
+      <c r="L23" s="37">
         <f t="shared" si="5"/>
         <v>72410.822500799986</v>
       </c>
-      <c r="M23" s="39">
-        <v>0</v>
-      </c>
-      <c r="N23" s="40">
+      <c r="M23" s="38">
+        <v>0</v>
+      </c>
+      <c r="N23" s="39">
         <f t="shared" si="0"/>
         <v>72371.17</v>
       </c>
-      <c r="O23" s="41">
+      <c r="O23" s="40">
         <f t="shared" si="1"/>
         <v>74542.17</v>
       </c>
-      <c r="P23" s="25">
+      <c r="P23" s="24">
         <f t="shared" si="7"/>
         <v>0.17</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="192" t="s">
+      <c r="A24" s="130" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="88">
+      <c r="B24" s="87">
         <f t="shared" si="6"/>
         <v>18</v>
       </c>
-      <c r="C24" s="88" t="s">
+      <c r="C24" s="87" t="s">
         <v>120</v>
       </c>
-      <c r="D24" s="88" t="s">
+      <c r="D24" s="87" t="s">
         <v>88</v>
       </c>
-      <c r="E24" s="89">
+      <c r="E24" s="88">
         <v>0.95</v>
       </c>
-      <c r="F24" s="35">
+      <c r="F24" s="34">
         <v>2996892.18</v>
       </c>
-      <c r="G24" s="35">
-        <v>0</v>
-      </c>
-      <c r="H24" s="36"/>
-      <c r="I24" s="37">
+      <c r="G24" s="34">
+        <v>0</v>
+      </c>
+      <c r="H24" s="35"/>
+      <c r="I24" s="36">
         <f t="shared" si="2"/>
         <v>2996892.18</v>
       </c>
-      <c r="J24" s="37">
+      <c r="J24" s="36">
         <f t="shared" si="3"/>
         <v>88408.319310000006</v>
       </c>
-      <c r="K24" s="38">
+      <c r="K24" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L24" s="38">
+      <c r="L24" s="37">
         <f t="shared" si="5"/>
         <v>77292.450983999996</v>
       </c>
-      <c r="M24" s="39">
-        <v>0</v>
-      </c>
-      <c r="N24" s="40">
+      <c r="M24" s="38">
+        <v>0</v>
+      </c>
+      <c r="N24" s="39">
         <f t="shared" si="0"/>
         <v>3162593.18</v>
       </c>
-      <c r="O24" s="41">
+      <c r="O24" s="40">
         <f t="shared" si="1"/>
         <v>3257471.18</v>
       </c>
-      <c r="P24" s="25">
+      <c r="P24" s="24">
         <f t="shared" si="7"/>
         <v>0.18000000000000002</v>
       </c>
-      <c r="Q24" s="76"/>
-      <c r="R24" s="75"/>
+      <c r="Q24" s="75"/>
+      <c r="R24" s="74"/>
     </row>
     <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="192" t="s">
+      <c r="A25" s="130" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="88">
+      <c r="B25" s="87">
         <f t="shared" si="6"/>
         <v>19</v>
       </c>
-      <c r="C25" s="88" t="s">
+      <c r="C25" s="87" t="s">
         <v>121</v>
       </c>
-      <c r="D25" s="88" t="s">
+      <c r="D25" s="87" t="s">
         <v>82</v>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="32">
         <v>1.94</v>
       </c>
-      <c r="F25" s="34">
+      <c r="F25" s="33">
         <v>131119.19</v>
       </c>
-      <c r="G25" s="35">
+      <c r="G25" s="34">
         <v>131800</v>
       </c>
-      <c r="H25" s="36"/>
-      <c r="I25" s="37">
+      <c r="H25" s="35"/>
+      <c r="I25" s="36">
         <f t="shared" si="2"/>
         <v>-680.80999999999767</v>
       </c>
-      <c r="J25" s="37">
+      <c r="J25" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K25" s="38">
+      <c r="K25" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L25" s="38">
+      <c r="L25" s="37">
         <f t="shared" si="5"/>
         <v>157839.32095679999</v>
       </c>
-      <c r="M25" s="39">
-        <v>0</v>
-      </c>
-      <c r="N25" s="40">
+      <c r="M25" s="38">
+        <v>0</v>
+      </c>
+      <c r="N25" s="39">
         <f t="shared" si="0"/>
         <v>157159.19</v>
       </c>
-      <c r="O25" s="41">
+      <c r="O25" s="40">
         <f t="shared" si="1"/>
         <v>161874.19</v>
       </c>
-      <c r="P25" s="25">
+      <c r="P25" s="24">
         <f t="shared" si="7"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="192" t="s">
+      <c r="A26" s="130" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="88">
+      <c r="B26" s="87">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="C26" s="88" t="s">
+      <c r="C26" s="87" t="s">
         <v>122</v>
       </c>
-      <c r="D26" s="88" t="s">
+      <c r="D26" s="87" t="s">
         <v>89</v>
       </c>
-      <c r="E26" s="33">
+      <c r="E26" s="32">
         <v>1.84</v>
       </c>
-      <c r="F26" s="34">
+      <c r="F26" s="33">
         <v>194767.2</v>
       </c>
-      <c r="G26" s="35">
+      <c r="G26" s="34">
         <v>124753.2</v>
       </c>
-      <c r="H26" s="36"/>
-      <c r="I26" s="37">
+      <c r="H26" s="35"/>
+      <c r="I26" s="36">
         <f t="shared" si="2"/>
         <v>70014.000000000015</v>
       </c>
-      <c r="J26" s="37">
+      <c r="J26" s="36">
         <f t="shared" si="3"/>
         <v>2065.4130000000005</v>
       </c>
-      <c r="K26" s="38">
+      <c r="K26" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L26" s="38">
+      <c r="L26" s="37">
         <f t="shared" si="5"/>
         <v>149703.27348479998</v>
       </c>
-      <c r="M26" s="39">
-        <v>0</v>
-      </c>
-      <c r="N26" s="40">
+      <c r="M26" s="38">
+        <v>0</v>
+      </c>
+      <c r="N26" s="39">
         <f t="shared" si="0"/>
         <v>221783.2</v>
       </c>
-      <c r="O26" s="41">
+      <c r="O26" s="40">
         <f t="shared" si="1"/>
         <v>228436.2</v>
       </c>
-      <c r="P26" s="25">
+      <c r="P26" s="24">
         <f t="shared" si="7"/>
         <v>0.20000000000000004</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="192" t="s">
+      <c r="A27" s="130" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="88">
+      <c r="B27" s="87">
         <f t="shared" si="6"/>
         <v>21</v>
       </c>
-      <c r="C27" s="88">
+      <c r="C27" s="87">
         <v>1106</v>
       </c>
-      <c r="D27" s="88" t="s">
+      <c r="D27" s="87" t="s">
         <v>90</v>
       </c>
-      <c r="E27" s="33">
+      <c r="E27" s="32">
         <v>5.12</v>
       </c>
-      <c r="F27" s="34">
+      <c r="F27" s="33">
         <v>6425609.21</v>
       </c>
-      <c r="G27" s="35">
+      <c r="G27" s="34">
         <f>500000+600000</f>
         <v>1100000</v>
       </c>
-      <c r="H27" s="36"/>
-      <c r="I27" s="37">
+      <c r="H27" s="35"/>
+      <c r="I27" s="36">
         <f t="shared" si="2"/>
         <v>5325609.21</v>
       </c>
-      <c r="J27" s="37">
+      <c r="J27" s="36">
         <f t="shared" si="3"/>
         <v>157105.47169500001</v>
       </c>
-      <c r="K27" s="38">
+      <c r="K27" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L27" s="38">
+      <c r="L27" s="37">
         <f t="shared" si="5"/>
         <v>416565.63056639995</v>
       </c>
-      <c r="M27" s="39">
-        <v>0</v>
-      </c>
-      <c r="N27" s="40">
+      <c r="M27" s="38">
+        <v>0</v>
+      </c>
+      <c r="N27" s="39">
         <f t="shared" si="0"/>
         <v>5899280.21</v>
       </c>
-      <c r="O27" s="41">
+      <c r="O27" s="40">
         <f t="shared" si="1"/>
         <v>6076258.21</v>
       </c>
-      <c r="P27" s="25">
+      <c r="P27" s="24">
         <f t="shared" si="7"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="192" t="s">
+      <c r="A28" s="130" t="s">
         <v>17</v>
       </c>
-      <c r="B28" s="88">
+      <c r="B28" s="164">
         <f t="shared" si="6"/>
         <v>22</v>
       </c>
-      <c r="C28" s="88">
+      <c r="C28" s="164">
         <v>1101</v>
       </c>
-      <c r="D28" s="88" t="s">
+      <c r="D28" s="164" t="s">
         <v>82</v>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="32">
         <v>3.88</v>
       </c>
-      <c r="F28" s="34">
+      <c r="F28" s="33">
         <v>261894.22</v>
       </c>
-      <c r="G28" s="35">
-        <v>0</v>
-      </c>
-      <c r="H28" s="36"/>
-      <c r="I28" s="37">
+      <c r="G28" s="34">
+        <v>0</v>
+      </c>
+      <c r="H28" s="35"/>
+      <c r="I28" s="36">
         <f t="shared" si="2"/>
         <v>261894.22</v>
       </c>
-      <c r="J28" s="37">
+      <c r="J28" s="36">
         <f t="shared" si="3"/>
         <v>7725.8794900000003</v>
       </c>
-      <c r="K28" s="38">
+      <c r="K28" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L28" s="38">
+      <c r="L28" s="37">
         <f t="shared" si="5"/>
         <v>315678.64191359997</v>
       </c>
-      <c r="M28" s="39">
-        <v>0</v>
-      </c>
-      <c r="N28" s="40">
+      <c r="M28" s="38">
+        <v>0</v>
+      </c>
+      <c r="N28" s="39">
         <f t="shared" si="0"/>
         <v>585299.22</v>
       </c>
-      <c r="O28" s="41">
+      <c r="O28" s="40">
         <f t="shared" si="1"/>
         <v>602858.22</v>
       </c>
-      <c r="P28" s="25">
+      <c r="P28" s="24">
         <f t="shared" si="7"/>
         <v>0.22000000000000006</v>
       </c>
@@ -4568,341 +4521,341 @@
       </c>
     </row>
     <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="192" t="s">
+      <c r="A29" s="130" t="s">
         <v>18</v>
       </c>
-      <c r="B29" s="88">
+      <c r="B29" s="87">
         <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="C29" s="88">
+      <c r="C29" s="87">
         <v>1102</v>
       </c>
-      <c r="D29" s="88" t="s">
+      <c r="D29" s="87" t="s">
         <v>91</v>
       </c>
-      <c r="E29" s="33">
+      <c r="E29" s="32">
         <v>0.92</v>
       </c>
-      <c r="F29" s="34">
+      <c r="F29" s="33">
         <v>64247.23</v>
       </c>
-      <c r="G29" s="35">
+      <c r="G29" s="34">
         <f>F29</f>
         <v>64247.23</v>
       </c>
-      <c r="H29" s="36"/>
-      <c r="I29" s="37">
+      <c r="H29" s="35"/>
+      <c r="I29" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J29" s="37">
+      <c r="J29" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K29" s="38">
+      <c r="K29" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L29" s="38">
+      <c r="L29" s="37">
         <f t="shared" si="5"/>
         <v>74851.636742399991</v>
       </c>
-      <c r="M29" s="39">
-        <v>0</v>
-      </c>
-      <c r="N29" s="40">
+      <c r="M29" s="38">
+        <v>0</v>
+      </c>
+      <c r="N29" s="39">
         <f t="shared" si="0"/>
         <v>74852.23</v>
       </c>
-      <c r="O29" s="41">
+      <c r="O29" s="40">
         <f t="shared" si="1"/>
         <v>77098.23</v>
       </c>
-      <c r="P29" s="25">
+      <c r="P29" s="24">
         <f t="shared" si="7"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="192" t="s">
+      <c r="A30" s="130" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="88">
+      <c r="B30" s="87">
         <f t="shared" si="6"/>
         <v>24</v>
       </c>
-      <c r="C30" s="88">
+      <c r="C30" s="87">
         <v>1103</v>
       </c>
-      <c r="D30" s="88" t="s">
+      <c r="D30" s="87" t="s">
         <v>92</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="32">
         <v>1.43</v>
       </c>
-      <c r="F30" s="34">
+      <c r="F30" s="33">
         <v>5037347.24</v>
       </c>
-      <c r="G30" s="35">
-        <v>0</v>
-      </c>
-      <c r="H30" s="36"/>
-      <c r="I30" s="37">
+      <c r="G30" s="34">
+        <v>0</v>
+      </c>
+      <c r="H30" s="35"/>
+      <c r="I30" s="36">
         <f t="shared" si="2"/>
         <v>5037347.24</v>
       </c>
-      <c r="J30" s="37">
+      <c r="J30" s="36">
         <f t="shared" si="3"/>
         <v>148601.74358000001</v>
       </c>
-      <c r="K30" s="38">
+      <c r="K30" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L30" s="38">
+      <c r="L30" s="37">
         <f t="shared" si="5"/>
         <v>116345.4788496</v>
       </c>
-      <c r="M30" s="39">
-        <v>0</v>
-      </c>
-      <c r="N30" s="40">
+      <c r="M30" s="38">
+        <v>0</v>
+      </c>
+      <c r="N30" s="39">
         <f t="shared" si="0"/>
         <v>5302294.24</v>
       </c>
-      <c r="O30" s="41">
+      <c r="O30" s="40">
         <f t="shared" si="1"/>
         <v>5461363.2400000002</v>
       </c>
-      <c r="P30" s="25">
+      <c r="P30" s="24">
         <f t="shared" si="7"/>
         <v>0.24000000000000007</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="192" t="s">
+      <c r="A31" s="130" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="88">
+      <c r="B31" s="87">
         <f t="shared" si="6"/>
         <v>25</v>
       </c>
-      <c r="C31" s="88">
+      <c r="C31" s="87">
         <v>1104</v>
       </c>
-      <c r="D31" s="88" t="s">
+      <c r="D31" s="87" t="s">
         <v>93</v>
       </c>
-      <c r="E31" s="33">
+      <c r="E31" s="32">
         <v>2.19</v>
       </c>
-      <c r="F31" s="34">
+      <c r="F31" s="33">
         <v>142674.25</v>
       </c>
-      <c r="G31" s="35">
-        <v>0</v>
-      </c>
-      <c r="H31" s="36"/>
-      <c r="I31" s="37">
+      <c r="G31" s="34">
+        <v>0</v>
+      </c>
+      <c r="H31" s="35"/>
+      <c r="I31" s="36">
         <f t="shared" si="2"/>
         <v>142674.25</v>
       </c>
-      <c r="J31" s="37">
+      <c r="J31" s="36">
         <f t="shared" si="3"/>
         <v>4208.8903749999999</v>
       </c>
-      <c r="K31" s="38">
+      <c r="K31" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L31" s="38">
+      <c r="L31" s="37">
         <f t="shared" si="5"/>
         <v>178179.43963679997</v>
       </c>
-      <c r="M31" s="39">
-        <v>0</v>
-      </c>
-      <c r="N31" s="40">
+      <c r="M31" s="38">
+        <v>0</v>
+      </c>
+      <c r="N31" s="39">
         <f t="shared" si="0"/>
         <v>325063.25</v>
       </c>
-      <c r="O31" s="41">
+      <c r="O31" s="40">
         <f t="shared" si="1"/>
         <v>334815.25</v>
       </c>
-      <c r="P31" s="25">
+      <c r="P31" s="24">
         <f t="shared" si="7"/>
         <v>0.25000000000000006</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="192" t="s">
+      <c r="A32" s="130" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="88">
+      <c r="B32" s="87">
         <f t="shared" si="6"/>
         <v>26</v>
       </c>
-      <c r="C32" s="88">
+      <c r="C32" s="87">
         <v>1105</v>
       </c>
-      <c r="D32" s="88" t="s">
+      <c r="D32" s="87" t="s">
         <v>94</v>
       </c>
-      <c r="E32" s="33">
+      <c r="E32" s="32">
         <v>1.94</v>
       </c>
-      <c r="F32" s="34">
+      <c r="F32" s="33">
         <v>170408.26</v>
       </c>
-      <c r="G32" s="35">
+      <c r="G32" s="34">
         <f>F32</f>
         <v>170408.26</v>
       </c>
-      <c r="H32" s="36"/>
-      <c r="I32" s="37">
+      <c r="H32" s="35"/>
+      <c r="I32" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J32" s="37">
+      <c r="J32" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K32" s="38">
+      <c r="K32" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L32" s="38">
+      <c r="L32" s="37">
         <f t="shared" si="5"/>
         <v>157839.32095679999</v>
       </c>
-      <c r="M32" s="39">
-        <v>0</v>
-      </c>
-      <c r="N32" s="40">
+      <c r="M32" s="38">
+        <v>0</v>
+      </c>
+      <c r="N32" s="39">
         <f t="shared" si="0"/>
         <v>157839.26</v>
       </c>
-      <c r="O32" s="41">
+      <c r="O32" s="40">
         <f t="shared" si="1"/>
         <v>162574.26</v>
       </c>
-      <c r="P32" s="25">
+      <c r="P32" s="24">
         <f t="shared" si="7"/>
         <v>0.26000000000000006</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="192" t="s">
+      <c r="A33" s="130" t="s">
         <v>20</v>
       </c>
-      <c r="B33" s="88">
+      <c r="B33" s="87">
         <f t="shared" si="6"/>
         <v>27</v>
       </c>
-      <c r="C33" s="88">
+      <c r="C33" s="87">
         <v>2206</v>
       </c>
-      <c r="D33" s="88" t="s">
+      <c r="D33" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="E33" s="33">
+      <c r="E33" s="32">
         <v>2.17</v>
       </c>
-      <c r="F33" s="34">
+      <c r="F33" s="33">
         <v>148090.26999999999</v>
       </c>
-      <c r="G33" s="35">
+      <c r="G33" s="34">
         <f>F33</f>
         <v>148090.26999999999</v>
       </c>
-      <c r="H33" s="36"/>
-      <c r="I33" s="37">
+      <c r="H33" s="35"/>
+      <c r="I33" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J33" s="37">
+      <c r="J33" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K33" s="38">
+      <c r="K33" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L33" s="38">
+      <c r="L33" s="37">
         <f t="shared" si="5"/>
         <v>176552.23014239999</v>
       </c>
-      <c r="M33" s="39">
-        <v>0</v>
-      </c>
-      <c r="N33" s="40">
+      <c r="M33" s="38">
+        <v>0</v>
+      </c>
+      <c r="N33" s="39">
         <f t="shared" si="0"/>
         <v>176552.27</v>
       </c>
-      <c r="O33" s="41">
+      <c r="O33" s="40">
         <f t="shared" si="1"/>
         <v>181849.27</v>
       </c>
-      <c r="P33" s="25">
+      <c r="P33" s="24">
         <f t="shared" si="7"/>
         <v>0.27000000000000007</v>
       </c>
-      <c r="R33" s="24"/>
+      <c r="R33" s="23"/>
     </row>
     <row r="34" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="192" t="s">
+      <c r="A34" s="130" t="s">
         <v>20</v>
       </c>
-      <c r="B34" s="88">
+      <c r="B34" s="87">
         <f t="shared" si="6"/>
         <v>28</v>
       </c>
-      <c r="C34" s="88">
+      <c r="C34" s="87">
         <v>2207</v>
       </c>
-      <c r="D34" s="88" t="s">
+      <c r="D34" s="87" t="s">
         <v>96</v>
       </c>
-      <c r="E34" s="33">
+      <c r="E34" s="32">
         <v>1.23</v>
       </c>
-      <c r="F34" s="35">
+      <c r="F34" s="34">
         <v>81578.28</v>
       </c>
-      <c r="G34" s="35">
+      <c r="G34" s="34">
         <v>84025.279999999999</v>
       </c>
-      <c r="H34" s="36"/>
-      <c r="I34" s="37">
+      <c r="H34" s="35"/>
+      <c r="I34" s="36">
         <f t="shared" si="2"/>
         <v>-2447</v>
       </c>
-      <c r="J34" s="37">
+      <c r="J34" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K34" s="38">
+      <c r="K34" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L34" s="38">
+      <c r="L34" s="37">
         <f t="shared" si="5"/>
         <v>100073.38390559999</v>
       </c>
-      <c r="M34" s="39">
-        <v>0</v>
-      </c>
-      <c r="N34" s="40">
+      <c r="M34" s="38">
+        <v>0</v>
+      </c>
+      <c r="N34" s="39">
         <f t="shared" si="0"/>
         <v>97626.28</v>
       </c>
-      <c r="O34" s="41">
+      <c r="O34" s="40">
         <f t="shared" si="1"/>
         <v>100555.28</v>
       </c>
-      <c r="P34" s="25">
+      <c r="P34" s="24">
         <f t="shared" si="7"/>
         <v>0.28000000000000008</v>
       </c>
@@ -4911,172 +4864,172 @@
       </c>
     </row>
     <row r="35" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="192" t="s">
+      <c r="A35" s="130" t="s">
         <v>21</v>
       </c>
-      <c r="B35" s="88">
+      <c r="B35" s="87">
         <f t="shared" si="6"/>
         <v>29</v>
       </c>
-      <c r="C35" s="88">
+      <c r="C35" s="87">
         <v>2208</v>
       </c>
-      <c r="D35" s="88" t="s">
+      <c r="D35" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="E35" s="33">
+      <c r="E35" s="32">
         <v>1.29</v>
       </c>
-      <c r="F35" s="34">
+      <c r="F35" s="33">
         <v>87463.29</v>
       </c>
-      <c r="G35" s="35">
+      <c r="G35" s="34">
         <f>F35</f>
         <v>87463.29</v>
       </c>
-      <c r="H35" s="36"/>
-      <c r="I35" s="37">
+      <c r="H35" s="35"/>
+      <c r="I35" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J35" s="37">
+      <c r="J35" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K35" s="38">
+      <c r="K35" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L35" s="38">
+      <c r="L35" s="37">
         <f t="shared" si="5"/>
         <v>104955.01238879999</v>
       </c>
-      <c r="M35" s="39">
-        <v>0</v>
-      </c>
-      <c r="N35" s="40">
+      <c r="M35" s="38">
+        <v>0</v>
+      </c>
+      <c r="N35" s="39">
         <f t="shared" si="0"/>
         <v>104955.29</v>
       </c>
-      <c r="O35" s="41">
+      <c r="O35" s="40">
         <f t="shared" si="1"/>
         <v>108104.29</v>
       </c>
-      <c r="P35" s="25">
+      <c r="P35" s="24">
         <f t="shared" si="7"/>
         <v>0.29000000000000009</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="192" t="s">
+      <c r="A36" s="130" t="s">
         <v>21</v>
       </c>
-      <c r="B36" s="88">
+      <c r="B36" s="87">
         <f t="shared" si="6"/>
         <v>30</v>
       </c>
-      <c r="C36" s="88">
+      <c r="C36" s="87">
         <v>2201</v>
       </c>
-      <c r="D36" s="88" t="s">
+      <c r="D36" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="E36" s="33">
+      <c r="E36" s="32">
         <v>1.36</v>
       </c>
-      <c r="F36" s="34">
+      <c r="F36" s="33">
         <v>92209.3</v>
       </c>
-      <c r="G36" s="35">
+      <c r="G36" s="34">
         <f>F36</f>
         <v>92209.3</v>
       </c>
-      <c r="H36" s="36"/>
-      <c r="I36" s="37">
+      <c r="H36" s="35"/>
+      <c r="I36" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J36" s="37">
+      <c r="J36" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="38">
+      <c r="K36" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L36" s="38">
+      <c r="L36" s="37">
         <f t="shared" si="5"/>
         <v>110650.2456192</v>
       </c>
-      <c r="M36" s="39">
-        <v>0</v>
-      </c>
-      <c r="N36" s="40">
+      <c r="M36" s="38">
+        <v>0</v>
+      </c>
+      <c r="N36" s="39">
         <f t="shared" si="0"/>
         <v>110650.3</v>
       </c>
-      <c r="O36" s="41">
+      <c r="O36" s="40">
         <f t="shared" si="1"/>
         <v>113970.3</v>
       </c>
-      <c r="P36" s="25">
+      <c r="P36" s="24">
         <f t="shared" si="7"/>
         <v>0.3000000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="192" t="s">
+      <c r="A37" s="130" t="s">
         <v>22</v>
       </c>
-      <c r="B37" s="88">
+      <c r="B37" s="87">
         <f t="shared" si="6"/>
         <v>31</v>
       </c>
-      <c r="C37" s="88">
+      <c r="C37" s="87">
         <v>2202</v>
       </c>
-      <c r="D37" s="88" t="s">
+      <c r="D37" s="87" t="s">
         <v>98</v>
       </c>
-      <c r="E37" s="33">
+      <c r="E37" s="32">
         <v>0.57999999999999996</v>
       </c>
-      <c r="F37" s="35">
+      <c r="F37" s="34">
         <v>70047.31</v>
       </c>
-      <c r="G37" s="35">
+      <c r="G37" s="34">
         <f>30737.31+72148.31</f>
         <v>102885.62</v>
       </c>
-      <c r="H37" s="36"/>
-      <c r="I37" s="37">
+      <c r="H37" s="35"/>
+      <c r="I37" s="36">
         <f t="shared" si="2"/>
         <v>-32838.31</v>
       </c>
-      <c r="J37" s="37">
+      <c r="J37" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K37" s="38">
+      <c r="K37" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L37" s="38">
+      <c r="L37" s="37">
         <f t="shared" si="5"/>
         <v>47189.075337599992</v>
       </c>
-      <c r="M37" s="39">
-        <v>0</v>
-      </c>
-      <c r="N37" s="40">
+      <c r="M37" s="38">
+        <v>0</v>
+      </c>
+      <c r="N37" s="39">
         <f t="shared" si="0"/>
         <v>14351.31</v>
       </c>
-      <c r="O37" s="41">
+      <c r="O37" s="40">
         <f t="shared" si="1"/>
         <v>14782.31</v>
       </c>
-      <c r="P37" s="25">
+      <c r="P37" s="24">
         <f t="shared" si="7"/>
         <v>0.31000000000000011</v>
       </c>
@@ -5085,58 +5038,58 @@
       </c>
     </row>
     <row r="38" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="192" t="s">
+      <c r="A38" s="130" t="s">
         <v>23</v>
       </c>
-      <c r="B38" s="88">
+      <c r="B38" s="87">
         <f t="shared" si="6"/>
         <v>32</v>
       </c>
-      <c r="C38" s="88">
+      <c r="C38" s="87">
         <v>2203</v>
       </c>
-      <c r="D38" s="88" t="s">
+      <c r="D38" s="87" t="s">
         <v>98</v>
       </c>
-      <c r="E38" s="33">
+      <c r="E38" s="32">
         <v>0.57999999999999996</v>
       </c>
-      <c r="F38" s="34">
+      <c r="F38" s="33">
         <v>70047.320000000007</v>
       </c>
-      <c r="G38" s="35">
+      <c r="G38" s="34">
         <f>30737.32+72148.32</f>
         <v>102885.64000000001</v>
       </c>
-      <c r="H38" s="36"/>
-      <c r="I38" s="37">
+      <c r="H38" s="35"/>
+      <c r="I38" s="36">
         <f t="shared" si="2"/>
         <v>-32838.320000000007</v>
       </c>
-      <c r="J38" s="37">
+      <c r="J38" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K38" s="38">
+      <c r="K38" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L38" s="38">
+      <c r="L38" s="37">
         <f t="shared" si="5"/>
         <v>47189.075337599992</v>
       </c>
-      <c r="M38" s="39">
-        <v>0</v>
-      </c>
-      <c r="N38" s="40">
+      <c r="M38" s="38">
+        <v>0</v>
+      </c>
+      <c r="N38" s="39">
         <f t="shared" si="0"/>
         <v>14351.32</v>
       </c>
-      <c r="O38" s="41">
+      <c r="O38" s="40">
         <f t="shared" si="1"/>
         <v>14782.32</v>
       </c>
-      <c r="P38" s="25">
+      <c r="P38" s="24">
         <f t="shared" si="7"/>
         <v>0.32000000000000012</v>
       </c>
@@ -5145,57 +5098,57 @@
       </c>
     </row>
     <row r="39" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="192" t="s">
+      <c r="A39" s="130" t="s">
         <v>24</v>
       </c>
-      <c r="B39" s="88">
+      <c r="B39" s="87">
         <f t="shared" si="6"/>
         <v>33</v>
       </c>
-      <c r="C39" s="88">
+      <c r="C39" s="87">
         <v>2204</v>
       </c>
-      <c r="D39" s="88" t="s">
+      <c r="D39" s="87" t="s">
         <v>99</v>
       </c>
-      <c r="E39" s="33">
+      <c r="E39" s="32">
         <v>1.36</v>
       </c>
-      <c r="F39" s="34">
+      <c r="F39" s="33">
         <v>90110.33</v>
       </c>
-      <c r="G39" s="35">
+      <c r="G39" s="34">
         <v>92813.33</v>
       </c>
-      <c r="H39" s="36"/>
-      <c r="I39" s="37">
+      <c r="H39" s="35"/>
+      <c r="I39" s="36">
         <f t="shared" si="2"/>
         <v>-2703</v>
       </c>
-      <c r="J39" s="37">
+      <c r="J39" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K39" s="38">
+      <c r="K39" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L39" s="38">
+      <c r="L39" s="37">
         <f t="shared" si="5"/>
         <v>110650.2456192</v>
       </c>
-      <c r="M39" s="39">
-        <v>0</v>
-      </c>
-      <c r="N39" s="40">
+      <c r="M39" s="38">
+        <v>0</v>
+      </c>
+      <c r="N39" s="39">
         <f t="shared" si="0"/>
         <v>107947.33</v>
       </c>
-      <c r="O39" s="41">
+      <c r="O39" s="40">
         <f t="shared" si="1"/>
         <v>111185.33</v>
       </c>
-      <c r="P39" s="25">
+      <c r="P39" s="24">
         <f t="shared" si="7"/>
         <v>0.33000000000000013</v>
       </c>
@@ -5204,58 +5157,58 @@
       </c>
     </row>
     <row r="40" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="192" t="s">
+      <c r="A40" s="130" t="s">
         <v>25</v>
       </c>
-      <c r="B40" s="88">
+      <c r="B40" s="87">
         <f t="shared" si="6"/>
         <v>34</v>
       </c>
-      <c r="C40" s="88">
+      <c r="C40" s="87">
         <v>2205</v>
       </c>
-      <c r="D40" s="88" t="s">
+      <c r="D40" s="87" t="s">
         <v>98</v>
       </c>
-      <c r="E40" s="33">
+      <c r="E40" s="32">
         <v>1.67</v>
       </c>
-      <c r="F40" s="34">
+      <c r="F40" s="33">
         <v>201686.34</v>
       </c>
-      <c r="G40" s="35">
+      <c r="G40" s="34">
         <f>88502.34+207737.34</f>
         <v>296239.68</v>
       </c>
-      <c r="H40" s="36"/>
-      <c r="I40" s="37">
+      <c r="H40" s="35"/>
+      <c r="I40" s="36">
         <f t="shared" si="2"/>
         <v>-94553.34</v>
       </c>
-      <c r="J40" s="37">
+      <c r="J40" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K40" s="38">
+      <c r="K40" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L40" s="38">
+      <c r="L40" s="37">
         <f t="shared" si="5"/>
         <v>135871.99278239999</v>
       </c>
-      <c r="M40" s="39">
-        <v>0</v>
-      </c>
-      <c r="N40" s="40">
+      <c r="M40" s="38">
+        <v>0</v>
+      </c>
+      <c r="N40" s="39">
         <f t="shared" si="0"/>
         <v>41319.339999999997</v>
       </c>
-      <c r="O40" s="41">
+      <c r="O40" s="40">
         <f t="shared" si="1"/>
         <v>42559.34</v>
       </c>
-      <c r="P40" s="25">
+      <c r="P40" s="24">
         <f t="shared" si="7"/>
         <v>0.34000000000000014</v>
       </c>
@@ -5264,58 +5217,58 @@
       </c>
     </row>
     <row r="41" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="192" t="s">
+      <c r="A41" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="B41" s="88">
+      <c r="B41" s="87">
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
-      <c r="C41" s="88">
+      <c r="C41" s="87">
         <v>2206</v>
       </c>
-      <c r="D41" s="88" t="s">
+      <c r="D41" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="E41" s="33">
+      <c r="E41" s="32">
         <v>2.17</v>
       </c>
-      <c r="F41" s="34">
+      <c r="F41" s="33">
         <v>141878.35</v>
       </c>
-      <c r="G41" s="35">
+      <c r="G41" s="34">
         <f>225272.71-G42</f>
         <v>141878.34999999998</v>
       </c>
-      <c r="H41" s="36"/>
-      <c r="I41" s="37">
+      <c r="H41" s="35"/>
+      <c r="I41" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J41" s="37">
+      <c r="J41" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K41" s="38">
+      <c r="K41" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L41" s="38">
+      <c r="L41" s="37">
         <f t="shared" si="5"/>
         <v>176552.23014239999</v>
       </c>
-      <c r="M41" s="39">
-        <v>0</v>
-      </c>
-      <c r="N41" s="40">
+      <c r="M41" s="38">
+        <v>0</v>
+      </c>
+      <c r="N41" s="39">
         <f t="shared" si="0"/>
         <v>176552.35</v>
       </c>
-      <c r="O41" s="41">
+      <c r="O41" s="40">
         <f t="shared" si="1"/>
         <v>181849.35</v>
       </c>
-      <c r="P41" s="25">
+      <c r="P41" s="24">
         <f t="shared" si="7"/>
         <v>0.35000000000000014</v>
       </c>
@@ -5324,58 +5277,58 @@
       </c>
     </row>
     <row r="42" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="192" t="s">
+      <c r="A42" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="B42" s="88">
+      <c r="B42" s="87">
         <f t="shared" si="6"/>
         <v>36</v>
       </c>
-      <c r="C42" s="88">
+      <c r="C42" s="87">
         <v>2207</v>
       </c>
-      <c r="D42" s="88" t="s">
+      <c r="D42" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="E42" s="33">
+      <c r="E42" s="32">
         <v>1.23</v>
       </c>
-      <c r="F42" s="34">
+      <c r="F42" s="33">
         <v>83394.36</v>
       </c>
-      <c r="G42" s="35">
+      <c r="G42" s="34">
         <f>F42</f>
         <v>83394.36</v>
       </c>
-      <c r="H42" s="36"/>
-      <c r="I42" s="37">
+      <c r="H42" s="35"/>
+      <c r="I42" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J42" s="37">
+      <c r="J42" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K42" s="38">
+      <c r="K42" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L42" s="38">
+      <c r="L42" s="37">
         <f t="shared" si="5"/>
         <v>100073.38390559999</v>
       </c>
-      <c r="M42" s="39">
-        <v>0</v>
-      </c>
-      <c r="N42" s="40">
+      <c r="M42" s="38">
+        <v>0</v>
+      </c>
+      <c r="N42" s="39">
         <f t="shared" si="0"/>
         <v>100073.36</v>
       </c>
-      <c r="O42" s="41">
+      <c r="O42" s="40">
         <f t="shared" si="1"/>
         <v>103075.36</v>
       </c>
-      <c r="P42" s="25">
+      <c r="P42" s="24">
         <f t="shared" si="7"/>
         <v>0.36000000000000015</v>
       </c>
@@ -5384,662 +5337,662 @@
       </c>
     </row>
     <row r="43" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="192" t="s">
+      <c r="A43" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="B43" s="88">
+      <c r="B43" s="87">
         <f t="shared" si="6"/>
         <v>37</v>
       </c>
-      <c r="C43" s="88">
+      <c r="C43" s="87">
         <v>3308</v>
       </c>
-      <c r="D43" s="88" t="s">
+      <c r="D43" s="87" t="s">
         <v>123</v>
       </c>
-      <c r="E43" s="33">
+      <c r="E43" s="32">
         <v>1.23</v>
       </c>
-      <c r="F43" s="34">
+      <c r="F43" s="33">
         <v>148548.37</v>
       </c>
-      <c r="G43" s="35">
+      <c r="G43" s="34">
         <f>65185.37+83394.37</f>
         <v>148579.74</v>
       </c>
-      <c r="H43" s="36"/>
-      <c r="I43" s="37">
+      <c r="H43" s="35"/>
+      <c r="I43" s="36">
         <f t="shared" si="2"/>
         <v>-31.369999999995343</v>
       </c>
-      <c r="J43" s="37">
+      <c r="J43" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K43" s="38">
+      <c r="K43" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L43" s="38">
+      <c r="L43" s="37">
         <f t="shared" si="5"/>
         <v>100073.38390559999</v>
       </c>
-      <c r="M43" s="39">
-        <v>0</v>
-      </c>
-      <c r="N43" s="40">
+      <c r="M43" s="38">
+        <v>0</v>
+      </c>
+      <c r="N43" s="39">
         <f t="shared" si="0"/>
         <v>100042.37</v>
       </c>
-      <c r="O43" s="41">
+      <c r="O43" s="40">
         <f t="shared" si="1"/>
         <v>103043.37</v>
       </c>
-      <c r="P43" s="25">
+      <c r="P43" s="24">
         <f t="shared" si="7"/>
         <v>0.37000000000000016</v>
       </c>
-      <c r="Q43" s="75"/>
+      <c r="Q43" s="74"/>
     </row>
     <row r="44" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="192" t="s">
+      <c r="A44" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="B44" s="88">
+      <c r="B44" s="87">
         <f t="shared" si="6"/>
         <v>38</v>
       </c>
-      <c r="C44" s="88">
+      <c r="C44" s="87">
         <v>3301</v>
       </c>
-      <c r="D44" s="131" t="s">
+      <c r="D44" s="126" t="s">
         <v>124</v>
       </c>
-      <c r="E44" s="33">
+      <c r="E44" s="32">
         <v>1.36</v>
       </c>
-      <c r="F44" s="34">
+      <c r="F44" s="33">
         <v>438561.38</v>
       </c>
-      <c r="G44" s="35">
-        <v>0</v>
-      </c>
-      <c r="H44" s="36"/>
-      <c r="I44" s="37">
+      <c r="G44" s="34">
+        <v>0</v>
+      </c>
+      <c r="H44" s="35"/>
+      <c r="I44" s="36">
         <f t="shared" si="2"/>
         <v>438561.38</v>
       </c>
-      <c r="J44" s="37">
+      <c r="J44" s="36">
         <f t="shared" si="3"/>
         <v>12937.560710000002</v>
       </c>
-      <c r="K44" s="38">
+      <c r="K44" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L44" s="38">
+      <c r="L44" s="37">
         <f t="shared" si="5"/>
         <v>110650.2456192</v>
       </c>
-      <c r="M44" s="39">
-        <v>0</v>
-      </c>
-      <c r="N44" s="40">
+      <c r="M44" s="38">
+        <v>0</v>
+      </c>
+      <c r="N44" s="39">
         <f t="shared" si="0"/>
         <v>562149.38</v>
       </c>
-      <c r="O44" s="41">
+      <c r="O44" s="40">
         <f t="shared" si="1"/>
         <v>579013.38</v>
       </c>
-      <c r="P44" s="25">
+      <c r="P44" s="24">
         <f t="shared" si="7"/>
         <v>0.38000000000000017</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A45" s="192" t="s">
+      <c r="A45" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="B45" s="88">
+      <c r="B45" s="87">
         <f>B44+1</f>
         <v>39</v>
       </c>
-      <c r="C45" s="88">
+      <c r="C45" s="87">
         <v>3302</v>
       </c>
-      <c r="D45" s="88" t="s">
+      <c r="D45" s="87" t="s">
         <v>101</v>
       </c>
-      <c r="E45" s="33">
+      <c r="E45" s="32">
         <v>0.57999999999999996</v>
       </c>
-      <c r="F45" s="34">
+      <c r="F45" s="33">
         <v>39582.39</v>
       </c>
-      <c r="G45" s="35">
+      <c r="G45" s="34">
         <f>F45</f>
         <v>39582.39</v>
       </c>
-      <c r="H45" s="43"/>
-      <c r="I45" s="37">
+      <c r="H45" s="42"/>
+      <c r="I45" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J45" s="37">
+      <c r="J45" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K45" s="38">
+      <c r="K45" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L45" s="38">
+      <c r="L45" s="37">
         <f t="shared" si="5"/>
         <v>47189.075337599992</v>
       </c>
-      <c r="M45" s="39">
-        <v>0</v>
-      </c>
-      <c r="N45" s="40">
+      <c r="M45" s="38">
+        <v>0</v>
+      </c>
+      <c r="N45" s="39">
         <f t="shared" si="0"/>
         <v>47189.39</v>
       </c>
-      <c r="O45" s="41">
+      <c r="O45" s="40">
         <f t="shared" si="1"/>
         <v>48605.39</v>
       </c>
-      <c r="P45" s="25">
+      <c r="P45" s="24">
         <f t="shared" si="7"/>
         <v>0.39000000000000018</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A46" s="75"/>
-      <c r="B46" s="88">
+      <c r="A46" s="74"/>
+      <c r="B46" s="87">
         <f t="shared" ref="B46:B64" si="8">B45+1</f>
         <v>40</v>
       </c>
-      <c r="C46" s="88">
+      <c r="C46" s="87">
         <v>3303</v>
       </c>
-      <c r="D46" s="88" t="s">
+      <c r="D46" s="87" t="s">
         <v>101</v>
       </c>
-      <c r="E46" s="33">
+      <c r="E46" s="32">
         <v>0.57999999999999996</v>
       </c>
-      <c r="F46" s="34">
+      <c r="F46" s="33">
         <v>39582.400000000001</v>
       </c>
-      <c r="G46" s="35">
+      <c r="G46" s="34">
         <f>F46</f>
         <v>39582.400000000001</v>
       </c>
-      <c r="H46" s="43"/>
-      <c r="I46" s="37">
+      <c r="H46" s="42"/>
+      <c r="I46" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J46" s="37">
+      <c r="J46" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K46" s="38">
+      <c r="K46" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L46" s="38">
+      <c r="L46" s="37">
         <f t="shared" si="5"/>
         <v>47189.075337599992</v>
       </c>
-      <c r="M46" s="39">
-        <v>0</v>
-      </c>
-      <c r="N46" s="40">
+      <c r="M46" s="38">
+        <v>0</v>
+      </c>
+      <c r="N46" s="39">
         <f t="shared" si="0"/>
         <v>47189.4</v>
       </c>
-      <c r="O46" s="41">
+      <c r="O46" s="40">
         <f t="shared" si="1"/>
         <v>48605.4</v>
       </c>
-      <c r="P46" s="25">
+      <c r="P46" s="24">
         <f t="shared" si="7"/>
         <v>0.40000000000000019</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A47" s="75"/>
-      <c r="B47" s="88">
+      <c r="A47" s="74"/>
+      <c r="B47" s="214">
         <f t="shared" si="8"/>
         <v>41</v>
       </c>
-      <c r="C47" s="88">
+      <c r="C47" s="214">
         <v>3304</v>
       </c>
-      <c r="D47" s="88" t="s">
+      <c r="D47" s="214" t="s">
         <v>131</v>
       </c>
-      <c r="E47" s="33">
+      <c r="E47" s="32">
         <v>1.36</v>
       </c>
-      <c r="F47" s="34">
+      <c r="F47" s="33">
         <v>92164.41</v>
       </c>
-      <c r="G47" s="35">
+      <c r="G47" s="34">
         <v>95000</v>
       </c>
-      <c r="H47" s="43"/>
-      <c r="I47" s="37">
+      <c r="H47" s="42"/>
+      <c r="I47" s="36">
         <f t="shared" si="2"/>
         <v>-2835.5899999999965</v>
       </c>
-      <c r="J47" s="37">
+      <c r="J47" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K47" s="38">
+      <c r="K47" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L47" s="38">
+      <c r="L47" s="37">
         <f t="shared" si="5"/>
         <v>110650.2456192</v>
       </c>
-      <c r="M47" s="39">
-        <v>0</v>
-      </c>
-      <c r="N47" s="40">
+      <c r="M47" s="38">
+        <v>0</v>
+      </c>
+      <c r="N47" s="39">
         <f t="shared" si="0"/>
         <v>107815.41</v>
       </c>
-      <c r="O47" s="41">
+      <c r="O47" s="40">
         <f t="shared" si="1"/>
         <v>111049.41</v>
       </c>
-      <c r="P47" s="25">
+      <c r="P47" s="24">
         <f t="shared" si="7"/>
         <v>0.4100000000000002</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A48" s="75"/>
-      <c r="B48" s="88">
+      <c r="A48" s="74"/>
+      <c r="B48" s="87">
         <f t="shared" si="8"/>
         <v>42</v>
       </c>
-      <c r="C48" s="88">
+      <c r="C48" s="87">
         <v>3305</v>
       </c>
-      <c r="D48" s="88" t="s">
+      <c r="D48" s="87" t="s">
         <v>132</v>
       </c>
-      <c r="E48" s="33">
+      <c r="E48" s="32">
         <v>1.67</v>
       </c>
-      <c r="F48" s="34">
+      <c r="F48" s="33">
         <v>1390599.42</v>
       </c>
-      <c r="G48" s="35">
-        <v>0</v>
-      </c>
-      <c r="H48" s="43"/>
-      <c r="I48" s="37">
+      <c r="G48" s="34">
+        <v>0</v>
+      </c>
+      <c r="H48" s="42"/>
+      <c r="I48" s="36">
         <f t="shared" si="2"/>
         <v>1390599.42</v>
       </c>
-      <c r="J48" s="37">
+      <c r="J48" s="36">
         <f t="shared" si="3"/>
         <v>41022.682890000004</v>
       </c>
-      <c r="K48" s="38">
+      <c r="K48" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L48" s="38">
+      <c r="L48" s="37">
         <f t="shared" si="5"/>
         <v>135871.99278239999</v>
       </c>
-      <c r="M48" s="39">
-        <v>0</v>
-      </c>
-      <c r="N48" s="40">
+      <c r="M48" s="38">
+        <v>0</v>
+      </c>
+      <c r="N48" s="39">
         <f t="shared" si="0"/>
         <v>1567494.42</v>
       </c>
-      <c r="O48" s="41">
+      <c r="O48" s="40">
         <f t="shared" si="1"/>
         <v>1614519.42</v>
       </c>
-      <c r="P48" s="25">
+      <c r="P48" s="24">
         <f t="shared" si="7"/>
         <v>0.42000000000000021</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A49" s="75"/>
-      <c r="B49" s="88">
+      <c r="A49" s="74"/>
+      <c r="B49" s="87">
         <f t="shared" si="8"/>
         <v>43</v>
       </c>
-      <c r="C49" s="88">
+      <c r="C49" s="87">
         <v>4406</v>
       </c>
-      <c r="D49" s="88" t="s">
+      <c r="D49" s="87" t="s">
         <v>133</v>
       </c>
-      <c r="E49" s="33">
+      <c r="E49" s="32">
         <v>2.17</v>
       </c>
-      <c r="F49" s="34">
+      <c r="F49" s="33">
         <v>147127.43</v>
       </c>
-      <c r="G49" s="35">
+      <c r="G49" s="34">
         <v>151541.43</v>
       </c>
-      <c r="H49" s="43"/>
-      <c r="I49" s="37">
+      <c r="H49" s="42"/>
+      <c r="I49" s="36">
         <f t="shared" si="2"/>
         <v>-4414</v>
       </c>
-      <c r="J49" s="37">
+      <c r="J49" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K49" s="38">
+      <c r="K49" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L49" s="38">
+      <c r="L49" s="37">
         <f t="shared" si="5"/>
         <v>176552.23014239999</v>
       </c>
-      <c r="M49" s="39">
-        <v>0</v>
-      </c>
-      <c r="N49" s="40">
+      <c r="M49" s="38">
+        <v>0</v>
+      </c>
+      <c r="N49" s="39">
         <f t="shared" si="0"/>
         <v>172138.43</v>
       </c>
-      <c r="O49" s="41">
+      <c r="O49" s="40">
         <f t="shared" si="1"/>
         <v>177302.43</v>
       </c>
-      <c r="P49" s="25">
+      <c r="P49" s="24">
         <f t="shared" si="7"/>
         <v>0.43000000000000022</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A50" s="75"/>
-      <c r="B50" s="88">
+      <c r="A50" s="74"/>
+      <c r="B50" s="87">
         <f t="shared" si="8"/>
         <v>44</v>
       </c>
-      <c r="C50" s="88">
+      <c r="C50" s="87">
         <v>4407</v>
       </c>
-      <c r="D50" s="88" t="s">
+      <c r="D50" s="87" t="s">
         <v>134</v>
       </c>
-      <c r="E50" s="33">
+      <c r="E50" s="32">
         <v>1.23</v>
       </c>
-      <c r="F50" s="34">
+      <c r="F50" s="33">
         <v>85896.44</v>
       </c>
-      <c r="G50" s="35">
+      <c r="G50" s="34">
         <v>83394.44</v>
       </c>
-      <c r="H50" s="43"/>
-      <c r="I50" s="37">
+      <c r="H50" s="42"/>
+      <c r="I50" s="36">
         <f t="shared" si="2"/>
         <v>2502</v>
       </c>
-      <c r="J50" s="37">
+      <c r="J50" s="36">
         <f t="shared" si="3"/>
         <v>73.809000000000012</v>
       </c>
-      <c r="K50" s="38">
+      <c r="K50" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L50" s="38">
+      <c r="L50" s="37">
         <f t="shared" si="5"/>
         <v>100073.38390559999</v>
       </c>
-      <c r="M50" s="39">
-        <v>0</v>
-      </c>
-      <c r="N50" s="40">
+      <c r="M50" s="38">
+        <v>0</v>
+      </c>
+      <c r="N50" s="39">
         <f t="shared" si="0"/>
         <v>102649.44</v>
       </c>
-      <c r="O50" s="41">
+      <c r="O50" s="40">
         <f t="shared" si="1"/>
         <v>105728.44</v>
       </c>
-      <c r="P50" s="25">
+      <c r="P50" s="24">
         <f t="shared" si="7"/>
         <v>0.44000000000000022</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A51" s="75"/>
-      <c r="B51" s="88">
+      <c r="A51" s="74"/>
+      <c r="B51" s="87">
         <f t="shared" si="8"/>
         <v>45</v>
       </c>
-      <c r="C51" s="88">
+      <c r="C51" s="87">
         <v>4408</v>
       </c>
-      <c r="D51" s="88" t="s">
+      <c r="D51" s="87" t="s">
         <v>135</v>
       </c>
-      <c r="E51" s="33">
+      <c r="E51" s="32">
         <v>1.29</v>
       </c>
-      <c r="F51" s="34">
+      <c r="F51" s="33">
         <v>136549.45000000001</v>
       </c>
-      <c r="G51" s="35">
+      <c r="G51" s="34">
         <f>46313.46+87463+2773</f>
         <v>136549.46</v>
       </c>
-      <c r="H51" s="43"/>
-      <c r="I51" s="37">
+      <c r="H51" s="42"/>
+      <c r="I51" s="36">
         <f t="shared" si="2"/>
         <v>-9.9999999802093953E-3</v>
       </c>
-      <c r="J51" s="37">
+      <c r="J51" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K51" s="38">
+      <c r="K51" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L51" s="38">
+      <c r="L51" s="37">
         <f t="shared" si="5"/>
         <v>104955.01238879999</v>
       </c>
-      <c r="M51" s="39">
-        <v>0</v>
-      </c>
-      <c r="N51" s="40">
+      <c r="M51" s="38">
+        <v>0</v>
+      </c>
+      <c r="N51" s="39">
         <f t="shared" si="0"/>
         <v>104955.45</v>
       </c>
-      <c r="O51" s="41">
+      <c r="O51" s="40">
         <f t="shared" si="1"/>
         <v>108104.45</v>
       </c>
-      <c r="P51" s="25">
+      <c r="P51" s="24">
         <f t="shared" si="7"/>
         <v>0.45000000000000023</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A52" s="75"/>
-      <c r="B52" s="88">
+      <c r="A52" s="74"/>
+      <c r="B52" s="87">
         <f t="shared" si="8"/>
         <v>46</v>
       </c>
-      <c r="C52" s="88">
+      <c r="C52" s="87">
         <v>4401</v>
       </c>
-      <c r="D52" s="88" t="s">
+      <c r="D52" s="87" t="s">
         <v>136</v>
       </c>
-      <c r="E52" s="33">
+      <c r="E52" s="32">
         <v>1.36</v>
       </c>
-      <c r="F52" s="34">
+      <c r="F52" s="33">
         <f>46313.46+90032.46+0.54</f>
         <v>136346.46000000002</v>
       </c>
-      <c r="G52" s="35">
+      <c r="G52" s="34">
         <v>92733.46</v>
       </c>
-      <c r="H52" s="43"/>
-      <c r="I52" s="37">
+      <c r="H52" s="42"/>
+      <c r="I52" s="36">
         <f t="shared" si="2"/>
         <v>43613.000000000015</v>
       </c>
-      <c r="J52" s="37">
+      <c r="J52" s="36">
         <f t="shared" si="3"/>
         <v>1286.5835000000004</v>
       </c>
-      <c r="K52" s="38">
+      <c r="K52" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L52" s="38">
+      <c r="L52" s="37">
         <f t="shared" si="5"/>
         <v>110650.2456192</v>
       </c>
-      <c r="M52" s="39">
-        <v>0</v>
-      </c>
-      <c r="N52" s="40">
+      <c r="M52" s="38">
+        <v>0</v>
+      </c>
+      <c r="N52" s="39">
         <f t="shared" si="0"/>
         <v>155550.46</v>
       </c>
-      <c r="O52" s="41">
+      <c r="O52" s="40">
         <f t="shared" si="1"/>
         <v>160217.46</v>
       </c>
-      <c r="P52" s="25">
+      <c r="P52" s="24">
         <f t="shared" si="7"/>
         <v>0.46000000000000024</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A53" s="75"/>
-      <c r="B53" s="88">
+      <c r="A53" s="74"/>
+      <c r="B53" s="87">
         <f t="shared" si="8"/>
         <v>47</v>
       </c>
-      <c r="C53" s="88">
+      <c r="C53" s="87">
         <v>4402</v>
       </c>
-      <c r="D53" s="88" t="s">
+      <c r="D53" s="87" t="s">
         <v>137</v>
       </c>
-      <c r="E53" s="33">
+      <c r="E53" s="32">
         <v>0.57999999999999996</v>
       </c>
-      <c r="F53" s="34">
+      <c r="F53" s="33">
         <v>-1954.53</v>
       </c>
-      <c r="G53" s="35">
+      <c r="G53" s="34">
         <v>2013.53</v>
       </c>
-      <c r="H53" s="43"/>
-      <c r="I53" s="37">
+      <c r="H53" s="42"/>
+      <c r="I53" s="36">
         <f t="shared" si="2"/>
         <v>-3968.06</v>
       </c>
-      <c r="J53" s="37">
+      <c r="J53" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K53" s="38">
+      <c r="K53" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L53" s="38">
+      <c r="L53" s="37">
         <f t="shared" si="5"/>
         <v>47189.075337599992</v>
       </c>
-      <c r="M53" s="39">
-        <v>0</v>
-      </c>
-      <c r="N53" s="40">
+      <c r="M53" s="38">
+        <v>0</v>
+      </c>
+      <c r="N53" s="39">
         <f t="shared" si="0"/>
         <v>43221.47</v>
       </c>
-      <c r="O53" s="41">
+      <c r="O53" s="40">
         <f t="shared" si="1"/>
         <v>44518.47</v>
       </c>
-      <c r="P53" s="25">
+      <c r="P53" s="24">
         <f t="shared" si="7"/>
         <v>0.47000000000000025</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A54" s="75"/>
-      <c r="B54" s="88">
+      <c r="A54" s="74"/>
+      <c r="B54" s="87">
         <f t="shared" si="8"/>
         <v>48</v>
       </c>
-      <c r="C54" s="88">
+      <c r="C54" s="87">
         <v>4403</v>
       </c>
-      <c r="D54" s="88" t="s">
+      <c r="D54" s="87" t="s">
         <v>138</v>
       </c>
-      <c r="E54" s="33">
+      <c r="E54" s="32">
         <v>0.57999999999999996</v>
       </c>
-      <c r="F54" s="34">
+      <c r="F54" s="33">
         <v>33752.480000000003</v>
       </c>
-      <c r="G54" s="35">
+      <c r="G54" s="34">
         <f>F54</f>
         <v>33752.480000000003</v>
       </c>
-      <c r="H54" s="43"/>
-      <c r="I54" s="37">
+      <c r="H54" s="42"/>
+      <c r="I54" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J54" s="37">
+      <c r="J54" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K54" s="38">
+      <c r="K54" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L54" s="38">
+      <c r="L54" s="37">
         <f t="shared" si="5"/>
         <v>47189.075337599992</v>
       </c>
-      <c r="M54" s="39">
-        <v>0</v>
-      </c>
-      <c r="N54" s="40">
+      <c r="M54" s="38">
+        <v>0</v>
+      </c>
+      <c r="N54" s="39">
         <f t="shared" si="0"/>
         <v>47189.48</v>
       </c>
-      <c r="O54" s="41">
+      <c r="O54" s="40">
         <f t="shared" si="1"/>
         <v>48605.48</v>
       </c>
-      <c r="P54" s="25">
+      <c r="P54" s="24">
         <f t="shared" si="7"/>
         <v>0.48000000000000026</v>
       </c>
@@ -6048,56 +6001,56 @@
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A55" s="75"/>
-      <c r="B55" s="88">
+      <c r="A55" s="74"/>
+      <c r="B55" s="87">
         <f t="shared" si="8"/>
         <v>49</v>
       </c>
-      <c r="C55" s="88">
+      <c r="C55" s="87">
         <v>4404</v>
       </c>
-      <c r="D55" s="88" t="s">
+      <c r="D55" s="87" t="s">
         <v>138</v>
       </c>
-      <c r="E55" s="33">
+      <c r="E55" s="32">
         <v>1.36</v>
       </c>
-      <c r="F55" s="34">
+      <c r="F55" s="33">
         <v>92209.49</v>
       </c>
-      <c r="G55" s="35">
+      <c r="G55" s="34">
         <f>F55</f>
         <v>92209.49</v>
       </c>
-      <c r="H55" s="43"/>
-      <c r="I55" s="37">
+      <c r="H55" s="42"/>
+      <c r="I55" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J55" s="37">
+      <c r="J55" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K55" s="38">
+      <c r="K55" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L55" s="38">
+      <c r="L55" s="37">
         <f t="shared" si="5"/>
         <v>110650.2456192</v>
       </c>
-      <c r="M55" s="39">
-        <v>0</v>
-      </c>
-      <c r="N55" s="40">
+      <c r="M55" s="38">
+        <v>0</v>
+      </c>
+      <c r="N55" s="39">
         <f t="shared" si="0"/>
         <v>110650.49</v>
       </c>
-      <c r="O55" s="41">
+      <c r="O55" s="40">
         <f t="shared" si="1"/>
         <v>113970.49</v>
       </c>
-      <c r="P55" s="25">
+      <c r="P55" s="24">
         <f t="shared" si="7"/>
         <v>0.49000000000000027</v>
       </c>
@@ -6106,56 +6059,56 @@
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A56" s="75"/>
-      <c r="B56" s="88">
+      <c r="A56" s="74"/>
+      <c r="B56" s="87">
         <f t="shared" si="8"/>
         <v>50</v>
       </c>
-      <c r="C56" s="88">
+      <c r="C56" s="87">
         <v>4405</v>
       </c>
-      <c r="D56" s="88" t="s">
+      <c r="D56" s="87" t="s">
         <v>138</v>
       </c>
-      <c r="E56" s="33">
+      <c r="E56" s="32">
         <v>1.67</v>
       </c>
-      <c r="F56" s="34">
+      <c r="F56" s="33">
         <v>113227.5</v>
       </c>
-      <c r="G56" s="35">
+      <c r="G56" s="34">
         <f>F56</f>
         <v>113227.5</v>
       </c>
-      <c r="H56" s="43"/>
-      <c r="I56" s="37">
+      <c r="H56" s="42"/>
+      <c r="I56" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J56" s="37">
+      <c r="J56" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K56" s="38">
+      <c r="K56" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L56" s="38">
+      <c r="L56" s="37">
         <f t="shared" si="5"/>
         <v>135871.99278239999</v>
       </c>
-      <c r="M56" s="39">
-        <v>0</v>
-      </c>
-      <c r="N56" s="40">
+      <c r="M56" s="38">
+        <v>0</v>
+      </c>
+      <c r="N56" s="39">
         <f t="shared" si="0"/>
         <v>135872.5</v>
       </c>
-      <c r="O56" s="41">
+      <c r="O56" s="40">
         <f t="shared" si="1"/>
         <v>139948.5</v>
       </c>
-      <c r="P56" s="25">
+      <c r="P56" s="24">
         <f t="shared" si="7"/>
         <v>0.50000000000000022</v>
       </c>
@@ -6164,273 +6117,273 @@
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A57" s="75"/>
-      <c r="B57" s="88">
+      <c r="A57" s="74"/>
+      <c r="B57" s="87">
         <f t="shared" si="8"/>
         <v>51</v>
       </c>
-      <c r="C57" s="88">
+      <c r="C57" s="87">
         <v>5506</v>
       </c>
-      <c r="D57" s="88" t="s">
+      <c r="D57" s="87" t="s">
         <v>139</v>
       </c>
-      <c r="E57" s="33">
+      <c r="E57" s="32">
         <v>2.17</v>
       </c>
-      <c r="F57" s="34">
+      <c r="F57" s="33">
         <v>143777.51</v>
       </c>
-      <c r="G57" s="35">
+      <c r="G57" s="34">
         <v>148090.51</v>
       </c>
-      <c r="H57" s="43"/>
-      <c r="I57" s="37">
+      <c r="H57" s="42"/>
+      <c r="I57" s="36">
         <f t="shared" si="2"/>
         <v>-4313</v>
       </c>
-      <c r="J57" s="37">
+      <c r="J57" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K57" s="38">
+      <c r="K57" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L57" s="38">
+      <c r="L57" s="37">
         <f t="shared" si="5"/>
         <v>176552.23014239999</v>
       </c>
-      <c r="M57" s="39">
-        <v>0</v>
-      </c>
-      <c r="N57" s="40">
+      <c r="M57" s="38">
+        <v>0</v>
+      </c>
+      <c r="N57" s="39">
         <f t="shared" si="0"/>
         <v>172239.51</v>
       </c>
-      <c r="O57" s="41">
+      <c r="O57" s="40">
         <f t="shared" si="1"/>
         <v>177406.51</v>
       </c>
-      <c r="P57" s="25">
+      <c r="P57" s="24">
         <f t="shared" si="7"/>
         <v>0.51000000000000023</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A58" s="75"/>
-      <c r="B58" s="88">
+      <c r="A58" s="74"/>
+      <c r="B58" s="87">
         <f t="shared" si="8"/>
         <v>52</v>
       </c>
-      <c r="C58" s="88">
+      <c r="C58" s="87">
         <v>5507</v>
       </c>
-      <c r="D58" s="88" t="s">
+      <c r="D58" s="87" t="s">
         <v>140</v>
       </c>
-      <c r="E58" s="33">
+      <c r="E58" s="32">
         <v>1.79</v>
       </c>
-      <c r="F58" s="34">
+      <c r="F58" s="33">
         <v>284290.52</v>
       </c>
-      <c r="G58" s="35">
+      <c r="G58" s="34">
         <f>116000+164000+4291</f>
         <v>284291</v>
       </c>
-      <c r="H58" s="43"/>
-      <c r="I58" s="37">
+      <c r="H58" s="42"/>
+      <c r="I58" s="36">
         <f t="shared" si="2"/>
         <v>-0.47999999998137355</v>
       </c>
-      <c r="J58" s="37">
+      <c r="J58" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K58" s="38">
+      <c r="K58" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L58" s="38">
+      <c r="L58" s="37">
         <f t="shared" si="5"/>
         <v>145635.24974879998</v>
       </c>
-      <c r="M58" s="39">
-        <v>0</v>
-      </c>
-      <c r="N58" s="40">
+      <c r="M58" s="38">
+        <v>0</v>
+      </c>
+      <c r="N58" s="39">
         <f t="shared" si="0"/>
         <v>145635.51999999999</v>
       </c>
-      <c r="O58" s="41">
+      <c r="O58" s="40">
         <f t="shared" si="1"/>
         <v>150004.51999999999</v>
       </c>
-      <c r="P58" s="25">
+      <c r="P58" s="24">
         <f t="shared" si="7"/>
         <v>0.52000000000000024</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A59" s="75"/>
-      <c r="B59" s="88">
+      <c r="A59" s="74"/>
+      <c r="B59" s="87">
         <f t="shared" si="8"/>
         <v>53</v>
       </c>
-      <c r="C59" s="88">
+      <c r="C59" s="87">
         <v>5508</v>
       </c>
-      <c r="D59" s="88" t="s">
+      <c r="D59" s="87" t="s">
         <v>141</v>
       </c>
-      <c r="E59" s="33">
+      <c r="E59" s="32">
         <v>1.29</v>
       </c>
-      <c r="F59" s="34">
+      <c r="F59" s="33">
         <v>-83039.47</v>
       </c>
-      <c r="G59" s="35">
-        <v>0</v>
-      </c>
-      <c r="H59" s="43"/>
-      <c r="I59" s="37">
+      <c r="G59" s="34">
+        <v>0</v>
+      </c>
+      <c r="H59" s="42"/>
+      <c r="I59" s="36">
         <f t="shared" si="2"/>
         <v>-83039.47</v>
       </c>
-      <c r="J59" s="37">
+      <c r="J59" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K59" s="38">
+      <c r="K59" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L59" s="38">
+      <c r="L59" s="37">
         <f t="shared" si="5"/>
         <v>104955.01238879999</v>
       </c>
-      <c r="M59" s="39">
-        <v>0</v>
-      </c>
-      <c r="N59" s="40">
+      <c r="M59" s="38">
+        <v>0</v>
+      </c>
+      <c r="N59" s="39">
         <f t="shared" si="0"/>
         <v>21916.53</v>
       </c>
-      <c r="O59" s="41">
+      <c r="O59" s="40">
         <f t="shared" si="1"/>
         <v>22573.53</v>
       </c>
-      <c r="P59" s="25">
+      <c r="P59" s="24">
         <f t="shared" si="7"/>
         <v>0.53000000000000025</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A60" s="75"/>
-      <c r="B60" s="88">
+      <c r="A60" s="74"/>
+      <c r="B60" s="87">
         <f t="shared" si="8"/>
         <v>54</v>
       </c>
-      <c r="C60" s="88">
+      <c r="C60" s="87">
         <v>5501</v>
       </c>
-      <c r="D60" s="88" t="s">
+      <c r="D60" s="87" t="s">
         <v>142</v>
       </c>
-      <c r="E60" s="33">
+      <c r="E60" s="32">
         <v>1.36</v>
       </c>
-      <c r="F60" s="34">
+      <c r="F60" s="33">
         <v>88609.54</v>
       </c>
-      <c r="G60" s="35">
+      <c r="G60" s="34">
         <v>92000</v>
       </c>
-      <c r="H60" s="43"/>
-      <c r="I60" s="37">
+      <c r="H60" s="42"/>
+      <c r="I60" s="36">
         <f t="shared" si="2"/>
         <v>-3390.4600000000064</v>
       </c>
-      <c r="J60" s="37">
+      <c r="J60" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K60" s="38">
+      <c r="K60" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L60" s="38">
+      <c r="L60" s="37">
         <f t="shared" si="5"/>
         <v>110650.2456192</v>
       </c>
-      <c r="M60" s="39">
-        <v>0</v>
-      </c>
-      <c r="N60" s="40">
+      <c r="M60" s="38">
+        <v>0</v>
+      </c>
+      <c r="N60" s="39">
         <f t="shared" si="0"/>
         <v>107260.54</v>
       </c>
-      <c r="O60" s="41">
+      <c r="O60" s="40">
         <f t="shared" si="1"/>
         <v>110478.54</v>
       </c>
-      <c r="P60" s="25">
+      <c r="P60" s="24">
         <f t="shared" si="7"/>
         <v>0.54000000000000026</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A61" s="75"/>
-      <c r="B61" s="88">
+      <c r="A61" s="74"/>
+      <c r="B61" s="87">
         <f t="shared" si="8"/>
         <v>55</v>
       </c>
-      <c r="C61" s="88">
+      <c r="C61" s="87">
         <v>5503</v>
       </c>
-      <c r="D61" s="88" t="s">
+      <c r="D61" s="87" t="s">
         <v>143</v>
       </c>
-      <c r="E61" s="33">
+      <c r="E61" s="32">
         <v>0.57999999999999996</v>
       </c>
-      <c r="F61" s="34">
+      <c r="F61" s="33">
         <v>793542.55</v>
       </c>
-      <c r="G61" s="35">
+      <c r="G61" s="34">
         <f>39324+300000+600000</f>
         <v>939324</v>
       </c>
-      <c r="H61" s="43"/>
-      <c r="I61" s="37">
+      <c r="H61" s="42"/>
+      <c r="I61" s="36">
         <f t="shared" si="2"/>
         <v>-145781.44999999995</v>
       </c>
-      <c r="J61" s="37">
+      <c r="J61" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K61" s="38">
+      <c r="K61" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L61" s="38">
+      <c r="L61" s="37">
         <f t="shared" si="5"/>
         <v>47189.075337599992</v>
       </c>
-      <c r="M61" s="39">
-        <v>0</v>
-      </c>
-      <c r="N61" s="40">
+      <c r="M61" s="38">
+        <v>0</v>
+      </c>
+      <c r="N61" s="39">
         <f t="shared" si="0"/>
         <v>-98591.45</v>
       </c>
-      <c r="O61" s="41">
+      <c r="O61" s="40">
         <f t="shared" si="1"/>
         <v>-101549.45</v>
       </c>
-      <c r="P61" s="25">
+      <c r="P61" s="24">
         <f t="shared" si="7"/>
         <v>0.55000000000000027</v>
       </c>
@@ -6439,324 +6392,319 @@
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A62" s="75"/>
-      <c r="B62" s="88">
+      <c r="A62" s="74"/>
+      <c r="B62" s="87">
         <f t="shared" si="8"/>
         <v>56</v>
       </c>
-      <c r="C62" s="88">
+      <c r="C62" s="87">
         <v>5504</v>
       </c>
-      <c r="D62" s="88" t="s">
+      <c r="D62" s="87" t="s">
         <v>82</v>
       </c>
-      <c r="E62" s="33">
+      <c r="E62" s="32">
         <v>1.36</v>
       </c>
-      <c r="F62" s="34">
+      <c r="F62" s="33">
         <v>90994.559999999998</v>
       </c>
-      <c r="G62" s="35">
+      <c r="G62" s="34">
         <f>20000+71000</f>
         <v>91000</v>
       </c>
-      <c r="H62" s="43"/>
-      <c r="I62" s="37">
+      <c r="H62" s="42"/>
+      <c r="I62" s="36">
         <f t="shared" si="2"/>
         <v>-5.4400000000023283</v>
       </c>
-      <c r="J62" s="37">
+      <c r="J62" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K62" s="38">
+      <c r="K62" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L62" s="38">
+      <c r="L62" s="37">
         <f t="shared" si="5"/>
         <v>110650.2456192</v>
       </c>
-      <c r="M62" s="39">
-        <v>0</v>
-      </c>
-      <c r="N62" s="40">
+      <c r="M62" s="38">
+        <v>0</v>
+      </c>
+      <c r="N62" s="39">
         <f t="shared" si="0"/>
         <v>110645.56</v>
       </c>
-      <c r="O62" s="41">
+      <c r="O62" s="40">
         <f t="shared" si="1"/>
         <v>113964.56</v>
       </c>
-      <c r="P62" s="25">
+      <c r="P62" s="24">
         <f t="shared" si="7"/>
         <v>0.56000000000000028</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A63" s="75"/>
-      <c r="B63" s="88">
+      <c r="A63" s="74"/>
+      <c r="B63" s="87">
         <f t="shared" si="8"/>
         <v>57</v>
       </c>
-      <c r="C63" s="88">
+      <c r="C63" s="87">
         <v>5502</v>
       </c>
-      <c r="D63" s="88" t="s">
+      <c r="D63" s="87" t="s">
         <v>78</v>
       </c>
-      <c r="E63" s="33">
+      <c r="E63" s="32">
         <v>0.57999999999999996</v>
       </c>
-      <c r="F63" s="34">
+      <c r="F63" s="33">
         <v>92117.57</v>
       </c>
-      <c r="G63" s="35">
-        <v>0</v>
-      </c>
-      <c r="H63" s="43"/>
-      <c r="I63" s="37">
+      <c r="G63" s="34">
+        <v>0</v>
+      </c>
+      <c r="H63" s="42"/>
+      <c r="I63" s="36">
         <f t="shared" si="2"/>
         <v>92117.57</v>
       </c>
-      <c r="J63" s="37">
+      <c r="J63" s="36">
         <f t="shared" si="3"/>
         <v>2717.4683150000005</v>
       </c>
-      <c r="K63" s="38">
+      <c r="K63" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L63" s="38">
+      <c r="L63" s="37">
         <f t="shared" si="5"/>
         <v>47189.075337599992</v>
       </c>
-      <c r="M63" s="39">
-        <v>0</v>
-      </c>
-      <c r="N63" s="40">
+      <c r="M63" s="38">
+        <v>0</v>
+      </c>
+      <c r="N63" s="39">
         <f t="shared" si="0"/>
         <v>142024.57</v>
       </c>
-      <c r="O63" s="41">
+      <c r="O63" s="40">
         <f t="shared" si="1"/>
         <v>146285.57</v>
       </c>
-      <c r="P63" s="25">
+      <c r="P63" s="24">
         <f t="shared" si="7"/>
         <v>0.57000000000000028</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B64" s="88">
+      <c r="B64" s="87">
         <f t="shared" si="8"/>
         <v>58</v>
       </c>
-      <c r="C64" s="88">
+      <c r="C64" s="87">
         <v>5505</v>
       </c>
-      <c r="D64" s="88" t="s">
+      <c r="D64" s="87" t="s">
         <v>144</v>
       </c>
-      <c r="E64" s="33">
+      <c r="E64" s="32">
         <v>1.67</v>
       </c>
-      <c r="F64" s="34">
+      <c r="F64" s="33">
         <v>113227.58</v>
       </c>
-      <c r="G64" s="35">
-        <v>0</v>
-      </c>
-      <c r="H64" s="43"/>
-      <c r="I64" s="37">
+      <c r="G64" s="34">
+        <v>0</v>
+      </c>
+      <c r="H64" s="42"/>
+      <c r="I64" s="36">
         <f t="shared" si="2"/>
         <v>113227.58</v>
       </c>
-      <c r="J64" s="37">
+      <c r="J64" s="36">
         <f t="shared" si="3"/>
         <v>3340.2136100000002</v>
       </c>
-      <c r="K64" s="38">
+      <c r="K64" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L64" s="38">
+      <c r="L64" s="37">
         <f t="shared" si="5"/>
         <v>135871.99278239999</v>
       </c>
-      <c r="M64" s="39">
-        <v>0</v>
-      </c>
-      <c r="N64" s="40">
+      <c r="M64" s="38">
+        <v>0</v>
+      </c>
+      <c r="N64" s="39">
         <f t="shared" si="0"/>
         <v>252440.58</v>
       </c>
-      <c r="O64" s="41">
+      <c r="O64" s="40">
         <f t="shared" si="1"/>
         <v>260013.58</v>
       </c>
-      <c r="P64" s="25">
+      <c r="P64" s="24">
         <f t="shared" si="7"/>
         <v>0.58000000000000029</v>
       </c>
     </row>
     <row r="65" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B65" s="88"/>
-      <c r="C65" s="31"/>
-      <c r="D65" s="31"/>
-      <c r="E65" s="33"/>
-      <c r="F65" s="42"/>
-      <c r="G65" s="35"/>
-      <c r="H65" s="43"/>
-      <c r="I65" s="44"/>
-      <c r="J65" s="37"/>
-      <c r="K65" s="38"/>
-      <c r="L65" s="45"/>
-      <c r="M65" s="42"/>
-      <c r="N65" s="34"/>
-      <c r="O65" s="34"/>
-      <c r="P65" s="25"/>
+      <c r="B65" s="87"/>
+      <c r="C65" s="30"/>
+      <c r="D65" s="30"/>
+      <c r="E65" s="32"/>
+      <c r="F65" s="41"/>
+      <c r="G65" s="34"/>
+      <c r="H65" s="42"/>
+      <c r="I65" s="43"/>
+      <c r="J65" s="36"/>
+      <c r="K65" s="37"/>
+      <c r="L65" s="44"/>
+      <c r="M65" s="41"/>
+      <c r="N65" s="33"/>
+      <c r="O65" s="33"/>
+      <c r="P65" s="24"/>
     </row>
     <row r="66" spans="2:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="46"/>
-      <c r="C66" s="47"/>
-      <c r="D66" s="106"/>
-      <c r="E66" s="108">
+      <c r="B66" s="45"/>
+      <c r="C66" s="46"/>
+      <c r="D66" s="105"/>
+      <c r="E66" s="107">
         <f>SUM(E6:E64)</f>
         <v>99.940000000000026</v>
       </c>
-      <c r="F66" s="48">
+      <c r="F66" s="47">
         <f>SUM(F6:F64)</f>
         <v>28717845.109999999</v>
       </c>
-      <c r="G66" s="48">
+      <c r="G66" s="47">
         <f>SUM(G6:G64)</f>
         <v>7982295.1100000003</v>
       </c>
-      <c r="H66" s="107">
+      <c r="H66" s="106">
         <f t="shared" ref="H66" si="9">SUM(H6:H45)</f>
         <v>0</v>
       </c>
-      <c r="I66" s="48">
+      <c r="I66" s="47">
         <f t="shared" ref="I66:O66" si="10">SUM(I6:I64)</f>
         <v>20735549.999999996</v>
       </c>
-      <c r="J66" s="48">
+      <c r="J66" s="47">
         <f t="shared" si="10"/>
         <v>624600.80369999993</v>
       </c>
-      <c r="K66" s="48">
+      <c r="K66" s="47">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L66" s="48">
+      <c r="L66" s="47">
         <f t="shared" si="10"/>
         <v>8131165.8435167996</v>
       </c>
-      <c r="M66" s="48">
+      <c r="M66" s="47">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="N66" s="48">
+      <c r="N66" s="47">
         <f t="shared" si="10"/>
         <v>29491334.109999999</v>
       </c>
-      <c r="O66" s="48">
+      <c r="O66" s="47">
         <f t="shared" si="10"/>
         <v>30376076.109999999</v>
       </c>
     </row>
     <row r="67" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D67" s="27"/>
+      <c r="D67" s="26"/>
     </row>
     <row r="68" spans="2:16" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="69" spans="2:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D69" s="163" t="s">
+      <c r="D69" s="193" t="s">
         <v>69</v>
       </c>
-      <c r="E69" s="163"/>
-      <c r="F69" s="163"/>
-      <c r="G69" s="163"/>
-      <c r="H69" s="163"/>
-      <c r="I69" s="163"/>
-      <c r="J69" s="163"/>
-      <c r="K69" s="163"/>
-      <c r="L69" s="163"/>
-      <c r="M69" s="163"/>
-      <c r="N69" s="163"/>
+      <c r="E69" s="193"/>
+      <c r="F69" s="193"/>
+      <c r="G69" s="193"/>
+      <c r="H69" s="193"/>
+      <c r="I69" s="193"/>
+      <c r="J69" s="193"/>
+      <c r="K69" s="193"/>
+      <c r="L69" s="193"/>
+      <c r="M69" s="193"/>
+      <c r="N69" s="193"/>
     </row>
     <row r="70" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D70" s="163"/>
-      <c r="E70" s="163"/>
-      <c r="F70" s="163"/>
-      <c r="G70" s="163"/>
-      <c r="H70" s="163"/>
-      <c r="I70" s="163"/>
-      <c r="J70" s="163"/>
-      <c r="K70" s="163"/>
-      <c r="L70" s="163"/>
-      <c r="M70" s="163"/>
-      <c r="N70" s="163"/>
+      <c r="D70" s="193"/>
+      <c r="E70" s="193"/>
+      <c r="F70" s="193"/>
+      <c r="G70" s="193"/>
+      <c r="H70" s="193"/>
+      <c r="I70" s="193"/>
+      <c r="J70" s="193"/>
+      <c r="K70" s="193"/>
+      <c r="L70" s="193"/>
+      <c r="M70" s="193"/>
+      <c r="N70" s="193"/>
     </row>
     <row r="71" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D71" s="163"/>
-      <c r="E71" s="163"/>
-      <c r="F71" s="163"/>
-      <c r="G71" s="163"/>
-      <c r="H71" s="163"/>
-      <c r="I71" s="163"/>
-      <c r="J71" s="163"/>
-      <c r="K71" s="163"/>
-      <c r="L71" s="163"/>
-      <c r="M71" s="163"/>
-      <c r="N71" s="163"/>
+      <c r="D71" s="193"/>
+      <c r="E71" s="193"/>
+      <c r="F71" s="193"/>
+      <c r="G71" s="193"/>
+      <c r="H71" s="193"/>
+      <c r="I71" s="193"/>
+      <c r="J71" s="193"/>
+      <c r="K71" s="193"/>
+      <c r="L71" s="193"/>
+      <c r="M71" s="193"/>
+      <c r="N71" s="193"/>
     </row>
     <row r="72" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D72" s="163"/>
-      <c r="E72" s="163"/>
-      <c r="F72" s="163"/>
-      <c r="G72" s="163"/>
-      <c r="H72" s="163"/>
-      <c r="I72" s="163"/>
-      <c r="J72" s="163"/>
-      <c r="K72" s="163"/>
-      <c r="L72" s="163"/>
-      <c r="M72" s="163"/>
-      <c r="N72" s="163"/>
+      <c r="D72" s="193"/>
+      <c r="E72" s="193"/>
+      <c r="F72" s="193"/>
+      <c r="G72" s="193"/>
+      <c r="H72" s="193"/>
+      <c r="I72" s="193"/>
+      <c r="J72" s="193"/>
+      <c r="K72" s="193"/>
+      <c r="L72" s="193"/>
+      <c r="M72" s="193"/>
+      <c r="N72" s="193"/>
     </row>
     <row r="73" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D73" s="163"/>
-      <c r="E73" s="163"/>
-      <c r="F73" s="163"/>
-      <c r="G73" s="163"/>
-      <c r="H73" s="163"/>
-      <c r="I73" s="163"/>
-      <c r="J73" s="163"/>
-      <c r="K73" s="163"/>
-      <c r="L73" s="163"/>
-      <c r="M73" s="163"/>
-      <c r="N73" s="163"/>
+      <c r="D73" s="193"/>
+      <c r="E73" s="193"/>
+      <c r="F73" s="193"/>
+      <c r="G73" s="193"/>
+      <c r="H73" s="193"/>
+      <c r="I73" s="193"/>
+      <c r="J73" s="193"/>
+      <c r="K73" s="193"/>
+      <c r="L73" s="193"/>
+      <c r="M73" s="193"/>
+      <c r="N73" s="193"/>
     </row>
     <row r="74" spans="2:16" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D74" s="163"/>
-      <c r="E74" s="163"/>
-      <c r="F74" s="163"/>
-      <c r="G74" s="163"/>
-      <c r="H74" s="163"/>
-      <c r="I74" s="163"/>
-      <c r="J74" s="163"/>
-      <c r="K74" s="163"/>
-      <c r="L74" s="163"/>
-      <c r="M74" s="163"/>
-      <c r="N74" s="163"/>
+      <c r="D74" s="193"/>
+      <c r="E74" s="193"/>
+      <c r="F74" s="193"/>
+      <c r="G74" s="193"/>
+      <c r="H74" s="193"/>
+      <c r="I74" s="193"/>
+      <c r="J74" s="193"/>
+      <c r="K74" s="193"/>
+      <c r="L74" s="193"/>
+      <c r="M74" s="193"/>
+      <c r="N74" s="193"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
     <mergeCell ref="B1:J2"/>
     <mergeCell ref="O4:O5"/>
     <mergeCell ref="D69:N74"/>
@@ -6769,6 +6717,11 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="B3:O3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -6777,482 +6730,249 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B56D240-6D8B-4144-A545-69291A6FAA07}">
-  <dimension ref="A2:L56"/>
+  <dimension ref="C2:J32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C3" s="121" t="s">
+    <row r="2" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C3" s="120" t="s">
         <v>154</v>
       </c>
-      <c r="D3" s="122">
+      <c r="D3" s="121">
         <v>1</v>
       </c>
-      <c r="E3" s="118"/>
-      <c r="F3" s="118"/>
-      <c r="G3" s="118"/>
-      <c r="H3" s="119"/>
-    </row>
-    <row r="4" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C4" s="123" t="s">
+      <c r="E3" s="117"/>
+      <c r="F3" s="117"/>
+      <c r="G3" s="117"/>
+      <c r="H3" s="118"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+    </row>
+    <row r="4" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="122" t="s">
         <v>155</v>
       </c>
-      <c r="D4" s="124" t="s">
-        <v>166</v>
-      </c>
-      <c r="H4" s="120"/>
-      <c r="I4" s="149"/>
-      <c r="J4" s="149"/>
-    </row>
-    <row r="5" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C5" s="123"/>
-      <c r="D5" s="124"/>
-      <c r="H5" s="120"/>
-      <c r="I5" s="149"/>
-      <c r="J5" s="149"/>
-    </row>
-    <row r="6" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C6" s="181" t="s">
-        <v>167</v>
-      </c>
-      <c r="D6" s="182"/>
-      <c r="E6" s="182"/>
-      <c r="F6" s="182"/>
-      <c r="G6" s="182"/>
-      <c r="H6" s="183"/>
-      <c r="I6" s="149"/>
-      <c r="J6" s="149"/>
-    </row>
-    <row r="7" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C7" s="184"/>
-      <c r="D7" s="185"/>
-      <c r="E7" s="185"/>
-      <c r="F7" s="185"/>
-      <c r="G7" s="185"/>
-      <c r="H7" s="186"/>
-      <c r="I7" s="75"/>
-      <c r="J7" s="75"/>
-    </row>
-    <row r="8" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C8" s="187"/>
-      <c r="D8" s="188"/>
-      <c r="E8" s="188"/>
-      <c r="F8" s="188"/>
-      <c r="G8" s="188"/>
-      <c r="H8" s="189"/>
-      <c r="I8" s="75"/>
-      <c r="J8" s="75"/>
-    </row>
-    <row r="9" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C9" s="75"/>
-      <c r="D9" s="75"/>
-      <c r="E9" s="75"/>
-    </row>
-    <row r="10" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C10" s="75"/>
-      <c r="D10" s="75"/>
-    </row>
-    <row r="11" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C11" s="127" t="s">
+      <c r="D4" s="123" t="s">
+        <v>190</v>
+      </c>
+      <c r="H4" s="119"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+    </row>
+    <row r="5" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C5" s="122"/>
+      <c r="D5" s="123"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+    </row>
+    <row r="6" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C6" s="205" t="s">
+        <v>191</v>
+      </c>
+      <c r="D6" s="206"/>
+      <c r="E6" s="206"/>
+      <c r="F6" s="206"/>
+      <c r="G6" s="206"/>
+      <c r="H6" s="207"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+    </row>
+    <row r="7" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C7" s="208"/>
+      <c r="D7" s="209"/>
+      <c r="E7" s="209"/>
+      <c r="F7" s="209"/>
+      <c r="G7" s="209"/>
+      <c r="H7" s="210"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+    </row>
+    <row r="8" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="211"/>
+      <c r="D8" s="212"/>
+      <c r="E8" s="212"/>
+      <c r="F8" s="212"/>
+      <c r="G8" s="212"/>
+      <c r="H8" s="213"/>
+      <c r="I8" s="74"/>
+      <c r="J8" s="74"/>
+    </row>
+    <row r="9" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C9" s="74"/>
+      <c r="D9" s="74"/>
+      <c r="E9" s="74"/>
+    </row>
+    <row r="10" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="160" t="s">
         <v>154</v>
       </c>
-      <c r="D11" s="128">
+      <c r="D11" s="161">
         <f>D3+1</f>
         <v>2</v>
       </c>
-      <c r="E11" s="118"/>
-      <c r="F11" s="118"/>
-      <c r="G11" s="118"/>
-      <c r="H11" s="119"/>
-    </row>
-    <row r="12" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C12" s="129" t="s">
+      <c r="E11" s="117"/>
+      <c r="F11" s="117"/>
+      <c r="G11" s="117"/>
+      <c r="H11" s="118"/>
+    </row>
+    <row r="12" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="162" t="s">
         <v>155</v>
       </c>
-      <c r="D12" s="130" t="s">
-        <v>168</v>
-      </c>
-      <c r="H12" s="120"/>
-    </row>
-    <row r="13" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C13" s="129"/>
-      <c r="D13" s="130"/>
-      <c r="H13" s="120"/>
-      <c r="I13" s="149"/>
-      <c r="J13" s="149"/>
-      <c r="K13" s="149"/>
-    </row>
-    <row r="14" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C14" s="181" t="s">
-        <v>169</v>
-      </c>
-      <c r="D14" s="182"/>
-      <c r="E14" s="182"/>
-      <c r="F14" s="182"/>
-      <c r="G14" s="182"/>
-      <c r="H14" s="183"/>
-      <c r="I14" s="149"/>
-      <c r="J14" s="149"/>
-      <c r="K14" s="149"/>
-    </row>
-    <row r="15" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C15" s="184"/>
-      <c r="D15" s="185"/>
-      <c r="E15" s="185"/>
-      <c r="F15" s="185"/>
-      <c r="G15" s="185"/>
-      <c r="H15" s="186"/>
-      <c r="I15" s="149"/>
-      <c r="J15" s="149"/>
-      <c r="K15" s="149"/>
-    </row>
-    <row r="16" spans="3:11" ht="67.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C16" s="187"/>
-      <c r="D16" s="188"/>
-      <c r="E16" s="188"/>
-      <c r="F16" s="188"/>
-      <c r="G16" s="188"/>
-      <c r="H16" s="189"/>
-      <c r="I16" s="149"/>
-      <c r="J16" s="149"/>
-      <c r="K16" s="149"/>
-    </row>
-    <row r="18" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C19" s="132" t="s">
+      <c r="D12" s="163" t="s">
+        <v>193</v>
+      </c>
+      <c r="H12" s="119"/>
+    </row>
+    <row r="13" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C13" s="162"/>
+      <c r="D13" s="163" t="s">
+        <v>192</v>
+      </c>
+      <c r="H13" s="119"/>
+    </row>
+    <row r="14" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="205" t="s">
+        <v>194</v>
+      </c>
+      <c r="D14" s="206"/>
+      <c r="E14" s="206"/>
+      <c r="F14" s="206"/>
+      <c r="G14" s="206"/>
+      <c r="H14" s="207"/>
+    </row>
+    <row r="15" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C15" s="208"/>
+      <c r="D15" s="209"/>
+      <c r="E15" s="209"/>
+      <c r="F15" s="209"/>
+      <c r="G15" s="209"/>
+      <c r="H15" s="210"/>
+    </row>
+    <row r="16" spans="3:10" ht="117" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C16" s="211"/>
+      <c r="D16" s="212"/>
+      <c r="E16" s="212"/>
+      <c r="F16" s="212"/>
+      <c r="G16" s="212"/>
+      <c r="H16" s="213"/>
+    </row>
+    <row r="18" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C19" s="165" t="s">
         <v>154</v>
       </c>
-      <c r="D19" s="133">
+      <c r="D19" s="166">
         <f>D11+1</f>
         <v>3</v>
       </c>
-      <c r="E19" s="118"/>
-      <c r="F19" s="118"/>
-      <c r="G19" s="118"/>
-      <c r="H19" s="119"/>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C20" s="134" t="s">
+      <c r="E19" s="117"/>
+      <c r="F19" s="117"/>
+      <c r="G19" s="117"/>
+      <c r="H19" s="118"/>
+    </row>
+    <row r="20" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C20" s="167" t="s">
         <v>155</v>
       </c>
-      <c r="D20" s="135" t="s">
-        <v>170</v>
-      </c>
-      <c r="H20" s="120"/>
-    </row>
-    <row r="21" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="134"/>
-      <c r="D21" s="135"/>
-      <c r="H21" s="120"/>
-      <c r="I21" s="149"/>
-      <c r="J21" s="149"/>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C22" s="181" t="s">
-        <v>171</v>
-      </c>
-      <c r="D22" s="182"/>
-      <c r="E22" s="182"/>
-      <c r="F22" s="182"/>
-      <c r="G22" s="182"/>
-      <c r="H22" s="183"/>
-      <c r="I22" s="149"/>
-      <c r="J22" s="149"/>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C23" s="184"/>
-      <c r="D23" s="185"/>
-      <c r="E23" s="185"/>
-      <c r="F23" s="185"/>
-      <c r="G23" s="185"/>
-      <c r="H23" s="186"/>
-      <c r="I23" s="149"/>
-      <c r="J23" s="149"/>
-    </row>
-    <row r="24" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C24" s="187"/>
-      <c r="D24" s="188"/>
-      <c r="E24" s="188"/>
-      <c r="F24" s="188"/>
-      <c r="G24" s="188"/>
-      <c r="H24" s="189"/>
-    </row>
-    <row r="26" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C27" s="136" t="s">
+      <c r="D20" s="168">
+        <v>22</v>
+      </c>
+      <c r="H20" s="119"/>
+    </row>
+    <row r="21" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C21" s="167"/>
+      <c r="D21" s="168"/>
+      <c r="H21" s="119"/>
+    </row>
+    <row r="22" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C22" s="205" t="s">
+        <v>195</v>
+      </c>
+      <c r="D22" s="206"/>
+      <c r="E22" s="206"/>
+      <c r="F22" s="206"/>
+      <c r="G22" s="206"/>
+      <c r="H22" s="207"/>
+    </row>
+    <row r="23" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C23" s="208"/>
+      <c r="D23" s="209"/>
+      <c r="E23" s="209"/>
+      <c r="F23" s="209"/>
+      <c r="G23" s="209"/>
+      <c r="H23" s="210"/>
+    </row>
+    <row r="24" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C24" s="211"/>
+      <c r="D24" s="212"/>
+      <c r="E24" s="212"/>
+      <c r="F24" s="212"/>
+      <c r="G24" s="212"/>
+      <c r="H24" s="213"/>
+    </row>
+    <row r="26" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="27" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C27" s="215" t="s">
         <v>154</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="216">
         <f>D19+1</f>
         <v>4</v>
       </c>
-      <c r="E27" s="118"/>
-      <c r="F27" s="118"/>
-      <c r="G27" s="118"/>
-      <c r="H27" s="119"/>
-    </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C28" s="137" t="s">
+      <c r="E27" s="117"/>
+      <c r="F27" s="117"/>
+      <c r="G27" s="117"/>
+      <c r="H27" s="118"/>
+    </row>
+    <row r="28" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C28" s="217" t="s">
         <v>155</v>
       </c>
-      <c r="D28" s="138" t="s">
-        <v>172</v>
-      </c>
-      <c r="H28" s="120"/>
-      <c r="I28" s="149"/>
-      <c r="J28" s="149"/>
-    </row>
-    <row r="29" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C29" s="137"/>
-      <c r="D29" s="138"/>
-      <c r="H29" s="120"/>
-      <c r="I29" s="149"/>
-      <c r="J29" s="149"/>
-    </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C30" s="181" t="s">
-        <v>173</v>
-      </c>
-      <c r="D30" s="182"/>
-      <c r="E30" s="182"/>
-      <c r="F30" s="182"/>
-      <c r="G30" s="182"/>
-      <c r="H30" s="183"/>
-      <c r="I30" s="149"/>
-      <c r="J30" s="149"/>
-    </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C31" s="184"/>
-      <c r="D31" s="185"/>
-      <c r="E31" s="185"/>
-      <c r="F31" s="185"/>
-      <c r="G31" s="185"/>
-      <c r="H31" s="186"/>
-      <c r="I31" s="149"/>
-      <c r="J31" s="149"/>
-    </row>
-    <row r="32" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C32" s="187"/>
-      <c r="D32" s="188"/>
-      <c r="E32" s="188"/>
-      <c r="F32" s="188"/>
-      <c r="G32" s="188"/>
-      <c r="H32" s="189"/>
-    </row>
-    <row r="34" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C35" s="127" t="s">
-        <v>154</v>
-      </c>
-      <c r="D35" s="128">
-        <f>D27+1</f>
-        <v>5</v>
-      </c>
-      <c r="E35" s="118"/>
-      <c r="F35" s="118"/>
-      <c r="G35" s="118"/>
-      <c r="H35" s="119"/>
-      <c r="I35" s="190" t="s">
-        <v>176</v>
-      </c>
-      <c r="J35" s="191"/>
-      <c r="K35" s="191"/>
-      <c r="L35" s="191"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C36" s="129" t="s">
-        <v>155</v>
-      </c>
-      <c r="D36" s="130" t="s">
-        <v>174</v>
-      </c>
-      <c r="H36" s="120"/>
-      <c r="I36" s="190"/>
-      <c r="J36" s="191"/>
-      <c r="K36" s="191"/>
-      <c r="L36" s="191"/>
-    </row>
-    <row r="37" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C37" s="129"/>
-      <c r="D37" s="130"/>
-      <c r="H37" s="120"/>
-      <c r="I37" s="190"/>
-      <c r="J37" s="191"/>
-      <c r="K37" s="191"/>
-      <c r="L37" s="191"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C38" s="181" t="s">
-        <v>175</v>
-      </c>
-      <c r="D38" s="182"/>
-      <c r="E38" s="182"/>
-      <c r="F38" s="182"/>
-      <c r="G38" s="182"/>
-      <c r="H38" s="183"/>
-      <c r="I38" s="190"/>
-      <c r="J38" s="191"/>
-      <c r="K38" s="191"/>
-      <c r="L38" s="191"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C39" s="184"/>
-      <c r="D39" s="185"/>
-      <c r="E39" s="185"/>
-      <c r="F39" s="185"/>
-      <c r="G39" s="185"/>
-      <c r="H39" s="186"/>
-      <c r="I39" s="190"/>
-      <c r="J39" s="191"/>
-      <c r="K39" s="191"/>
-      <c r="L39" s="191"/>
-    </row>
-    <row r="40" spans="1:12" ht="34.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C40" s="187"/>
-      <c r="D40" s="188"/>
-      <c r="E40" s="188"/>
-      <c r="F40" s="188"/>
-      <c r="G40" s="188"/>
-      <c r="H40" s="189"/>
-      <c r="I40" s="190"/>
-      <c r="J40" s="191"/>
-      <c r="K40" s="191"/>
-      <c r="L40" s="191"/>
-    </row>
-    <row r="42" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="95"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C43" s="139" t="s">
-        <v>154</v>
-      </c>
-      <c r="D43" s="140">
-        <f>D35+1</f>
-        <v>6</v>
-      </c>
-      <c r="E43" s="118"/>
-      <c r="F43" s="118"/>
-      <c r="G43" s="118"/>
-      <c r="H43" s="119"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C44" s="141" t="s">
-        <v>155</v>
-      </c>
-      <c r="D44" s="142" t="s">
-        <v>177</v>
-      </c>
-      <c r="H44" s="120"/>
-      <c r="I44" s="149"/>
-      <c r="J44" s="149"/>
-    </row>
-    <row r="45" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C45" s="141"/>
-      <c r="D45" s="142"/>
-      <c r="H45" s="120"/>
-      <c r="I45" s="149"/>
-      <c r="J45" s="149"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C46" s="181" t="s">
-        <v>178</v>
-      </c>
-      <c r="D46" s="182"/>
-      <c r="E46" s="182"/>
-      <c r="F46" s="182"/>
-      <c r="G46" s="182"/>
-      <c r="H46" s="183"/>
-      <c r="I46" s="149"/>
-      <c r="J46" s="149"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C47" s="184"/>
-      <c r="D47" s="185"/>
-      <c r="E47" s="185"/>
-      <c r="F47" s="185"/>
-      <c r="G47" s="185"/>
-      <c r="H47" s="186"/>
-      <c r="I47" s="149"/>
-      <c r="J47" s="149"/>
-    </row>
-    <row r="48" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C48" s="187"/>
-      <c r="D48" s="188"/>
-      <c r="E48" s="188"/>
-      <c r="F48" s="188"/>
-      <c r="G48" s="188"/>
-      <c r="H48" s="189"/>
-    </row>
-    <row r="50" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="51" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C51" s="143" t="s">
-        <v>154</v>
-      </c>
-      <c r="D51" s="144">
-        <f>D43+1</f>
-        <v>7</v>
-      </c>
-      <c r="E51" s="118"/>
-      <c r="F51" s="118"/>
-      <c r="G51" s="118"/>
-      <c r="H51" s="119"/>
-    </row>
-    <row r="52" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C52" s="145" t="s">
-        <v>155</v>
-      </c>
-      <c r="D52" s="146" t="s">
-        <v>177</v>
-      </c>
-      <c r="H52" s="120"/>
-    </row>
-    <row r="53" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C53" s="145"/>
-      <c r="D53" s="146"/>
-      <c r="H53" s="120"/>
-    </row>
-    <row r="54" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C54" s="181" t="s">
-        <v>180</v>
-      </c>
-      <c r="D54" s="182"/>
-      <c r="E54" s="182"/>
-      <c r="F54" s="182"/>
-      <c r="G54" s="182"/>
-      <c r="H54" s="183"/>
-      <c r="I54" s="149"/>
-      <c r="J54" s="149"/>
-    </row>
-    <row r="55" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C55" s="184"/>
-      <c r="D55" s="185"/>
-      <c r="E55" s="185"/>
-      <c r="F55" s="185"/>
-      <c r="G55" s="185"/>
-      <c r="H55" s="186"/>
-      <c r="I55" s="149"/>
-      <c r="J55" s="149"/>
-    </row>
-    <row r="56" spans="3:10" ht="67.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C56" s="187"/>
-      <c r="D56" s="188"/>
-      <c r="E56" s="188"/>
-      <c r="F56" s="188"/>
-      <c r="G56" s="188"/>
-      <c r="H56" s="189"/>
-      <c r="I56" s="149"/>
-      <c r="J56" s="149"/>
+      <c r="D28" s="129">
+        <v>41</v>
+      </c>
+      <c r="H28" s="119"/>
+    </row>
+    <row r="29" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C29" s="217"/>
+      <c r="D29" s="129"/>
+      <c r="H29" s="119"/>
+    </row>
+    <row r="30" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C30" s="205" t="s">
+        <v>196</v>
+      </c>
+      <c r="D30" s="206"/>
+      <c r="E30" s="206"/>
+      <c r="F30" s="206"/>
+      <c r="G30" s="206"/>
+      <c r="H30" s="207"/>
+    </row>
+    <row r="31" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C31" s="208"/>
+      <c r="D31" s="209"/>
+      <c r="E31" s="209"/>
+      <c r="F31" s="209"/>
+      <c r="G31" s="209"/>
+      <c r="H31" s="210"/>
+    </row>
+    <row r="32" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C32" s="211"/>
+      <c r="D32" s="212"/>
+      <c r="E32" s="212"/>
+      <c r="F32" s="212"/>
+      <c r="G32" s="212"/>
+      <c r="H32" s="213"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="C54:H56"/>
-    <mergeCell ref="I35:L40"/>
-    <mergeCell ref="C46:H48"/>
+  <mergeCells count="4">
     <mergeCell ref="C6:H8"/>
     <mergeCell ref="C14:H16"/>
     <mergeCell ref="C22:H24"/>
     <mergeCell ref="C30:H32"/>
-    <mergeCell ref="C38:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026/GALERIA MITRE/Junio/Junio MITRE.xlsx
+++ b/2026/GALERIA MITRE/Junio/Junio MITRE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GALERIA MITRE\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D846D8-46D4-4D02-94C9-4BC8B06DC054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0417D70-2E5F-44D2-8BD5-07AFB0ED6F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="199">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -620,6 +620,12 @@
   </si>
   <si>
     <t>Deposito  $ 112.000,00 abonado el día 08 de julio de 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> local 16 Atanes mikaela Galería Monumenta pago $170.000 20/07</t>
+  </si>
+  <si>
+    <t>L 16</t>
   </si>
 </sst>
 </file>
@@ -802,7 +808,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -884,6 +890,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1247,7 +1259,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="218">
+  <cellXfs count="223">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1481,145 +1493,150 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2046,7 +2063,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="63"/>
-      <c r="B9" s="172" t="s">
+      <c r="B9" s="182" t="s">
         <v>166</v>
       </c>
       <c r="C9" s="63"/>
@@ -2054,13 +2071,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="63"/>
-      <c r="B10" s="172"/>
+      <c r="B10" s="182"/>
       <c r="C10" s="63"/>
       <c r="D10" s="63"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="63"/>
-      <c r="B11" s="172"/>
+      <c r="B11" s="182"/>
       <c r="C11" s="63"/>
       <c r="D11" s="63"/>
     </row>
@@ -2143,10 +2160,10 @@
       <c r="F22" s="129"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="170" t="s">
+      <c r="A23" s="177" t="s">
         <v>167</v>
       </c>
-      <c r="B23" s="171"/>
+      <c r="B23" s="178"/>
       <c r="C23" s="82">
         <v>1231605.7</v>
       </c>
@@ -2193,10 +2210,10 @@
       <c r="F26" s="129"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="170" t="s">
+      <c r="A27" s="177" t="s">
         <v>168</v>
       </c>
-      <c r="B27" s="171"/>
+      <c r="B27" s="178"/>
       <c r="C27" s="82">
         <v>815681.8</v>
       </c>
@@ -2285,10 +2302,10 @@
       <c r="F35" s="4"/>
     </row>
     <row r="36" spans="1:7" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="170" t="s">
+      <c r="A36" s="177" t="s">
         <v>183</v>
       </c>
-      <c r="B36" s="171"/>
+      <c r="B36" s="178"/>
       <c r="C36" s="82">
         <v>710000</v>
       </c>
@@ -2341,10 +2358,10 @@
       <c r="D40" s="31"/>
     </row>
     <row r="41" spans="1:7" s="19" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="170" t="s">
+      <c r="A41" s="177" t="s">
         <v>130</v>
       </c>
-      <c r="B41" s="171"/>
+      <c r="B41" s="178"/>
       <c r="C41" s="96">
         <v>111379</v>
       </c>
@@ -2383,10 +2400,10 @@
       <c r="F44" s="74"/>
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="170" t="s">
+      <c r="A45" s="177" t="s">
         <v>181</v>
       </c>
-      <c r="B45" s="171"/>
+      <c r="B45" s="178"/>
       <c r="C45" s="100">
         <v>11596.99</v>
       </c>
@@ -2396,10 +2413,10 @@
       <c r="F45" s="74"/>
     </row>
     <row r="46" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="170" t="s">
+      <c r="A46" s="177" t="s">
         <v>129</v>
       </c>
-      <c r="B46" s="171"/>
+      <c r="B46" s="178"/>
       <c r="C46" s="100">
         <v>11930.96</v>
       </c>
@@ -2552,10 +2569,10 @@
       <c r="D58" s="55"/>
     </row>
     <row r="59" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="177" t="s">
+      <c r="A59" s="179" t="s">
         <v>156</v>
       </c>
-      <c r="B59" s="178"/>
+      <c r="B59" s="180"/>
       <c r="C59" s="85">
         <v>202000</v>
       </c>
@@ -2564,10 +2581,10 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="177" t="s">
+      <c r="A60" s="179" t="s">
         <v>176</v>
       </c>
-      <c r="B60" s="178"/>
+      <c r="B60" s="180"/>
       <c r="C60" s="85">
         <v>229900</v>
       </c>
@@ -2576,10 +2593,10 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="170" t="s">
+      <c r="A61" s="177" t="s">
         <v>178</v>
       </c>
-      <c r="B61" s="171"/>
+      <c r="B61" s="178"/>
       <c r="C61" s="85">
         <v>35000</v>
       </c>
@@ -2590,10 +2607,10 @@
       <c r="F61" s="24"/>
     </row>
     <row r="62" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="177" t="s">
+      <c r="A62" s="179" t="s">
         <v>179</v>
       </c>
-      <c r="B62" s="178"/>
+      <c r="B62" s="180"/>
       <c r="C62" s="85">
         <v>9395</v>
       </c>
@@ -2607,10 +2624,10 @@
       <c r="F62" s="24"/>
     </row>
     <row r="63" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="177" t="s">
+      <c r="A63" s="179" t="s">
         <v>171</v>
       </c>
-      <c r="B63" s="178"/>
+      <c r="B63" s="180"/>
       <c r="C63" s="85">
         <v>18300</v>
       </c>
@@ -2668,10 +2685,10 @@
       <c r="D67" s="55"/>
     </row>
     <row r="68" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="170" t="s">
+      <c r="A68" s="177" t="s">
         <v>73</v>
       </c>
-      <c r="B68" s="171"/>
+      <c r="B68" s="178"/>
       <c r="C68" s="85">
         <v>60000</v>
       </c>
@@ -2758,14 +2775,14 @@
       <c r="D77" s="68"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="170"/>
-      <c r="B78" s="171"/>
+      <c r="A78" s="177"/>
+      <c r="B78" s="178"/>
       <c r="C78" s="56"/>
       <c r="D78" s="54"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="170"/>
-      <c r="B79" s="171"/>
+      <c r="A79" s="177"/>
+      <c r="B79" s="178"/>
       <c r="C79" s="56"/>
       <c r="D79" s="54"/>
     </row>
@@ -2981,14 +2998,14 @@
       <c r="D108" s="99"/>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="169" t="s">
+      <c r="A109" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="B109" s="169"/>
+      <c r="B109" s="181"/>
     </row>
     <row r="110" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="169"/>
-      <c r="B110" s="169"/>
+      <c r="A110" s="181"/>
+      <c r="B110" s="181"/>
     </row>
     <row r="111" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="69" t="s">
@@ -3028,6 +3045,12 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A109:B110"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A14:D17"/>
     <mergeCell ref="A72:C72"/>
@@ -3041,12 +3064,6 @@
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A109:B110"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3081,17 +3098,17 @@
   <sheetData>
     <row r="1" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
-      <c r="B1" s="185" t="s">
+      <c r="B1" s="183" t="s">
         <v>151</v>
       </c>
-      <c r="C1" s="186"/>
-      <c r="D1" s="186"/>
-      <c r="E1" s="186"/>
-      <c r="F1" s="186"/>
-      <c r="G1" s="186"/>
-      <c r="H1" s="186"/>
-      <c r="I1" s="186"/>
-      <c r="J1" s="187"/>
+      <c r="C1" s="184"/>
+      <c r="D1" s="184"/>
+      <c r="E1" s="184"/>
+      <c r="F1" s="184"/>
+      <c r="G1" s="184"/>
+      <c r="H1" s="184"/>
+      <c r="I1" s="184"/>
+      <c r="J1" s="185"/>
       <c r="K1" s="111" t="s">
         <v>4</v>
       </c>
@@ -3109,15 +3126,15 @@
     </row>
     <row r="2" spans="1:18" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="188"/>
-      <c r="C2" s="189"/>
-      <c r="D2" s="189"/>
-      <c r="E2" s="189"/>
-      <c r="F2" s="189"/>
-      <c r="G2" s="189"/>
-      <c r="H2" s="189"/>
-      <c r="I2" s="189"/>
-      <c r="J2" s="190"/>
+      <c r="B2" s="186"/>
+      <c r="C2" s="187"/>
+      <c r="D2" s="187"/>
+      <c r="E2" s="187"/>
+      <c r="F2" s="187"/>
+      <c r="G2" s="187"/>
+      <c r="H2" s="187"/>
+      <c r="I2" s="187"/>
+      <c r="J2" s="188"/>
       <c r="K2" s="113" t="s">
         <v>63</v>
       </c>
@@ -3148,40 +3165,40 @@
       <c r="O3" s="204"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="179" t="s">
+      <c r="A4" s="205" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="181" t="s">
+      <c r="B4" s="207" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="183" t="s">
+      <c r="C4" s="192" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="183" t="s">
+      <c r="D4" s="192" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="183" t="s">
+      <c r="E4" s="192" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="183" t="s">
+      <c r="F4" s="192" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="183" t="s">
+      <c r="G4" s="192" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="183" t="s">
+      <c r="H4" s="192" t="s">
         <v>47</v>
       </c>
       <c r="I4" s="197" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="195" t="s">
+      <c r="J4" s="194" t="s">
         <v>46</v>
       </c>
-      <c r="K4" s="195" t="s">
+      <c r="K4" s="194" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="195" t="s">
+      <c r="L4" s="194" t="s">
         <v>45</v>
       </c>
       <c r="M4" s="200" t="s">
@@ -3190,30 +3207,30 @@
       <c r="N4" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="O4" s="191" t="s">
+      <c r="O4" s="189" t="s">
         <v>56</v>
       </c>
       <c r="R4" s="24"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="180"/>
-      <c r="B5" s="182"/>
-      <c r="C5" s="184"/>
-      <c r="D5" s="184"/>
-      <c r="E5" s="184"/>
-      <c r="F5" s="184"/>
-      <c r="G5" s="184"/>
-      <c r="H5" s="194"/>
+      <c r="A5" s="206"/>
+      <c r="B5" s="208"/>
+      <c r="C5" s="196"/>
+      <c r="D5" s="196"/>
+      <c r="E5" s="196"/>
+      <c r="F5" s="196"/>
+      <c r="G5" s="196"/>
+      <c r="H5" s="193"/>
       <c r="I5" s="198"/>
-      <c r="J5" s="196"/>
+      <c r="J5" s="195"/>
       <c r="K5" s="199"/>
-      <c r="L5" s="196"/>
+      <c r="L5" s="195"/>
       <c r="M5" s="201"/>
       <c r="N5" s="28" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 17/07</v>
       </c>
-      <c r="O5" s="192"/>
+      <c r="O5" s="190"/>
     </row>
     <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="130" t="s">
@@ -4122,14 +4139,14 @@
     </row>
     <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="130"/>
-      <c r="B22" s="87">
+      <c r="B22" s="222">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="C22" s="87" t="s">
+      <c r="C22" s="222" t="s">
         <v>118</v>
       </c>
-      <c r="D22" s="87" t="s">
+      <c r="D22" s="222" t="s">
         <v>87</v>
       </c>
       <c r="E22" s="32">
@@ -5564,14 +5581,14 @@
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" s="74"/>
-      <c r="B47" s="214">
+      <c r="B47" s="169">
         <f t="shared" si="8"/>
         <v>41</v>
       </c>
-      <c r="C47" s="214">
+      <c r="C47" s="169">
         <v>3304</v>
       </c>
-      <c r="D47" s="214" t="s">
+      <c r="D47" s="169" t="s">
         <v>131</v>
       </c>
       <c r="E47" s="32">
@@ -6624,87 +6641,92 @@
     </row>
     <row r="68" spans="2:16" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="69" spans="2:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D69" s="193" t="s">
+      <c r="D69" s="191" t="s">
         <v>69</v>
       </c>
-      <c r="E69" s="193"/>
-      <c r="F69" s="193"/>
-      <c r="G69" s="193"/>
-      <c r="H69" s="193"/>
-      <c r="I69" s="193"/>
-      <c r="J69" s="193"/>
-      <c r="K69" s="193"/>
-      <c r="L69" s="193"/>
-      <c r="M69" s="193"/>
-      <c r="N69" s="193"/>
+      <c r="E69" s="191"/>
+      <c r="F69" s="191"/>
+      <c r="G69" s="191"/>
+      <c r="H69" s="191"/>
+      <c r="I69" s="191"/>
+      <c r="J69" s="191"/>
+      <c r="K69" s="191"/>
+      <c r="L69" s="191"/>
+      <c r="M69" s="191"/>
+      <c r="N69" s="191"/>
     </row>
     <row r="70" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D70" s="193"/>
-      <c r="E70" s="193"/>
-      <c r="F70" s="193"/>
-      <c r="G70" s="193"/>
-      <c r="H70" s="193"/>
-      <c r="I70" s="193"/>
-      <c r="J70" s="193"/>
-      <c r="K70" s="193"/>
-      <c r="L70" s="193"/>
-      <c r="M70" s="193"/>
-      <c r="N70" s="193"/>
+      <c r="D70" s="191"/>
+      <c r="E70" s="191"/>
+      <c r="F70" s="191"/>
+      <c r="G70" s="191"/>
+      <c r="H70" s="191"/>
+      <c r="I70" s="191"/>
+      <c r="J70" s="191"/>
+      <c r="K70" s="191"/>
+      <c r="L70" s="191"/>
+      <c r="M70" s="191"/>
+      <c r="N70" s="191"/>
     </row>
     <row r="71" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D71" s="193"/>
-      <c r="E71" s="193"/>
-      <c r="F71" s="193"/>
-      <c r="G71" s="193"/>
-      <c r="H71" s="193"/>
-      <c r="I71" s="193"/>
-      <c r="J71" s="193"/>
-      <c r="K71" s="193"/>
-      <c r="L71" s="193"/>
-      <c r="M71" s="193"/>
-      <c r="N71" s="193"/>
+      <c r="D71" s="191"/>
+      <c r="E71" s="191"/>
+      <c r="F71" s="191"/>
+      <c r="G71" s="191"/>
+      <c r="H71" s="191"/>
+      <c r="I71" s="191"/>
+      <c r="J71" s="191"/>
+      <c r="K71" s="191"/>
+      <c r="L71" s="191"/>
+      <c r="M71" s="191"/>
+      <c r="N71" s="191"/>
     </row>
     <row r="72" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D72" s="193"/>
-      <c r="E72" s="193"/>
-      <c r="F72" s="193"/>
-      <c r="G72" s="193"/>
-      <c r="H72" s="193"/>
-      <c r="I72" s="193"/>
-      <c r="J72" s="193"/>
-      <c r="K72" s="193"/>
-      <c r="L72" s="193"/>
-      <c r="M72" s="193"/>
-      <c r="N72" s="193"/>
+      <c r="D72" s="191"/>
+      <c r="E72" s="191"/>
+      <c r="F72" s="191"/>
+      <c r="G72" s="191"/>
+      <c r="H72" s="191"/>
+      <c r="I72" s="191"/>
+      <c r="J72" s="191"/>
+      <c r="K72" s="191"/>
+      <c r="L72" s="191"/>
+      <c r="M72" s="191"/>
+      <c r="N72" s="191"/>
     </row>
     <row r="73" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D73" s="193"/>
-      <c r="E73" s="193"/>
-      <c r="F73" s="193"/>
-      <c r="G73" s="193"/>
-      <c r="H73" s="193"/>
-      <c r="I73" s="193"/>
-      <c r="J73" s="193"/>
-      <c r="K73" s="193"/>
-      <c r="L73" s="193"/>
-      <c r="M73" s="193"/>
-      <c r="N73" s="193"/>
+      <c r="D73" s="191"/>
+      <c r="E73" s="191"/>
+      <c r="F73" s="191"/>
+      <c r="G73" s="191"/>
+      <c r="H73" s="191"/>
+      <c r="I73" s="191"/>
+      <c r="J73" s="191"/>
+      <c r="K73" s="191"/>
+      <c r="L73" s="191"/>
+      <c r="M73" s="191"/>
+      <c r="N73" s="191"/>
     </row>
     <row r="74" spans="2:16" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D74" s="193"/>
-      <c r="E74" s="193"/>
-      <c r="F74" s="193"/>
-      <c r="G74" s="193"/>
-      <c r="H74" s="193"/>
-      <c r="I74" s="193"/>
-      <c r="J74" s="193"/>
-      <c r="K74" s="193"/>
-      <c r="L74" s="193"/>
-      <c r="M74" s="193"/>
-      <c r="N74" s="193"/>
+      <c r="D74" s="191"/>
+      <c r="E74" s="191"/>
+      <c r="F74" s="191"/>
+      <c r="G74" s="191"/>
+      <c r="H74" s="191"/>
+      <c r="I74" s="191"/>
+      <c r="J74" s="191"/>
+      <c r="K74" s="191"/>
+      <c r="L74" s="191"/>
+      <c r="M74" s="191"/>
+      <c r="N74" s="191"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
     <mergeCell ref="B1:J2"/>
     <mergeCell ref="O4:O5"/>
     <mergeCell ref="D69:N74"/>
@@ -6717,11 +6739,6 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="B3:O3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -6730,7 +6747,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B56D240-6D8B-4144-A545-69291A6FAA07}">
-  <dimension ref="C2:J32"/>
+  <dimension ref="C2:J40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -6767,34 +6784,34 @@
       <c r="J5" s="23"/>
     </row>
     <row r="6" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C6" s="205" t="s">
+      <c r="C6" s="209" t="s">
         <v>191</v>
       </c>
-      <c r="D6" s="206"/>
-      <c r="E6" s="206"/>
-      <c r="F6" s="206"/>
-      <c r="G6" s="206"/>
-      <c r="H6" s="207"/>
+      <c r="D6" s="210"/>
+      <c r="E6" s="210"/>
+      <c r="F6" s="210"/>
+      <c r="G6" s="210"/>
+      <c r="H6" s="211"/>
       <c r="I6" s="23"/>
       <c r="J6" s="23"/>
     </row>
     <row r="7" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C7" s="208"/>
-      <c r="D7" s="209"/>
-      <c r="E7" s="209"/>
-      <c r="F7" s="209"/>
-      <c r="G7" s="209"/>
-      <c r="H7" s="210"/>
+      <c r="C7" s="212"/>
+      <c r="D7" s="213"/>
+      <c r="E7" s="213"/>
+      <c r="F7" s="213"/>
+      <c r="G7" s="213"/>
+      <c r="H7" s="214"/>
       <c r="I7" s="23"/>
       <c r="J7" s="23"/>
     </row>
     <row r="8" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C8" s="211"/>
-      <c r="D8" s="212"/>
-      <c r="E8" s="212"/>
-      <c r="F8" s="212"/>
-      <c r="G8" s="212"/>
-      <c r="H8" s="213"/>
+      <c r="C8" s="215"/>
+      <c r="D8" s="216"/>
+      <c r="E8" s="216"/>
+      <c r="F8" s="216"/>
+      <c r="G8" s="216"/>
+      <c r="H8" s="217"/>
       <c r="I8" s="74"/>
       <c r="J8" s="74"/>
     </row>
@@ -6834,30 +6851,30 @@
       <c r="H13" s="119"/>
     </row>
     <row r="14" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C14" s="205" t="s">
+      <c r="C14" s="209" t="s">
         <v>194</v>
       </c>
-      <c r="D14" s="206"/>
-      <c r="E14" s="206"/>
-      <c r="F14" s="206"/>
-      <c r="G14" s="206"/>
-      <c r="H14" s="207"/>
+      <c r="D14" s="210"/>
+      <c r="E14" s="210"/>
+      <c r="F14" s="210"/>
+      <c r="G14" s="210"/>
+      <c r="H14" s="211"/>
     </row>
     <row r="15" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C15" s="208"/>
-      <c r="D15" s="209"/>
-      <c r="E15" s="209"/>
-      <c r="F15" s="209"/>
-      <c r="G15" s="209"/>
-      <c r="H15" s="210"/>
+      <c r="C15" s="212"/>
+      <c r="D15" s="213"/>
+      <c r="E15" s="213"/>
+      <c r="F15" s="213"/>
+      <c r="G15" s="213"/>
+      <c r="H15" s="214"/>
     </row>
     <row r="16" spans="3:10" ht="117" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C16" s="211"/>
-      <c r="D16" s="212"/>
-      <c r="E16" s="212"/>
-      <c r="F16" s="212"/>
-      <c r="G16" s="212"/>
-      <c r="H16" s="213"/>
+      <c r="C16" s="215"/>
+      <c r="D16" s="216"/>
+      <c r="E16" s="216"/>
+      <c r="F16" s="216"/>
+      <c r="G16" s="216"/>
+      <c r="H16" s="217"/>
     </row>
     <row r="18" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="19" spans="3:8" x14ac:dyDescent="0.3">
@@ -6888,37 +6905,37 @@
       <c r="H21" s="119"/>
     </row>
     <row r="22" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C22" s="205" t="s">
+      <c r="C22" s="209" t="s">
         <v>195</v>
       </c>
-      <c r="D22" s="206"/>
-      <c r="E22" s="206"/>
-      <c r="F22" s="206"/>
-      <c r="G22" s="206"/>
-      <c r="H22" s="207"/>
+      <c r="D22" s="210"/>
+      <c r="E22" s="210"/>
+      <c r="F22" s="210"/>
+      <c r="G22" s="210"/>
+      <c r="H22" s="211"/>
     </row>
     <row r="23" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C23" s="208"/>
-      <c r="D23" s="209"/>
-      <c r="E23" s="209"/>
-      <c r="F23" s="209"/>
-      <c r="G23" s="209"/>
-      <c r="H23" s="210"/>
+      <c r="C23" s="212"/>
+      <c r="D23" s="213"/>
+      <c r="E23" s="213"/>
+      <c r="F23" s="213"/>
+      <c r="G23" s="213"/>
+      <c r="H23" s="214"/>
     </row>
     <row r="24" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C24" s="211"/>
-      <c r="D24" s="212"/>
-      <c r="E24" s="212"/>
-      <c r="F24" s="212"/>
-      <c r="G24" s="212"/>
-      <c r="H24" s="213"/>
+      <c r="C24" s="215"/>
+      <c r="D24" s="216"/>
+      <c r="E24" s="216"/>
+      <c r="F24" s="216"/>
+      <c r="G24" s="216"/>
+      <c r="H24" s="217"/>
     </row>
     <row r="26" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="27" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C27" s="215" t="s">
+      <c r="C27" s="170" t="s">
         <v>154</v>
       </c>
-      <c r="D27" s="216">
+      <c r="D27" s="171">
         <f>D19+1</f>
         <v>4</v>
       </c>
@@ -6928,7 +6945,7 @@
       <c r="H27" s="118"/>
     </row>
     <row r="28" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C28" s="217" t="s">
+      <c r="C28" s="172" t="s">
         <v>155</v>
       </c>
       <c r="D28" s="129">
@@ -6937,42 +6954,97 @@
       <c r="H28" s="119"/>
     </row>
     <row r="29" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C29" s="217"/>
+      <c r="C29" s="172"/>
       <c r="D29" s="129"/>
       <c r="H29" s="119"/>
     </row>
     <row r="30" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C30" s="205" t="s">
+      <c r="C30" s="209" t="s">
         <v>196</v>
       </c>
-      <c r="D30" s="206"/>
-      <c r="E30" s="206"/>
-      <c r="F30" s="206"/>
-      <c r="G30" s="206"/>
-      <c r="H30" s="207"/>
+      <c r="D30" s="210"/>
+      <c r="E30" s="210"/>
+      <c r="F30" s="210"/>
+      <c r="G30" s="210"/>
+      <c r="H30" s="211"/>
     </row>
     <row r="31" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C31" s="208"/>
-      <c r="D31" s="209"/>
-      <c r="E31" s="209"/>
-      <c r="F31" s="209"/>
-      <c r="G31" s="209"/>
-      <c r="H31" s="210"/>
+      <c r="C31" s="212"/>
+      <c r="D31" s="213"/>
+      <c r="E31" s="213"/>
+      <c r="F31" s="213"/>
+      <c r="G31" s="213"/>
+      <c r="H31" s="214"/>
     </row>
     <row r="32" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C32" s="211"/>
-      <c r="D32" s="212"/>
-      <c r="E32" s="212"/>
-      <c r="F32" s="212"/>
-      <c r="G32" s="212"/>
-      <c r="H32" s="213"/>
+      <c r="C32" s="215"/>
+      <c r="D32" s="216"/>
+      <c r="E32" s="216"/>
+      <c r="F32" s="216"/>
+      <c r="G32" s="216"/>
+      <c r="H32" s="217"/>
+    </row>
+    <row r="34" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="35" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C35" s="218" t="s">
+        <v>154</v>
+      </c>
+      <c r="D35" s="219">
+        <f>D27+1</f>
+        <v>5</v>
+      </c>
+      <c r="E35" s="117"/>
+      <c r="F35" s="117"/>
+      <c r="G35" s="117"/>
+      <c r="H35" s="118"/>
+    </row>
+    <row r="36" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C36" s="220" t="s">
+        <v>155</v>
+      </c>
+      <c r="D36" s="221" t="s">
+        <v>198</v>
+      </c>
+      <c r="H36" s="119"/>
+    </row>
+    <row r="37" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C37" s="220"/>
+      <c r="D37" s="221"/>
+      <c r="H37" s="119"/>
+    </row>
+    <row r="38" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C38" s="209" t="s">
+        <v>197</v>
+      </c>
+      <c r="D38" s="210"/>
+      <c r="E38" s="210"/>
+      <c r="F38" s="210"/>
+      <c r="G38" s="210"/>
+      <c r="H38" s="211"/>
+    </row>
+    <row r="39" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C39" s="212"/>
+      <c r="D39" s="213"/>
+      <c r="E39" s="213"/>
+      <c r="F39" s="213"/>
+      <c r="G39" s="213"/>
+      <c r="H39" s="214"/>
+    </row>
+    <row r="40" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C40" s="215"/>
+      <c r="D40" s="216"/>
+      <c r="E40" s="216"/>
+      <c r="F40" s="216"/>
+      <c r="G40" s="216"/>
+      <c r="H40" s="217"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="C6:H8"/>
     <mergeCell ref="C14:H16"/>
     <mergeCell ref="C22:H24"/>
     <mergeCell ref="C30:H32"/>
+    <mergeCell ref="C38:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026/GALERIA MITRE/Junio/Junio MITRE.xlsx
+++ b/2026/GALERIA MITRE/Junio/Junio MITRE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GALERIA MITRE\Junio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\GALERIA MITRE\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0417D70-2E5F-44D2-8BD5-07AFB0ED6F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0077DBB6-F522-46FE-A2E4-9BDBE5E43F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$115</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1497,146 +1502,146 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1705,9 +1710,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1745,9 +1750,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1780,9 +1785,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1815,9 +1837,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1992,20 +2031,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L115"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5546875" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.44140625" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="131" t="s">
         <v>64</v>
       </c>
@@ -2013,7 +2052,7 @@
       <c r="C1" s="133"/>
       <c r="D1" s="133"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="134" t="s">
         <v>125</v>
       </c>
@@ -2021,7 +2060,7 @@
       <c r="C2" s="134"/>
       <c r="D2" s="134"/>
     </row>
-    <row r="3" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="134" t="s">
         <v>70</v>
       </c>
@@ -2029,115 +2068,115 @@
       <c r="C3" s="134"/>
       <c r="D3" s="134"/>
     </row>
-    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="173" t="s">
+    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="182" t="s">
         <v>151</v>
       </c>
-      <c r="B4" s="173"/>
+      <c r="B4" s="182"/>
       <c r="C4" s="135"/>
       <c r="D4" s="135"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="173"/>
-      <c r="B5" s="173"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="182"/>
+      <c r="B5" s="182"/>
       <c r="C5" s="135"/>
       <c r="D5" s="135"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="173"/>
-      <c r="B6" s="173"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="182"/>
+      <c r="B6" s="182"/>
       <c r="C6" s="135"/>
       <c r="D6" s="135"/>
     </row>
-    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="173"/>
-      <c r="B7" s="173"/>
+    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="182"/>
+      <c r="B7" s="182"/>
       <c r="C7" s="135"/>
       <c r="D7" s="135"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="63"/>
       <c r="B8" s="63"/>
       <c r="C8" s="63"/>
       <c r="D8" s="63"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="63"/>
-      <c r="B9" s="182" t="s">
+      <c r="B9" s="181" t="s">
         <v>166</v>
       </c>
       <c r="C9" s="63"/>
       <c r="D9" s="63"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="63"/>
-      <c r="B10" s="182"/>
+      <c r="B10" s="181"/>
       <c r="C10" s="63"/>
       <c r="D10" s="63"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="63"/>
-      <c r="B11" s="182"/>
+      <c r="B11" s="181"/>
       <c r="C11" s="63"/>
       <c r="D11" s="63"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="63"/>
       <c r="B12" s="63"/>
       <c r="C12" s="63"/>
       <c r="D12" s="63"/>
     </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="63"/>
       <c r="B13" s="63"/>
       <c r="C13" s="63"/>
       <c r="D13" s="63"/>
     </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="173" t="s">
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="182" t="s">
         <v>148</v>
       </c>
-      <c r="B14" s="173"/>
-      <c r="C14" s="173"/>
-      <c r="D14" s="173"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="173"/>
-      <c r="B15" s="173"/>
-      <c r="C15" s="173"/>
-      <c r="D15" s="173"/>
-    </row>
-    <row r="16" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="173"/>
-      <c r="B16" s="173"/>
-      <c r="C16" s="173"/>
-      <c r="D16" s="173"/>
-    </row>
-    <row r="17" spans="1:7" ht="156.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="173"/>
-      <c r="B17" s="173"/>
-      <c r="C17" s="173"/>
-      <c r="D17" s="173"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="182"/>
+      <c r="C14" s="182"/>
+      <c r="D14" s="182"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="182"/>
+      <c r="B15" s="182"/>
+      <c r="C15" s="182"/>
+      <c r="D15" s="182"/>
+    </row>
+    <row r="16" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="182"/>
+      <c r="B16" s="182"/>
+      <c r="C16" s="182"/>
+      <c r="D16" s="182"/>
+    </row>
+    <row r="17" spans="1:7" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="182"/>
+      <c r="B17" s="182"/>
+      <c r="C17" s="182"/>
+      <c r="D17" s="182"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="63"/>
       <c r="B18" s="63"/>
       <c r="C18" s="63"/>
       <c r="D18" s="63"/>
     </row>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="136"/>
       <c r="B19" s="63"/>
       <c r="C19" s="63"/>
       <c r="D19" s="63"/>
     </row>
-    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="63"/>
       <c r="B20" s="63"/>
       <c r="C20" s="63"/>
       <c r="D20" s="63"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="137" t="s">
         <v>26</v>
       </c>
@@ -2149,7 +2188,7 @@
       </c>
       <c r="F21" s="129"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>52</v>
       </c>
@@ -2159,11 +2198,11 @@
       <c r="E22" s="129"/>
       <c r="F22" s="129"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="177" t="s">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="179" t="s">
         <v>167</v>
       </c>
-      <c r="B23" s="178"/>
+      <c r="B23" s="180"/>
       <c r="C23" s="82">
         <v>1231605.7</v>
       </c>
@@ -2171,7 +2210,7 @@
       <c r="E23" s="129"/>
       <c r="F23" s="129"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="48" t="s">
         <v>55</v>
       </c>
@@ -2183,7 +2222,7 @@
       <c r="E24" s="129"/>
       <c r="F24" s="129"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="48" t="s">
         <v>54</v>
       </c>
@@ -2196,7 +2235,7 @@
       <c r="F25" s="129"/>
       <c r="G25" s="94"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="139" t="s">
         <v>53</v>
       </c>
@@ -2209,11 +2248,11 @@
       <c r="E26" s="129"/>
       <c r="F26" s="129"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="177" t="s">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="179" t="s">
         <v>168</v>
       </c>
-      <c r="B27" s="178"/>
+      <c r="B27" s="180"/>
       <c r="C27" s="82">
         <v>815681.8</v>
       </c>
@@ -2221,7 +2260,7 @@
       <c r="E27" s="129"/>
       <c r="F27" s="129"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="48" t="s">
         <v>55</v>
       </c>
@@ -2233,7 +2272,7 @@
       <c r="E28" s="129"/>
       <c r="F28" s="129"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="48" t="s">
         <v>54</v>
       </c>
@@ -2243,7 +2282,7 @@
       </c>
       <c r="D29" s="73"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="139" t="s">
         <v>53</v>
       </c>
@@ -2254,7 +2293,7 @@
       </c>
       <c r="D30" s="49"/>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="48"/>
       <c r="B31" s="48"/>
       <c r="C31" s="97">
@@ -2262,13 +2301,13 @@
       </c>
       <c r="D31" s="73"/>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="48"/>
       <c r="B32" s="48"/>
       <c r="C32" s="97"/>
       <c r="D32" s="73"/>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="139" t="s">
         <v>53</v>
       </c>
@@ -2279,7 +2318,7 @@
       </c>
       <c r="D33" s="49"/>
     </row>
-    <row r="34" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
         <v>0</v>
       </c>
@@ -2292,7 +2331,7 @@
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>38</v>
       </c>
@@ -2301,18 +2340,18 @@
       <c r="D35" s="51"/>
       <c r="F35" s="4"/>
     </row>
-    <row r="36" spans="1:7" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="177" t="s">
+    <row r="36" spans="1:7" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="179" t="s">
         <v>183</v>
       </c>
-      <c r="B36" s="178"/>
+      <c r="B36" s="180"/>
       <c r="C36" s="82">
         <v>710000</v>
       </c>
       <c r="D36" s="81"/>
       <c r="G36" s="4"/>
     </row>
-    <row r="37" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="141" t="s">
         <v>161</v>
       </c>
@@ -2325,7 +2364,7 @@
       </c>
       <c r="G37" s="4"/>
     </row>
-    <row r="38" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="141" t="s">
         <v>157</v>
       </c>
@@ -2338,7 +2377,7 @@
       </c>
       <c r="G38" s="4"/>
     </row>
-    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
         <v>34</v>
       </c>
@@ -2349,7 +2388,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>49</v>
       </c>
@@ -2357,11 +2396,11 @@
       <c r="C40" s="14"/>
       <c r="D40" s="31"/>
     </row>
-    <row r="41" spans="1:7" s="19" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="177" t="s">
+    <row r="41" spans="1:7" s="19" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="179" t="s">
         <v>130</v>
       </c>
-      <c r="B41" s="178"/>
+      <c r="B41" s="180"/>
       <c r="C41" s="96">
         <v>111379</v>
       </c>
@@ -2369,7 +2408,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="12" t="s">
         <v>1</v>
       </c>
@@ -2380,7 +2419,7 @@
         <v>111379</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>35</v>
       </c>
@@ -2388,7 +2427,7 @@
       <c r="C43" s="17"/>
       <c r="D43" s="53"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="48" t="s">
         <v>65</v>
       </c>
@@ -2399,11 +2438,11 @@
       <c r="D44" s="77"/>
       <c r="F44" s="74"/>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="177" t="s">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="179" t="s">
         <v>181</v>
       </c>
-      <c r="B45" s="178"/>
+      <c r="B45" s="180"/>
       <c r="C45" s="100">
         <v>11596.99</v>
       </c>
@@ -2412,11 +2451,11 @@
       </c>
       <c r="F45" s="74"/>
     </row>
-    <row r="46" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="177" t="s">
+    <row r="46" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="179" t="s">
         <v>129</v>
       </c>
-      <c r="B46" s="178"/>
+      <c r="B46" s="180"/>
       <c r="C46" s="100">
         <v>11930.96</v>
       </c>
@@ -2426,7 +2465,7 @@
       </c>
       <c r="F46" s="74"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="48" t="s">
         <v>66</v>
       </c>
@@ -2440,7 +2479,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="48" t="s">
         <v>67</v>
       </c>
@@ -2455,7 +2494,7 @@
         <v>Debito 12/06</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="48" t="s">
         <v>68</v>
       </c>
@@ -2470,7 +2509,7 @@
         <v>Debito 12/06</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
         <v>2</v>
       </c>
@@ -2481,7 +2520,7 @@
         <v>326409.02</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
         <v>37</v>
       </c>
@@ -2489,7 +2528,7 @@
       <c r="C51" s="17"/>
       <c r="D51" s="53"/>
     </row>
-    <row r="52" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="48" t="s">
         <v>127</v>
       </c>
@@ -2501,7 +2540,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="48" t="s">
         <v>126</v>
       </c>
@@ -2513,7 +2552,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="48" t="s">
         <v>160</v>
       </c>
@@ -2525,7 +2564,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="48" t="s">
         <v>128</v>
       </c>
@@ -2537,7 +2576,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="48" t="s">
         <v>159</v>
       </c>
@@ -2549,7 +2588,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
         <v>3</v>
       </c>
@@ -2560,7 +2599,7 @@
         <v>2314942.36</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
         <v>36</v>
       </c>
@@ -2568,11 +2607,11 @@
       <c r="C58" s="16"/>
       <c r="D58" s="55"/>
     </row>
-    <row r="59" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="179" t="s">
+    <row r="59" spans="1:6" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="186" t="s">
         <v>156</v>
       </c>
-      <c r="B59" s="180"/>
+      <c r="B59" s="187"/>
       <c r="C59" s="85">
         <v>202000</v>
       </c>
@@ -2580,11 +2619,11 @@
         <v>174</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="179" t="s">
+    <row r="60" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="186" t="s">
         <v>176</v>
       </c>
-      <c r="B60" s="180"/>
+      <c r="B60" s="187"/>
       <c r="C60" s="85">
         <v>229900</v>
       </c>
@@ -2592,11 +2631,11 @@
         <v>174</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="177" t="s">
+    <row r="61" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="179" t="s">
         <v>178</v>
       </c>
-      <c r="B61" s="178"/>
+      <c r="B61" s="180"/>
       <c r="C61" s="85">
         <v>35000</v>
       </c>
@@ -2606,11 +2645,11 @@
       <c r="E61" s="85"/>
       <c r="F61" s="24"/>
     </row>
-    <row r="62" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="179" t="s">
+    <row r="62" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="186" t="s">
         <v>179</v>
       </c>
-      <c r="B62" s="180"/>
+      <c r="B62" s="187"/>
       <c r="C62" s="85">
         <v>9395</v>
       </c>
@@ -2623,11 +2662,11 @@
       </c>
       <c r="F62" s="24"/>
     </row>
-    <row r="63" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="179" t="s">
+    <row r="63" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="186" t="s">
         <v>171</v>
       </c>
-      <c r="B63" s="180"/>
+      <c r="B63" s="187"/>
       <c r="C63" s="85">
         <v>18300</v>
       </c>
@@ -2637,7 +2676,7 @@
       <c r="E63" s="125"/>
       <c r="F63" s="24"/>
     </row>
-    <row r="64" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="127" t="s">
         <v>175</v>
       </c>
@@ -2651,7 +2690,7 @@
       <c r="E64" s="125"/>
       <c r="F64" s="24"/>
     </row>
-    <row r="65" spans="1:6" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="127" t="s">
         <v>175</v>
       </c>
@@ -2665,7 +2704,7 @@
       <c r="E65" s="24"/>
       <c r="F65" s="24"/>
     </row>
-    <row r="66" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="12" t="s">
         <v>11</v>
       </c>
@@ -2676,7 +2715,7 @@
         <v>808295</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="11" t="s">
         <v>29</v>
       </c>
@@ -2684,17 +2723,17 @@
       <c r="C67" s="8"/>
       <c r="D67" s="55"/>
     </row>
-    <row r="68" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="177" t="s">
+    <row r="68" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="179" t="s">
         <v>73</v>
       </c>
-      <c r="B68" s="178"/>
+      <c r="B68" s="180"/>
       <c r="C68" s="85">
         <v>60000</v>
       </c>
       <c r="D68" s="59"/>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="48" t="s">
         <v>71</v>
       </c>
@@ -2705,7 +2744,7 @@
       </c>
       <c r="D69" s="57"/>
     </row>
-    <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="143" t="s">
         <v>34</v>
       </c>
@@ -2716,31 +2755,31 @@
         <v>210902.53</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="48"/>
       <c r="B71" s="48"/>
       <c r="C71" s="48"/>
       <c r="D71" s="61"/>
     </row>
-    <row r="72" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="174" t="s">
+    <row r="72" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="183" t="s">
         <v>188</v>
       </c>
-      <c r="B72" s="175"/>
-      <c r="C72" s="176"/>
+      <c r="B72" s="184"/>
+      <c r="C72" s="185"/>
       <c r="D72" s="62">
         <f>(6780039.56+6780039.56*20%)-6423356.91</f>
         <v>1712690.561999999</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="144"/>
       <c r="B73" s="63"/>
       <c r="C73" s="63"/>
       <c r="D73" s="64"/>
       <c r="E73" s="24"/>
     </row>
-    <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="145" t="s">
         <v>30</v>
       </c>
@@ -2753,20 +2792,20 @@
       <c r="E74" s="24"/>
       <c r="F74" s="24"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="63"/>
       <c r="B75" s="63"/>
       <c r="C75" s="63"/>
       <c r="D75" s="63"/>
       <c r="F75" s="75"/>
     </row>
-    <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="63"/>
       <c r="B76" s="63"/>
       <c r="C76" s="63"/>
       <c r="D76" s="63"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="137" t="s">
         <v>39</v>
       </c>
@@ -2774,25 +2813,25 @@
       <c r="C77" s="67"/>
       <c r="D77" s="68"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="177"/>
-      <c r="B78" s="178"/>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="179"/>
+      <c r="B78" s="180"/>
       <c r="C78" s="56"/>
       <c r="D78" s="54"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="177"/>
-      <c r="B79" s="178"/>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="179"/>
+      <c r="B79" s="180"/>
       <c r="C79" s="56"/>
       <c r="D79" s="54"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="127"/>
       <c r="B80" s="147"/>
       <c r="C80" s="56"/>
       <c r="D80" s="54"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="148"/>
       <c r="B81" s="149"/>
       <c r="C81" s="150"/>
@@ -2801,19 +2840,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="63"/>
       <c r="B82" s="63"/>
       <c r="C82" s="63"/>
       <c r="D82" s="63"/>
     </row>
-    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="63"/>
       <c r="B83" s="63"/>
       <c r="C83" s="63"/>
       <c r="D83" s="63"/>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="151" t="s">
         <v>40</v>
       </c>
@@ -2823,13 +2862,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="63"/>
       <c r="B85" s="63"/>
       <c r="C85" s="63"/>
       <c r="D85" s="63"/>
     </row>
-    <row r="86" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="145" t="s">
         <v>41</v>
       </c>
@@ -2840,13 +2879,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="63"/>
       <c r="B87" s="63"/>
       <c r="C87" s="63"/>
       <c r="D87" s="63"/>
     </row>
-    <row r="88" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="154" t="s">
         <v>31</v>
       </c>
@@ -2857,7 +2896,7 @@
       <c r="C88" s="156"/>
       <c r="D88" s="63"/>
     </row>
-    <row r="89" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="154" t="s">
         <v>32</v>
       </c>
@@ -2868,7 +2907,7 @@
       <c r="C89" s="63"/>
       <c r="D89" s="63"/>
     </row>
-    <row r="90" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="154" t="s">
         <v>42</v>
       </c>
@@ -2879,7 +2918,7 @@
       <c r="C90" s="63"/>
       <c r="D90" s="63"/>
     </row>
-    <row r="91" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="154" t="s">
         <v>59</v>
       </c>
@@ -2890,13 +2929,13 @@
       <c r="C91" s="63"/>
       <c r="D91" s="63"/>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B95" s="21"/>
     </row>
-    <row r="96" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="10" t="s">
         <v>33</v>
       </c>
@@ -2904,7 +2943,7 @@
         <v>-14222.15</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
         <v>62</v>
       </c>
@@ -2913,7 +2952,7 @@
         <v>7982295.1100000003</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="102" t="s">
         <v>61</v>
       </c>
@@ -2922,7 +2961,7 @@
         <v>828486</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="102" t="s">
         <v>163</v>
       </c>
@@ -2930,7 +2969,7 @@
         <v>-600000</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="102" t="s">
         <v>186</v>
       </c>
@@ -2938,7 +2977,7 @@
         <v>-273000</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
         <v>72</v>
       </c>
@@ -2947,7 +2986,7 @@
         <v>-23137</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="20" t="s">
         <v>43</v>
       </c>
@@ -2956,7 +2995,7 @@
         <v>-6423356.9100000001</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
         <v>44</v>
       </c>
@@ -2965,7 +3004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="9" t="s">
         <v>11</v>
       </c>
@@ -2975,12 +3014,12 @@
       </c>
       <c r="D104" s="98"/>
     </row>
-    <row r="105" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
       <c r="B105" s="103"/>
       <c r="D105" s="98"/>
     </row>
-    <row r="106" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="115" t="s">
         <v>189</v>
       </c>
@@ -2989,25 +3028,25 @@
       </c>
       <c r="D106" s="98"/>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="103"/>
       <c r="D107" s="98"/>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D108" s="99"/>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="181" t="s">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="178" t="s">
         <v>50</v>
       </c>
-      <c r="B109" s="181"/>
-    </row>
-    <row r="110" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="181"/>
-      <c r="B110" s="181"/>
-    </row>
-    <row r="111" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B109" s="178"/>
+    </row>
+    <row r="110" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="178"/>
+      <c r="B110" s="178"/>
+    </row>
+    <row r="111" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="69" t="s">
         <v>184</v>
       </c>
@@ -3015,7 +3054,7 @@
         <v>92118</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="69" t="s">
         <v>187</v>
       </c>
@@ -3023,7 +3062,7 @@
         <v>260000</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="69" t="s">
         <v>185</v>
       </c>
@@ -3031,7 +3070,7 @@
         <v>476368</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="25" t="s">
         <v>11</v>
       </c>
@@ -3040,17 +3079,11 @@
         <v>828486</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L115" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A109:B110"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A14:D17"/>
     <mergeCell ref="A72:C72"/>
@@ -3064,6 +3097,12 @@
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A109:B110"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3074,41 +3113,41 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R74"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" customWidth="1"/>
-    <col min="3" max="3" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="5.42578125" customWidth="1"/>
     <col min="4" max="4" width="29" customWidth="1"/>
-    <col min="5" max="5" width="5.109375" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="7.5546875" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" customWidth="1"/>
-    <col min="10" max="10" width="11.109375" customWidth="1"/>
-    <col min="11" max="11" width="14.44140625" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" customWidth="1"/>
-    <col min="13" max="13" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.44140625" customWidth="1"/>
-    <col min="15" max="15" width="14.109375" customWidth="1"/>
-    <col min="16" max="16" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" customWidth="1"/>
+    <col min="16" max="16" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
-      <c r="B1" s="183" t="s">
+      <c r="B1" s="194" t="s">
         <v>151</v>
       </c>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="185"/>
+      <c r="C1" s="195"/>
+      <c r="D1" s="195"/>
+      <c r="E1" s="195"/>
+      <c r="F1" s="195"/>
+      <c r="G1" s="195"/>
+      <c r="H1" s="195"/>
+      <c r="I1" s="195"/>
+      <c r="J1" s="196"/>
       <c r="K1" s="111" t="s">
         <v>4</v>
       </c>
@@ -3124,17 +3163,17 @@
         <v>8136047.4719999991</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="186"/>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
-      <c r="E2" s="187"/>
-      <c r="F2" s="187"/>
-      <c r="G2" s="187"/>
-      <c r="H2" s="187"/>
-      <c r="I2" s="187"/>
-      <c r="J2" s="188"/>
+      <c r="B2" s="197"/>
+      <c r="C2" s="198"/>
+      <c r="D2" s="198"/>
+      <c r="E2" s="198"/>
+      <c r="F2" s="198"/>
+      <c r="G2" s="198"/>
+      <c r="H2" s="198"/>
+      <c r="I2" s="198"/>
+      <c r="J2" s="199"/>
       <c r="K2" s="113" t="s">
         <v>63</v>
       </c>
@@ -3145,30 +3184,30 @@
       </c>
       <c r="O2" s="110"/>
     </row>
-    <row r="3" spans="1:18" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="202" t="s">
+      <c r="B3" s="211" t="s">
         <v>148</v>
       </c>
-      <c r="C3" s="203"/>
-      <c r="D3" s="203"/>
-      <c r="E3" s="203"/>
-      <c r="F3" s="203"/>
-      <c r="G3" s="203"/>
-      <c r="H3" s="203"/>
-      <c r="I3" s="203"/>
-      <c r="J3" s="203"/>
-      <c r="K3" s="203"/>
-      <c r="L3" s="203"/>
-      <c r="M3" s="203"/>
-      <c r="N3" s="203"/>
-      <c r="O3" s="204"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="205" t="s">
+      <c r="C3" s="212"/>
+      <c r="D3" s="212"/>
+      <c r="E3" s="212"/>
+      <c r="F3" s="212"/>
+      <c r="G3" s="212"/>
+      <c r="H3" s="212"/>
+      <c r="I3" s="212"/>
+      <c r="J3" s="212"/>
+      <c r="K3" s="212"/>
+      <c r="L3" s="212"/>
+      <c r="M3" s="212"/>
+      <c r="N3" s="212"/>
+      <c r="O3" s="213"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="188" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="207" t="s">
+      <c r="B4" s="190" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="192" t="s">
@@ -3189,50 +3228,50 @@
       <c r="H4" s="192" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="197" t="s">
+      <c r="I4" s="206" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="194" t="s">
+      <c r="J4" s="204" t="s">
         <v>46</v>
       </c>
-      <c r="K4" s="194" t="s">
+      <c r="K4" s="204" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="194" t="s">
+      <c r="L4" s="204" t="s">
         <v>45</v>
       </c>
-      <c r="M4" s="200" t="s">
+      <c r="M4" s="209" t="s">
         <v>58</v>
       </c>
       <c r="N4" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="O4" s="189" t="s">
+      <c r="O4" s="200" t="s">
         <v>56</v>
       </c>
       <c r="R4" s="24"/>
     </row>
-    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="206"/>
-      <c r="B5" s="208"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="196"/>
-      <c r="E5" s="196"/>
-      <c r="F5" s="196"/>
-      <c r="G5" s="196"/>
-      <c r="H5" s="193"/>
-      <c r="I5" s="198"/>
-      <c r="J5" s="195"/>
-      <c r="K5" s="199"/>
-      <c r="L5" s="195"/>
-      <c r="M5" s="201"/>
+    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="189"/>
+      <c r="B5" s="191"/>
+      <c r="C5" s="193"/>
+      <c r="D5" s="193"/>
+      <c r="E5" s="193"/>
+      <c r="F5" s="193"/>
+      <c r="G5" s="193"/>
+      <c r="H5" s="203"/>
+      <c r="I5" s="207"/>
+      <c r="J5" s="205"/>
+      <c r="K5" s="208"/>
+      <c r="L5" s="205"/>
+      <c r="M5" s="210"/>
       <c r="N5" s="28" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 17/07</v>
       </c>
-      <c r="O5" s="190"/>
-    </row>
-    <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O5" s="201"/>
+    </row>
+    <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="130" t="s">
         <v>12</v>
       </c>
@@ -3286,7 +3325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="130"/>
       <c r="B7" s="87">
         <v>1</v>
@@ -3339,7 +3378,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="130" t="s">
         <v>13</v>
       </c>
@@ -3394,7 +3433,7 @@
       </c>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="130" t="s">
         <v>13</v>
       </c>
@@ -3451,7 +3490,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="130" t="s">
         <v>14</v>
       </c>
@@ -3511,7 +3550,7 @@
       </c>
       <c r="R10" s="24"/>
     </row>
-    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="157" t="s">
         <v>14</v>
       </c>
@@ -3568,7 +3607,7 @@
       </c>
       <c r="R11" s="24"/>
     </row>
-    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="130"/>
       <c r="B12" s="87">
         <f t="shared" si="6"/>
@@ -3623,7 +3662,7 @@
       </c>
       <c r="R12" s="24"/>
     </row>
-    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="130"/>
       <c r="B13" s="87">
         <f t="shared" si="6"/>
@@ -3681,7 +3720,7 @@
       </c>
       <c r="R13" s="24"/>
     </row>
-    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="130"/>
       <c r="B14" s="87">
         <f t="shared" si="6"/>
@@ -3736,7 +3775,7 @@
       </c>
       <c r="R14" s="24"/>
     </row>
-    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="130"/>
       <c r="B15" s="87">
         <f t="shared" si="6"/>
@@ -3792,7 +3831,7 @@
       </c>
       <c r="R15" s="24"/>
     </row>
-    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="130"/>
       <c r="B16" s="87">
         <f t="shared" si="6"/>
@@ -3850,7 +3889,7 @@
       </c>
       <c r="R16" s="24"/>
     </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="130"/>
       <c r="B17" s="87">
         <f t="shared" si="6"/>
@@ -3905,7 +3944,7 @@
       </c>
       <c r="R17" s="24"/>
     </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="130"/>
       <c r="B18" s="87">
         <f t="shared" si="6"/>
@@ -3960,7 +3999,7 @@
       </c>
       <c r="R18" s="24"/>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="130"/>
       <c r="B19" s="87">
         <f t="shared" si="6"/>
@@ -4019,7 +4058,7 @@
       </c>
       <c r="R19" s="24"/>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="130"/>
       <c r="B20" s="87">
         <f t="shared" si="6"/>
@@ -4078,7 +4117,7 @@
       </c>
       <c r="R20" s="24"/>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="130"/>
       <c r="B21" s="159">
         <f t="shared" si="6"/>
@@ -4137,16 +4176,16 @@
       </c>
       <c r="R21" s="24"/>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="130"/>
-      <c r="B22" s="222">
-        <f t="shared" si="6"/>
+      <c r="B22" s="177">
+        <f>B21+1</f>
         <v>16</v>
       </c>
-      <c r="C22" s="222" t="s">
+      <c r="C22" s="177" t="s">
         <v>118</v>
       </c>
-      <c r="D22" s="222" t="s">
+      <c r="D22" s="177" t="s">
         <v>87</v>
       </c>
       <c r="E22" s="32">
@@ -4195,7 +4234,7 @@
       </c>
       <c r="R22" s="24"/>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="130" t="s">
         <v>15</v>
       </c>
@@ -4251,7 +4290,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="130" t="s">
         <v>15</v>
       </c>
@@ -4309,7 +4348,7 @@
       <c r="Q24" s="75"/>
       <c r="R24" s="74"/>
     </row>
-    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="130" t="s">
         <v>16</v>
       </c>
@@ -4365,7 +4404,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="130" t="s">
         <v>16</v>
       </c>
@@ -4421,7 +4460,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="130" t="s">
         <v>17</v>
       </c>
@@ -4478,7 +4517,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="130" t="s">
         <v>17</v>
       </c>
@@ -4537,7 +4576,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="130" t="s">
         <v>18</v>
       </c>
@@ -4594,7 +4633,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="130" t="s">
         <v>18</v>
       </c>
@@ -4650,7 +4689,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="130" t="s">
         <v>19</v>
       </c>
@@ -4706,7 +4745,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="130" t="s">
         <v>19</v>
       </c>
@@ -4763,7 +4802,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="130" t="s">
         <v>20</v>
       </c>
@@ -4821,7 +4860,7 @@
       </c>
       <c r="R33" s="23"/>
     </row>
-    <row r="34" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="130" t="s">
         <v>20</v>
       </c>
@@ -4880,7 +4919,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="130" t="s">
         <v>21</v>
       </c>
@@ -4937,7 +4976,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="130" t="s">
         <v>21</v>
       </c>
@@ -4994,7 +5033,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="130" t="s">
         <v>22</v>
       </c>
@@ -5054,7 +5093,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="130" t="s">
         <v>23</v>
       </c>
@@ -5114,7 +5153,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="130" t="s">
         <v>24</v>
       </c>
@@ -5173,7 +5212,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="130" t="s">
         <v>25</v>
       </c>
@@ -5233,7 +5272,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="130" t="s">
         <v>27</v>
       </c>
@@ -5293,7 +5332,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="130" t="s">
         <v>27</v>
       </c>
@@ -5353,7 +5392,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="130" t="s">
         <v>27</v>
       </c>
@@ -5411,7 +5450,7 @@
       </c>
       <c r="Q43" s="74"/>
     </row>
-    <row r="44" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="130" t="s">
         <v>27</v>
       </c>
@@ -5467,7 +5506,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="130" t="s">
         <v>27</v>
       </c>
@@ -5524,7 +5563,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="74"/>
       <c r="B46" s="87">
         <f t="shared" ref="B46:B64" si="8">B45+1</f>
@@ -5579,7 +5618,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="74"/>
       <c r="B47" s="169">
         <f t="shared" si="8"/>
@@ -5633,7 +5672,7 @@
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="74"/>
       <c r="B48" s="87">
         <f t="shared" si="8"/>
@@ -5687,7 +5726,7 @@
         <v>0.42000000000000021</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="74"/>
       <c r="B49" s="87">
         <f t="shared" si="8"/>
@@ -5741,7 +5780,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="74"/>
       <c r="B50" s="87">
         <f t="shared" si="8"/>
@@ -5795,7 +5834,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="74"/>
       <c r="B51" s="87">
         <f t="shared" si="8"/>
@@ -5850,7 +5889,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="74"/>
       <c r="B52" s="87">
         <f t="shared" si="8"/>
@@ -5905,7 +5944,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="74"/>
       <c r="B53" s="87">
         <f t="shared" si="8"/>
@@ -5959,7 +5998,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="74"/>
       <c r="B54" s="87">
         <f t="shared" si="8"/>
@@ -6017,7 +6056,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="74"/>
       <c r="B55" s="87">
         <f t="shared" si="8"/>
@@ -6075,7 +6114,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="74"/>
       <c r="B56" s="87">
         <f t="shared" si="8"/>
@@ -6133,7 +6172,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="74"/>
       <c r="B57" s="87">
         <f t="shared" si="8"/>
@@ -6187,7 +6226,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="74"/>
       <c r="B58" s="87">
         <f t="shared" si="8"/>
@@ -6242,7 +6281,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="74"/>
       <c r="B59" s="87">
         <f t="shared" si="8"/>
@@ -6296,7 +6335,7 @@
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="74"/>
       <c r="B60" s="87">
         <f t="shared" si="8"/>
@@ -6350,7 +6389,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="74"/>
       <c r="B61" s="87">
         <f t="shared" si="8"/>
@@ -6408,7 +6447,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="74"/>
       <c r="B62" s="87">
         <f t="shared" si="8"/>
@@ -6463,7 +6502,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="74"/>
       <c r="B63" s="87">
         <f t="shared" si="8"/>
@@ -6517,7 +6556,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B64" s="87">
         <f t="shared" si="8"/>
         <v>58</v>
@@ -6570,7 +6609,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B65" s="87"/>
       <c r="C65" s="30"/>
       <c r="D65" s="30"/>
@@ -6587,7 +6626,7 @@
       <c r="O65" s="33"/>
       <c r="P65" s="24"/>
     </row>
-    <row r="66" spans="2:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B66" s="45"/>
       <c r="C66" s="46"/>
       <c r="D66" s="105"/>
@@ -6636,97 +6675,92 @@
         <v>30376076.109999999</v>
       </c>
     </row>
-    <row r="67" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D67" s="26"/>
     </row>
-    <row r="68" spans="2:16" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="69" spans="2:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D69" s="191" t="s">
+    <row r="68" spans="2:16" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="2:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D69" s="202" t="s">
         <v>69</v>
       </c>
-      <c r="E69" s="191"/>
-      <c r="F69" s="191"/>
-      <c r="G69" s="191"/>
-      <c r="H69" s="191"/>
-      <c r="I69" s="191"/>
-      <c r="J69" s="191"/>
-      <c r="K69" s="191"/>
-      <c r="L69" s="191"/>
-      <c r="M69" s="191"/>
-      <c r="N69" s="191"/>
-    </row>
-    <row r="70" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D70" s="191"/>
-      <c r="E70" s="191"/>
-      <c r="F70" s="191"/>
-      <c r="G70" s="191"/>
-      <c r="H70" s="191"/>
-      <c r="I70" s="191"/>
-      <c r="J70" s="191"/>
-      <c r="K70" s="191"/>
-      <c r="L70" s="191"/>
-      <c r="M70" s="191"/>
-      <c r="N70" s="191"/>
-    </row>
-    <row r="71" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D71" s="191"/>
-      <c r="E71" s="191"/>
-      <c r="F71" s="191"/>
-      <c r="G71" s="191"/>
-      <c r="H71" s="191"/>
-      <c r="I71" s="191"/>
-      <c r="J71" s="191"/>
-      <c r="K71" s="191"/>
-      <c r="L71" s="191"/>
-      <c r="M71" s="191"/>
-      <c r="N71" s="191"/>
-    </row>
-    <row r="72" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D72" s="191"/>
-      <c r="E72" s="191"/>
-      <c r="F72" s="191"/>
-      <c r="G72" s="191"/>
-      <c r="H72" s="191"/>
-      <c r="I72" s="191"/>
-      <c r="J72" s="191"/>
-      <c r="K72" s="191"/>
-      <c r="L72" s="191"/>
-      <c r="M72" s="191"/>
-      <c r="N72" s="191"/>
-    </row>
-    <row r="73" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D73" s="191"/>
-      <c r="E73" s="191"/>
-      <c r="F73" s="191"/>
-      <c r="G73" s="191"/>
-      <c r="H73" s="191"/>
-      <c r="I73" s="191"/>
-      <c r="J73" s="191"/>
-      <c r="K73" s="191"/>
-      <c r="L73" s="191"/>
-      <c r="M73" s="191"/>
-      <c r="N73" s="191"/>
-    </row>
-    <row r="74" spans="2:16" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D74" s="191"/>
-      <c r="E74" s="191"/>
-      <c r="F74" s="191"/>
-      <c r="G74" s="191"/>
-      <c r="H74" s="191"/>
-      <c r="I74" s="191"/>
-      <c r="J74" s="191"/>
-      <c r="K74" s="191"/>
-      <c r="L74" s="191"/>
-      <c r="M74" s="191"/>
-      <c r="N74" s="191"/>
+      <c r="E69" s="202"/>
+      <c r="F69" s="202"/>
+      <c r="G69" s="202"/>
+      <c r="H69" s="202"/>
+      <c r="I69" s="202"/>
+      <c r="J69" s="202"/>
+      <c r="K69" s="202"/>
+      <c r="L69" s="202"/>
+      <c r="M69" s="202"/>
+      <c r="N69" s="202"/>
+    </row>
+    <row r="70" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D70" s="202"/>
+      <c r="E70" s="202"/>
+      <c r="F70" s="202"/>
+      <c r="G70" s="202"/>
+      <c r="H70" s="202"/>
+      <c r="I70" s="202"/>
+      <c r="J70" s="202"/>
+      <c r="K70" s="202"/>
+      <c r="L70" s="202"/>
+      <c r="M70" s="202"/>
+      <c r="N70" s="202"/>
+    </row>
+    <row r="71" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D71" s="202"/>
+      <c r="E71" s="202"/>
+      <c r="F71" s="202"/>
+      <c r="G71" s="202"/>
+      <c r="H71" s="202"/>
+      <c r="I71" s="202"/>
+      <c r="J71" s="202"/>
+      <c r="K71" s="202"/>
+      <c r="L71" s="202"/>
+      <c r="M71" s="202"/>
+      <c r="N71" s="202"/>
+    </row>
+    <row r="72" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D72" s="202"/>
+      <c r="E72" s="202"/>
+      <c r="F72" s="202"/>
+      <c r="G72" s="202"/>
+      <c r="H72" s="202"/>
+      <c r="I72" s="202"/>
+      <c r="J72" s="202"/>
+      <c r="K72" s="202"/>
+      <c r="L72" s="202"/>
+      <c r="M72" s="202"/>
+      <c r="N72" s="202"/>
+    </row>
+    <row r="73" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D73" s="202"/>
+      <c r="E73" s="202"/>
+      <c r="F73" s="202"/>
+      <c r="G73" s="202"/>
+      <c r="H73" s="202"/>
+      <c r="I73" s="202"/>
+      <c r="J73" s="202"/>
+      <c r="K73" s="202"/>
+      <c r="L73" s="202"/>
+      <c r="M73" s="202"/>
+      <c r="N73" s="202"/>
+    </row>
+    <row r="74" spans="2:16" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D74" s="202"/>
+      <c r="E74" s="202"/>
+      <c r="F74" s="202"/>
+      <c r="G74" s="202"/>
+      <c r="H74" s="202"/>
+      <c r="I74" s="202"/>
+      <c r="J74" s="202"/>
+      <c r="K74" s="202"/>
+      <c r="L74" s="202"/>
+      <c r="M74" s="202"/>
+      <c r="N74" s="202"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
     <mergeCell ref="B1:J2"/>
     <mergeCell ref="O4:O5"/>
     <mergeCell ref="D69:N74"/>
@@ -6739,6 +6773,11 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="B3:O3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -6748,10 +6787,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B56D240-6D8B-4144-A545-69291A6FAA07}">
   <dimension ref="C2:J40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C3" s="120" t="s">
         <v>154</v>
       </c>
@@ -6765,7 +6804,7 @@
       <c r="I3" s="23"/>
       <c r="J3" s="23"/>
     </row>
-    <row r="4" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C4" s="122" t="s">
         <v>155</v>
       </c>
@@ -6776,52 +6815,52 @@
       <c r="I4" s="23"/>
       <c r="J4" s="23"/>
     </row>
-    <row r="5" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C5" s="122"/>
       <c r="D5" s="123"/>
       <c r="H5" s="119"/>
       <c r="I5" s="23"/>
       <c r="J5" s="23"/>
     </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C6" s="209" t="s">
+    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C6" s="214" t="s">
         <v>191</v>
       </c>
-      <c r="D6" s="210"/>
-      <c r="E6" s="210"/>
-      <c r="F6" s="210"/>
-      <c r="G6" s="210"/>
-      <c r="H6" s="211"/>
+      <c r="D6" s="215"/>
+      <c r="E6" s="215"/>
+      <c r="F6" s="215"/>
+      <c r="G6" s="215"/>
+      <c r="H6" s="216"/>
       <c r="I6" s="23"/>
       <c r="J6" s="23"/>
     </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C7" s="212"/>
-      <c r="D7" s="213"/>
-      <c r="E7" s="213"/>
-      <c r="F7" s="213"/>
-      <c r="G7" s="213"/>
-      <c r="H7" s="214"/>
+    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C7" s="217"/>
+      <c r="D7" s="218"/>
+      <c r="E7" s="218"/>
+      <c r="F7" s="218"/>
+      <c r="G7" s="218"/>
+      <c r="H7" s="219"/>
       <c r="I7" s="23"/>
       <c r="J7" s="23"/>
     </row>
-    <row r="8" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C8" s="215"/>
-      <c r="D8" s="216"/>
-      <c r="E8" s="216"/>
-      <c r="F8" s="216"/>
-      <c r="G8" s="216"/>
-      <c r="H8" s="217"/>
+    <row r="8" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="220"/>
+      <c r="D8" s="221"/>
+      <c r="E8" s="221"/>
+      <c r="F8" s="221"/>
+      <c r="G8" s="221"/>
+      <c r="H8" s="222"/>
       <c r="I8" s="74"/>
       <c r="J8" s="74"/>
     </row>
-    <row r="9" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C9" s="74"/>
       <c r="D9" s="74"/>
       <c r="E9" s="74"/>
     </row>
-    <row r="10" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C11" s="160" t="s">
         <v>154</v>
       </c>
@@ -6834,7 +6873,7 @@
       <c r="G11" s="117"/>
       <c r="H11" s="118"/>
     </row>
-    <row r="12" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C12" s="162" t="s">
         <v>155</v>
       </c>
@@ -6843,41 +6882,41 @@
       </c>
       <c r="H12" s="119"/>
     </row>
-    <row r="13" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C13" s="162"/>
       <c r="D13" s="163" t="s">
         <v>192</v>
       </c>
       <c r="H13" s="119"/>
     </row>
-    <row r="14" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C14" s="209" t="s">
+    <row r="14" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C14" s="214" t="s">
         <v>194</v>
       </c>
-      <c r="D14" s="210"/>
-      <c r="E14" s="210"/>
-      <c r="F14" s="210"/>
-      <c r="G14" s="210"/>
-      <c r="H14" s="211"/>
-    </row>
-    <row r="15" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C15" s="212"/>
-      <c r="D15" s="213"/>
-      <c r="E15" s="213"/>
-      <c r="F15" s="213"/>
-      <c r="G15" s="213"/>
-      <c r="H15" s="214"/>
-    </row>
-    <row r="16" spans="3:10" ht="117" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C16" s="215"/>
-      <c r="D16" s="216"/>
-      <c r="E16" s="216"/>
-      <c r="F16" s="216"/>
-      <c r="G16" s="216"/>
-      <c r="H16" s="217"/>
-    </row>
-    <row r="18" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="D14" s="215"/>
+      <c r="E14" s="215"/>
+      <c r="F14" s="215"/>
+      <c r="G14" s="215"/>
+      <c r="H14" s="216"/>
+    </row>
+    <row r="15" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C15" s="217"/>
+      <c r="D15" s="218"/>
+      <c r="E15" s="218"/>
+      <c r="F15" s="218"/>
+      <c r="G15" s="218"/>
+      <c r="H15" s="219"/>
+    </row>
+    <row r="16" spans="3:10" ht="117" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="220"/>
+      <c r="D16" s="221"/>
+      <c r="E16" s="221"/>
+      <c r="F16" s="221"/>
+      <c r="G16" s="221"/>
+      <c r="H16" s="222"/>
+    </row>
+    <row r="18" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C19" s="165" t="s">
         <v>154</v>
       </c>
@@ -6890,7 +6929,7 @@
       <c r="G19" s="117"/>
       <c r="H19" s="118"/>
     </row>
-    <row r="20" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C20" s="167" t="s">
         <v>155</v>
       </c>
@@ -6899,39 +6938,39 @@
       </c>
       <c r="H20" s="119"/>
     </row>
-    <row r="21" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C21" s="167"/>
       <c r="D21" s="168"/>
       <c r="H21" s="119"/>
     </row>
-    <row r="22" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C22" s="209" t="s">
+    <row r="22" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C22" s="214" t="s">
         <v>195</v>
       </c>
-      <c r="D22" s="210"/>
-      <c r="E22" s="210"/>
-      <c r="F22" s="210"/>
-      <c r="G22" s="210"/>
-      <c r="H22" s="211"/>
-    </row>
-    <row r="23" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C23" s="212"/>
-      <c r="D23" s="213"/>
-      <c r="E23" s="213"/>
-      <c r="F23" s="213"/>
-      <c r="G23" s="213"/>
-      <c r="H23" s="214"/>
-    </row>
-    <row r="24" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C24" s="215"/>
-      <c r="D24" s="216"/>
-      <c r="E24" s="216"/>
-      <c r="F24" s="216"/>
-      <c r="G24" s="216"/>
-      <c r="H24" s="217"/>
-    </row>
-    <row r="26" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="D22" s="215"/>
+      <c r="E22" s="215"/>
+      <c r="F22" s="215"/>
+      <c r="G22" s="215"/>
+      <c r="H22" s="216"/>
+    </row>
+    <row r="23" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C23" s="217"/>
+      <c r="D23" s="218"/>
+      <c r="E23" s="218"/>
+      <c r="F23" s="218"/>
+      <c r="G23" s="218"/>
+      <c r="H23" s="219"/>
+    </row>
+    <row r="24" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C24" s="220"/>
+      <c r="D24" s="221"/>
+      <c r="E24" s="221"/>
+      <c r="F24" s="221"/>
+      <c r="G24" s="221"/>
+      <c r="H24" s="222"/>
+    </row>
+    <row r="26" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C27" s="170" t="s">
         <v>154</v>
       </c>
@@ -6944,7 +6983,7 @@
       <c r="G27" s="117"/>
       <c r="H27" s="118"/>
     </row>
-    <row r="28" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C28" s="172" t="s">
         <v>155</v>
       </c>
@@ -6953,43 +6992,43 @@
       </c>
       <c r="H28" s="119"/>
     </row>
-    <row r="29" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C29" s="172"/>
       <c r="D29" s="129"/>
       <c r="H29" s="119"/>
     </row>
-    <row r="30" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C30" s="209" t="s">
+    <row r="30" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C30" s="214" t="s">
         <v>196</v>
       </c>
-      <c r="D30" s="210"/>
-      <c r="E30" s="210"/>
-      <c r="F30" s="210"/>
-      <c r="G30" s="210"/>
-      <c r="H30" s="211"/>
-    </row>
-    <row r="31" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C31" s="212"/>
-      <c r="D31" s="213"/>
-      <c r="E31" s="213"/>
-      <c r="F31" s="213"/>
-      <c r="G31" s="213"/>
-      <c r="H31" s="214"/>
-    </row>
-    <row r="32" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C32" s="215"/>
-      <c r="D32" s="216"/>
-      <c r="E32" s="216"/>
-      <c r="F32" s="216"/>
-      <c r="G32" s="216"/>
-      <c r="H32" s="217"/>
-    </row>
-    <row r="34" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="35" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C35" s="218" t="s">
+      <c r="D30" s="215"/>
+      <c r="E30" s="215"/>
+      <c r="F30" s="215"/>
+      <c r="G30" s="215"/>
+      <c r="H30" s="216"/>
+    </row>
+    <row r="31" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C31" s="217"/>
+      <c r="D31" s="218"/>
+      <c r="E31" s="218"/>
+      <c r="F31" s="218"/>
+      <c r="G31" s="218"/>
+      <c r="H31" s="219"/>
+    </row>
+    <row r="32" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C32" s="220"/>
+      <c r="D32" s="221"/>
+      <c r="E32" s="221"/>
+      <c r="F32" s="221"/>
+      <c r="G32" s="221"/>
+      <c r="H32" s="222"/>
+    </row>
+    <row r="34" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C35" s="173" t="s">
         <v>154</v>
       </c>
-      <c r="D35" s="219">
+      <c r="D35" s="174">
         <f>D27+1</f>
         <v>5</v>
       </c>
@@ -6998,45 +7037,45 @@
       <c r="G35" s="117"/>
       <c r="H35" s="118"/>
     </row>
-    <row r="36" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C36" s="220" t="s">
+    <row r="36" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C36" s="175" t="s">
         <v>155</v>
       </c>
-      <c r="D36" s="221" t="s">
+      <c r="D36" s="176" t="s">
         <v>198</v>
       </c>
       <c r="H36" s="119"/>
     </row>
-    <row r="37" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C37" s="220"/>
-      <c r="D37" s="221"/>
+    <row r="37" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="175"/>
+      <c r="D37" s="176"/>
       <c r="H37" s="119"/>
     </row>
-    <row r="38" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C38" s="209" t="s">
+    <row r="38" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C38" s="214" t="s">
         <v>197</v>
       </c>
-      <c r="D38" s="210"/>
-      <c r="E38" s="210"/>
-      <c r="F38" s="210"/>
-      <c r="G38" s="210"/>
-      <c r="H38" s="211"/>
-    </row>
-    <row r="39" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C39" s="212"/>
-      <c r="D39" s="213"/>
-      <c r="E39" s="213"/>
-      <c r="F39" s="213"/>
-      <c r="G39" s="213"/>
-      <c r="H39" s="214"/>
-    </row>
-    <row r="40" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C40" s="215"/>
-      <c r="D40" s="216"/>
-      <c r="E40" s="216"/>
-      <c r="F40" s="216"/>
-      <c r="G40" s="216"/>
-      <c r="H40" s="217"/>
+      <c r="D38" s="215"/>
+      <c r="E38" s="215"/>
+      <c r="F38" s="215"/>
+      <c r="G38" s="215"/>
+      <c r="H38" s="216"/>
+    </row>
+    <row r="39" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C39" s="217"/>
+      <c r="D39" s="218"/>
+      <c r="E39" s="218"/>
+      <c r="F39" s="218"/>
+      <c r="G39" s="218"/>
+      <c r="H39" s="219"/>
+    </row>
+    <row r="40" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="220"/>
+      <c r="D40" s="221"/>
+      <c r="E40" s="221"/>
+      <c r="F40" s="221"/>
+      <c r="G40" s="221"/>
+      <c r="H40" s="222"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7053,7 +7092,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDA6BF67-58D9-44B8-9885-F86EBBDE6C60}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
